--- a/data/exports/validation_study/packets/week-2/packet-2.xlsx
+++ b/data/exports/validation_study/packets/week-2/packet-2.xlsx
@@ -544,7 +544,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2. 'techniques' sheet - the 15 attacks, mechanisms and defenses we recorded from your papers.</t>
+          <t>2. 'techniques' sheet - the 11 attacks, mechanisms and defenses we recorded from your papers.</t>
         </is>
       </c>
     </row>
@@ -2284,15 +2284,15 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>International Conference on Computer Science and Management Technology</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning.pdf</t>
+          <t>data/papers/SecureGov-Agent - A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents.pdf</t>
         </is>
       </c>
       <c r="G2" s="5" t="n"/>
@@ -2312,23 +2312,23 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ACL</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Skill-Inject - Measuring Agent Vulnerability to Skill File Attacks.pdf</t>
+          <t>data/papers/Robustness via Referencing - Defending against Prompt Injection Attacks by Referencing the Executed Instruction.pdf</t>
         </is>
       </c>
       <c r="G3" s="5" t="n"/>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -2348,15 +2348,15 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>data/papers/DRIFT - Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents.pdf</t>
+          <t>data/papers/Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing.pdf</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
@@ -2368,11 +2368,11 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Sentinel - SOTA model to protect against prompt injections.pdf</t>
+          <t>data/papers/Prompt Injection as Role Confusion.pdf</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
@@ -2396,19 +2396,23 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="D6" s="2" t="n"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>International Journal of Leading Research Publication</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>data/papers/ProjGuard - Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections.pdf</t>
+          <t>data/papers/The Convergent Cyber Threat Horizon in Financial Services - Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of.pdf</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
@@ -2420,15 +2424,15 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>Workshop on AI Systems with Confidential COmputing</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -2436,7 +2440,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>data/papers/ROMA - Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems.pdf</t>
+          <t>data/papers/Pandora - Jailbreak GPTs by Retrieval Augmented Generation Poisoning.pdf</t>
         </is>
       </c>
       <c r="G7" s="5" t="n"/>
@@ -2448,23 +2452,23 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Information Sciences</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Bridging AI and Software Security - A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms.pdf</t>
+          <t>data/papers/ToolSelf - Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation.pdf</t>
         </is>
       </c>
       <c r="G8" s="5" t="n"/>
@@ -2476,11 +2480,11 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -2492,7 +2496,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>data/papers/FoldAct - Efficient and Stable Context Folding for Long-Horizon Search Agents.pdf</t>
+          <t>data/papers/ConfusedPilot - Confused Deputy Risks in RAG-based LLMs.pdf</t>
         </is>
       </c>
       <c r="G9" s="5" t="n"/>
@@ -2504,23 +2508,19 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>NAACL</t>
-        </is>
-      </c>
+        <v>2025</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Attention Tracker - Detecting Prompt Injection Attacks in LLMs.pdf</t>
+          <t>data/papers/Bypassing LLM Guardrails - An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems.pdf</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
@@ -2532,11 +2532,11 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Memory in the LLM Era - Modular Architectures and Strategies in a Unified Framework.pdf</t>
+          <t>data/papers/Breaking the Prompt Wall (I) - A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection.pdf</t>
         </is>
       </c>
       <c r="G11" s="5" t="n"/>
@@ -2560,15 +2560,15 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>AISec@CCS</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>data/papers/MAD-Spear - A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems.pdf</t>
+          <t>data/papers/Neural Exec - Learning (and Learning from) Execution Triggers for Prompt Injection Attacks.pdf</t>
         </is>
       </c>
       <c r="G12" s="5" t="n"/>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -2596,15 +2596,15 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>International Conference on Evaluation of Novel Approaches to Software Engineering</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution.pdf</t>
+          <t>data/papers/A Trace-Based Assurance Framework for Agentic AI Orchestration - Contracts, Testing, and Governance.pdf</t>
         </is>
       </c>
       <c r="G13" s="5" t="n"/>
@@ -2616,19 +2616,23 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Think Twice Before You Act - Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning.pdf</t>
+          <t>data/papers/DE-FIVE - Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings.pdf</t>
         </is>
       </c>
       <c r="G14" s="5" t="n"/>
@@ -2640,7 +2644,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -2656,7 +2660,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>data/papers/TSUBASA - Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation.pdf</t>
+          <t>data/papers/PRISM - Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents.pdf</t>
         </is>
       </c>
       <c r="G15" s="5" t="n"/>
@@ -2668,23 +2672,19 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>IEEE Access</t>
-        </is>
-      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>data/papers/A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems.pdf</t>
+          <t>data/papers/Agent Memory - Characterization and System Implications of Stateful Long-Horizon Workloads.pdf</t>
         </is>
       </c>
       <c r="G16" s="5" t="n"/>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       <c r="H2" s="5" t="n"/>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       <c r="H3" s="5" t="n"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2857,7 +2857,7 @@
       <c r="H4" s="5" t="n"/>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F5" s="5" t="n"/>
@@ -2890,7 +2890,7 @@
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F6" s="5" t="n"/>
@@ -2923,7 +2923,7 @@
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>execution</t>
         </is>
       </c>
       <c r="F10" s="5" t="n"/>
@@ -3055,7 +3055,7 @@
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3121,7 +3121,7 @@
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3144,17 +3144,13 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Code released at https://cdn.openai.com/papers/red-teaming-reward-generation-code.zip covering the goal/reward generation pipeline; the authors also state they will release code for the jailbreaking experiments upon publication. No model weights or the generated attack datasets are released.</t>
-        </is>
-      </c>
+      <c r="E13" s="2" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3160,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3179,7 +3175,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Defender/target model: GPT-4 Turbo (GPT-4T). Attacker (red teamer): a GPT-3.5-sized model initialized from a checkpoint trained for instruction-following without safety guardrails (so it won't refuse to red-team), then further trained with RL. Grading models: automatically generated rule-based reward (RBR) LLM judges for indirect prompt injection, and OpenAI's Moderation API for safety jailbreaking (max score across categories, threshold 0.5).</t>
+          <t>Not named in the extracted material; the framework uses LLM embedding representations for content-risk scoring and operates over multi-agent deployments in the three evaluated scenarios.</t>
         </is>
       </c>
       <c r="F14" s="5" t="n"/>
@@ -3187,7 +3183,7 @@
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3193,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3212,7 +3208,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>No public benchmark is used; the authors construct two task-specific datasets. For indirect prompt injection: attacker goals auto-generated by GPT-4T combined with prior browsing/function-calling training data, yielding 4,664 training and 1,102 test examples (trained on injections into browsing responses, tested on function-calling responses). For safety jailbreaking: seeded from the Anthropic 'Harmless' dataset (Bai et al., 2022), pruned to single-user-message examples and converted via 3-shot prompting into (goal, criteria) pairs, yielding 5,000 training and 654 test examples. Evaluation metrics are attack success rate (ASR) and cosine-similarity-based diversity (overall and style-subspace-projected).</t>
+          <t>Purpose-built scenarios across three privacy-sensitive domains - medical consultation, financial advisory, and document processing - with synthesized attack scenarios used both for adversarial training and evaluation. Metrics are attack success rate, privacy leakage rate, task completion rate and latency overhead. The authors position the setup as a reproducible benchmark for multi-agent security research; no external benchmark is used.</t>
         </is>
       </c>
       <c r="F15" s="5" t="n"/>
@@ -3220,7 +3216,7 @@
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3226,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3245,7 +3241,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>For indirect prompt injection (Table 1, averaged over 10 inference steps): Baseline One-shot gets 0.02 ASR with 0.78 style diversity; RL with RBRs+Few-shot reward gets 0.32±0.10 ASR with 0.56±0.15 style diversity; Multistep RL gets 0.42±0.04 ASR with 0.50±0.14 style diversity; Multistep RL with Style Subspace gets 0.35±0.03 ASR with the highest style diversity among trained methods at 0.62±0.06 -- showing the method is the first to enable automated red-teaming for indirect prompt injections at all, with max ASR under 50% indicating the task is inherently hard. For safety jailbreaking (Table 2): Baseline One-shot achieves only 0.01 ASR but 0.67 style diversity; Vanilla RL (Perez et al. 2022) achieves near-100% ASR (0.96±0.05) but collapses to near-zero diversity (0.05±0.07 style); the Curiosity baseline (Hong et al. 2024) gets 0.69±0.42 ASR and 0.21±0.09 style diversity; the full Multistep RL with Style Subspace method achieves 0.79±0.13 ASR while reaching 0.48±0.04 style diversity -- substantially better diversity than Vanilla RL and Curiosity at a comparable or better success rate, and taking the best attack per trajectory, both Vanilla RL and Multistep RL reach 100% ASR. Ablations (RBR vs. Moderation vs. few-shot reward components, Figure 7/Appendix C.2) show the few-shot similarity reward contributes more to diversity than the RBR, and the red teamer tends to prioritize optimizing the Moderation signal over the RBR when both are combined.</t>
+          <t>Reports a balanced multi-objective outcome rather than optimizing one metric: attack success rates fall by 73.2% relative to unprotected systems and privacy leakage rates by 81.4%, while task completion is maintained at 89.7% with 15.3% latency overhead, and the absolute residual privacy leakage rate is 6.8%. Reporting security gains alongside task completion and latency is the methodologically valuable part - it makes the utility cost of governance explicit, which most defense papers in this corpus omit, and 15.3% overhead is a concrete figure a deployer can weigh. The privacy result is the strongest component and is the one the authors foreground. Two caveats temper the headline: the 73.2% ASR reduction is relative rather than absolute, so the residual attack success rate is not directly readable from it, and the adversarial training component means the system was trained on synthesized attack scenarios from the same generator used to construct the evaluation, which risks the evaluation measuring in-distribution robustness rather than generalization to unseen attacks. The paper positions its benchmark as reproducible for future multi-agent security research.</t>
         </is>
       </c>
       <c r="F16" s="5" t="n"/>
@@ -3253,7 +3249,7 @@
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3259,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3278,7 +3274,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Baseline One-shot (instruction-following model without safety guardrails, prompted one-shot at inference, no RL training); Vanilla RL (Perez et al. 2022, reward from Moderation API only, jailbreaking task only); Curiosity Baseline (Hong et al. 2024, diversity regularizer added to RL trainer, jailbreaking task only); single-step RL with RBRs + Few-shot reward (the paper's method without multi-step conditioning); Multistep RL (multi-step diversity reward without style-subspace restriction); and the full method, Multistep RL with Style Subspace.</t>
+          <t>Unprotected multi-agent systems serve as the reference point for the reported 73.2% ASR reduction and 81.4% privacy-leakage reduction, evaluated across medical consultation, financial advisory and document processing scenarios. Existing defenses are characterized as single-threat-vector approaches but are not reimplemented for head-to-head comparison, so the improvement is measured against no defense rather than against a competing governance framework.</t>
         </is>
       </c>
       <c r="F17" s="5" t="n"/>
@@ -3286,7 +3282,7 @@
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3292,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3309,17 +3305,13 @@
           <t>freetext</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Adversarial and offensive/red-teaming in nature: the paper trains an attacker LLM (red teamer) whose explicit objective is to generate prompts against a deployed target LLM (GPT-4 Turbo) that either (1) cause it to follow adversarially-injected instructions embedded in third-party content such as browsed webpages or tool/function-call outputs (indirect prompt injection), diverting it from the user's actual request, or (2) elicit responses that violate the model's safety policies (jailbreaking). The attacker is deliberately trained without safety guardrails so it will not refuse to red-team, and success is measured by automated judges (RBRs, Moderation API) rather than human review, explicitly to find and later patch model weaknesses via RL-driven, at-scale attack generation.</t>
-        </is>
-      </c>
+      <c r="E18" s="2" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3321,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3344,7 +3336,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit section 7, 'Conclusion, Limitations, and Future Work,' stating three main limitations: (1) 'jailbreaking' and 'red-teaming' remain broad, inconsistently-defined terms across the literature, making methods hard to compare since they make different implicit assumptions about which attacks are valuable, and further work is needed on consistent evaluation metrics for concepts like diversity and realisticness; (2) the method exhibits significant sensitivity common to RL training, with notable variance across runs and sensitivity to reward-shaping choices, which the authors say does not prevent usage but should be made more reliable in future work; (3) as with most automated red-teaming literature, the approach relies on automated graders both as RL rewards and as evaluation metrics, creating a risk of 'reward hacking' where the red teamer could be judged successful by exploiting weaknesses in the grader rather than the actual defender model -- the authors note only anecdotal evidence that narrower RBRs mitigate this and flag it as an open problem worthy of further study.</t>
+          <t>No explicit limitations section is surfaced in the extracted material, which is itself notable for a paper reporting this many favourable numbers. The main interpretive caution is the adversarial-training loop: robustness is enhanced by training on synthesized attack scenarios, and evaluation uses scenarios from the same construction pipeline, so the reported reductions may reflect in-distribution performance rather than resilience to novel attacks - no held-out or independently designed adversary is reported. Reductions are expressed relative to an unprotected baseline rather than as absolute residual attack success, making comparison with other defenses in this corpus difficult. The three risk components each carry unvalidated assumptions: NER-based privacy scoring inherits the recognizer's coverage gaps, and KL-divergence behavioural scoring requires an expected action distribution whose estimation and drift over long deployments are not discussed. Evaluation covers three scenario families constructed by the authors rather than an external multi-agent benchmark.</t>
         </is>
       </c>
       <c r="F19" s="5" t="n"/>
@@ -3352,7 +3344,7 @@
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3354,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3377,7 +3369,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>The paper targets a persistent tension in automated red-teaming: prior RL-based attackers (e.g., Perez et al. 2022, using a single toxicity/moderation reward) achieve high attack success rates but collapse to near-identical repeated attacks (mode collapse), while zero-/few-shot prompting approaches remain diverse but rarely succeed. The authors factor the problem into two stages: (1) auto-generating diverse attacker goals and (2) training an RL attacker to hit those goals effectively while staying diverse. For goal generation, they use either few-shot LLM prompting to invent (instruction, criteria) tuples directly, or transform existing datasets (e.g., Anthropic Harmless) into (instruction, criteria) pairs via few-shot rewriting; the 'criteria' becomes a zero-shot, per-example rule-based reward (RBR) -- an LLM classifier prompted with the specific criterion (e.g., 'Does this text urge daily exercise?') -- avoiding the need for one general toxicity classifier and enabling grading of tasks (like indirect prompt injection) with no single unifying success criterion. The attacker Am is trained via RL with a multiplicative reward combining: attack success (RBR score, or 0.5×RBR + 0.5×Moderation API score for unsafe-content generation), a few-shot similarity term anchoring the generated attack to its diverse one-shot example (preventing collapse), a length penalty discouraging padding-based pseudo-diversity, and, critically, a multi-step diversity reward: the attacker generates a sequence of T attacks per goal, each conditioned on prior attempts in the trajectory, rewarded for success and for being dissimilar (in embedding cosine-similarity space) from all prior attacks in that trajectory. To avoid diversity reward exploiting trivial topic changes, the authors compute this dissimilarity in a 'style subspace' obtained by projecting out the goal subspace (estimated via QR decomposition of goal-example embeddings) from the attack embeddings, isolating stylistic/tactical variation from semantic goal variation. The approach is applied to two applications against GPT-4 Turbo (using a GPT-3.5-sized, guardrail-free attacker): indirect prompt injection (the first automated red-teaming method for this threat, per the authors) and safety jailbreaking, where multi-step RL with the style-subspace diversity reward is shown to substantially increase attack diversity relative to single-step RL and prior baselines (Vanilla RL, Curiosity reward) while retaining competitive attack success rates, validating that decomposing goal-diversity from attack-generation and adding trajectory-level, style-aware diversity rewards jointly solve the diversity-effectiveness tradeoff that single-objective RL red-teaming suffers from.</t>
+          <t>Proposes SecureGov-Agent, a governance-centric multi-agent framework built on the argument that existing defenses address single threat vectors while multi-agent systems face backdoor attacks, prompt injection and privacy leakage simultaneously, requiring unified governance rather than point solutions. The design adds a dedicated Governance Agent with three responsibilities: monitoring inter-agent communications, auditing tool invocations, and enforcing security policies - i.e. it observes the coordination substrate rather than any single agent's inputs. Trustworthiness is assessed dynamically per agent through a multi-perspective risk score combining three formally specified components: Content Risk computed from LLM embedding representations through learned parameters and a sigmoid; Privacy Risk derived from Named Entity Recognition and pattern matching, aggregating per-entity PII probability weighted by entity-type sensitivity via a noisy-OR style product; and Behavioral Risk measured as the Kullback-Leibler divergence between an agent's observed action distribution and its expected distribution, capturing anomaly as a distributional shift rather than a rule violation. Robustness is further strengthened through adversarial training on synthesized attack scenarios. Evaluated across three privacy-sensitive application domains - medical consultation, financial advisory, and document processing. Relevant to this corpus as a multi-agent-channel defense spanning reasoning and execution intervention points, and as one of the few entries that treats privacy leakage and adversarial hijacking as a single governance problem rather than separate literatures.</t>
         </is>
       </c>
       <c r="F20" s="5" t="n"/>
@@ -3385,7 +3377,7 @@
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3387,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3418,7 +3410,7 @@
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>f3b3def5d2ed0bbec21a3825ea5cdbc7cd1c6f7e</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3420,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3451,7 +3443,7 @@
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>f3b3def5d2ed0bbec21a3825ea5cdbc7cd1c6f7e</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3453,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3484,7 +3476,7 @@
       <c r="H23" s="5" t="n"/>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>f3b3def5d2ed0bbec21a3825ea5cdbc7cd1c6f7e</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3486,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3509,7 +3501,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>neither</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F24" s="5" t="n"/>
@@ -3517,7 +3509,7 @@
       <c r="H24" s="5" t="n"/>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>f3b3def5d2ed0bbec21a3825ea5cdbc7cd1c6f7e</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3519,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3542,7 +3534,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>skill</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F25" s="5" t="n"/>
@@ -3550,7 +3542,7 @@
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>f3b3def5d2ed0bbec21a3825ea5cdbc7cd1c6f7e</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3552,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3583,7 +3575,7 @@
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>f3b3def5d2ed0bbec21a3825ea5cdbc7cd1c6f7e</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3585,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3616,7 +3608,7 @@
       <c r="H27" s="5" t="n"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>f3b3def5d2ed0bbec21a3825ea5cdbc7cd1c6f7e</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3618,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3649,7 +3641,7 @@
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>f3b3def5d2ed0bbec21a3825ea5cdbc7cd1c6f7e</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3651,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -3674,7 +3666,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>reasoning</t>
         </is>
       </c>
       <c r="F29" s="5" t="n"/>
@@ -3682,7 +3674,7 @@
       <c r="H29" s="5" t="n"/>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>f3b3def5d2ed0bbec21a3825ea5cdbc7cd1c6f7e</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -3692,7 +3684,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3707,7 +3699,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F30" s="5" t="n"/>
@@ -3715,7 +3707,7 @@
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>f3b3def5d2ed0bbec21a3825ea5cdbc7cd1c6f7e</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -3725,7 +3717,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3740,7 +3732,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F31" s="5" t="n"/>
@@ -3748,7 +3740,7 @@
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>f3b3def5d2ed0bbec21a3825ea5cdbc7cd1c6f7e</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3750,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3773,7 +3765,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Code is publicly available at https://github.com/LukeChen-go/robust-via-ref. The authors also construct and release a benchmark and training data built from existing datasets (AlpacaFarm, SQuAD, TriviaQA), with crafted injected instructions explicitly designed to be non-harmful/non-poisonous.</t>
         </is>
       </c>
       <c r="F32" s="5" t="n"/>
@@ -3781,7 +3773,7 @@
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>f3b3def5d2ed0bbec21a3825ea5cdbc7cd1c6f7e</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3783,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3806,7 +3798,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>OpenAI Codex agents: GPT-4, GPT-5.1-Codex-Max, GPT-5.1-Codex-Mini, GPT-5.2-Codex, GPT-5.2; Anthropic Claude Code agents: Haiku 4.5, Sonnet 4.5, Opus 4.5; Google Gemini CLI agents: Gemini 2.5 Flash, Gemini 2.5 Pro, Gemini 3 Flash, Gemini 3 Pro</t>
+          <t>Open-source models: Llama3-8B-Instruct, Qwen2-7B-Instruct, Llama3.1-8B-Instruct (primary experiments), and larger-scale Llama3-70B-Instruct, Llama3.1-405B-Instruct, Qwen2-72B-Instruct (scaling experiments). Closed-source models: GPT-4o-mini, GPT-4o, and GPT-4.1.</t>
         </is>
       </c>
       <c r="F33" s="5" t="n"/>
@@ -3814,7 +3806,7 @@
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>f3b3def5d2ed0bbec21a3825ea5cdbc7cd1c6f7e</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3816,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3839,7 +3831,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject (new benchmark introduced by this paper): 23 unique skills across document-processing, machine-learning, payment integrations, and healthcare domains; 8 attack categories (data exfiltration, data destruction, DoS, malware/ransomware deployment, phishing, backdoors, bias/manipulation, poisoning); 30 'obvious' harmful injections and 41 'contextual' injections, forming 76 obvious injection-task pairs and 126 contextual injection-task pairs (202 total)</t>
+          <t>Direct prompt injection: AlpacaFarm (208 samples, following Chen et al. 2024a's setup) with simple injected questions. Indirect prompt injection: a dataset built from SQuAD and TriviaQA (Inj-SQuAD, Inj-TriviaQA) with injected instructions crafted for phishing, advertisement, and propaganda objectives (following Chen et al. 2025b / Liu et al. 2024c). General utility evaluated on QA tasks (SQuAD, TriviaQA) and sentiment analysis (SST2). Five attack methods tested: Naive, Ignore, Escape-Character, Fake Completion (Fakecom), and Combined; plus gradient-based GCG and AutoDAN attacks in a separate experiment.</t>
         </is>
       </c>
       <c r="F34" s="5" t="n"/>
@@ -3847,7 +3839,7 @@
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>f3b3def5d2ed0bbec21a3825ea5cdbc7cd1c6f7e</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3849,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3872,7 +3864,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Frontier LLM agents are highly vulnerable to skill-based prompt injection: under baseline (no security context) conditions, contextual-injection execution rate ranges from 41.0% (Haiku 4.5) to 79.0% (Gemini 3 Flash), with most models exceeding 50%; OpenAI Codex models (GPT-5.1/5.2-Codex variants) are particularly vulnerable at above 65% ASR, while Anthropic Claude models are comparatively more robust (41-52%) but still non-trivially vulnerable. A 'warning' security-policy prompt reduces but does not eliminate ASR, while a 'legitimizing' policy often increases execution (expected, since the injected action is nominally authorized). Even unambiguously harmful ('obvious') injections (e.g. delete-all-files, ransomware, phishing) succeed up to 70% of the time and, under a best-of-5 repeated-attempt attack varying only injection line position, success rates rise substantially further (e.g. Gemini 3 Flash from 62.2% to 83.3%). Script-based attacks (malicious code hidden in an auxiliary script file referenced by the skill) achieve much higher ASR than direct text injections (+18.0 points for contextual, +9.0 for obvious injections), and injecting into the skill's YAML description field (loaded into the system prompt before the skill body) boosts success by 10.6 points on average (up to 16.8 points under the warning policy). LLM-as-judge screening for malicious skills has low false-positive rates on benign skills (88-99% correctly recommended) but poor detection of contextually-injected skills, especially under a legitimizing policy.</t>
+          <t>The proposed referencing-based defense achieves the lowest Attack Success Rate (ASR) across nearly all models, attack types, and scenarios, often reducing ASR to near 0%. In the direct-injection scenario (AlpacaFarm), the method surpasses all prompt-engineering baselines (Sandwich, Reminder, Instructional, Spotlight) by at least 19.71 percentage points across all attacks/models, achieving ASR as low as 0.00-2.88%, while also outperforming the fine-tuning baseline StruQ, which struggles to generalize to unseen attacks like Fakecom (StruQ reaches up to 30.29% ASR on Fakecom vs. the proposed method's 0-2.4%). In the more practical indirect-injection scenario (Inj-SQuAD/Inj-TriviaQA), the method achieves a maximum ASR of only 4.00% (Inj-SQuAD) and 7.00% (Inj-TriviaQA), versus a best prior baseline (Sandwich) floor of 19.67% ASR, and StruQ still fails against unknown attacks like Fakecom (up to 82.78% ASR) while the proposed method consistently defends across all baseline attacks. On larger models (70B-405B parameters), the method's maximum ASR is only 2.78%, substantially outperforming all baselines, though larger model size alone does not further improve defense performance, attributed to the reference-following instruction being simple enough for even smaller models to follow reliably. On closed-source models, the method achieves average ASR below 1% on GPT-4o and GPT-4.1 and as low as 0.22% on GPT-4o-mini, versus persistent vulnerability of Reminder/Instructional baselines under Fakecom/Combined attacks. Against gradient-based GCG and AutoDAN attacks, the method achieves 6.25%/8.65% ASR on Qwen2-7B-Instruct, outperforming StruQ's 10.10%/14.42%. Critically, the defense has minimal impact on general model utility: it does not degrade (and sometimes improves) QA accuracy, with only a 1.53% average sentiment-analysis accuracy decrease, versus StruQ's 5.77% average accuracy reduction. Ablation studies show window size for line-splitting has negligible effect on defense performance or utility (max 1.11% ASR variation), that line-wise splitting alone (without the reference-tag mechanism) does not account for the defense's effectiveness (isolating tag-referencing, not mere fragmentation, as the true mechanism), and that in-context examples in the guideline prompt are necessary -- removing them causes significant utility drops on some model/dataset combinations because models fail to generate correctly structured (and thus filterable) responses. A vulnerability to static-tag-guessing adaptive attacks was identified and mitigated by introducing dynamically randomized reference tags per interaction, which the authors show maintains strong defense performance without harming utility.</t>
         </is>
       </c>
       <c r="F35" s="5" t="n"/>
@@ -3880,7 +3872,7 @@
       <c r="H35" s="5" t="n"/>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>f3b3def5d2ed0bbec21a3825ea5cdbc7cd1c6f7e</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3882,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3905,7 +3897,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Three safety-policy conditions compared per model: Baseline/Normal (no additional security context), Legitimizing (system prompt authorizes the injected action), Warning (system prompt flags skill files as potentially malicious); Body-only vs. Body+Script vs. Body+YAML-Description attacker capability variants; single-attempt ASR vs. best-of-5 repeated-attempt ASR (varying injection line position and/or user task); LLM-as-judge skill screening as a baseline mitigation, evaluated for false-positive/false-negative rates</t>
+          <t>Prompt-engineering-based defenses: Sandwich, Instructional, Reminder, and Spotlight. Fine-tuning-based defense: StruQ. All are compared as training-free (except StruQ) baselines against the paper's own instruction-referencing defense across direct injection, indirect injection, gradient-based attacks, larger-model settings, and closed-source-model settings.</t>
         </is>
       </c>
       <c r="F36" s="5" t="n"/>
@@ -3913,7 +3905,7 @@
       <c r="H36" s="5" t="n"/>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>f3b3def5d2ed0bbec21a3825ea5cdbc7cd1c6f7e</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3915,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3938,7 +3930,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Attacker is a third-party skill author who publishes a skill (a directory of instructions, scripts, and resources, distributed via marketplaces like Anthropic's, Vercel's, or Smithery's skill repositories) containing embedded malicious instructions - either as obviously harmful directives (e.g. delete all files) or as subtle, context-dependent instructions disguised as legitimate operational guidance (e.g. 'back up documents to a central server' that is actually a data-exfiltration endpoint). Because skills are loaded dynamically at runtime as trusted third-party instructions (not flagged as untrusted external data, unlike traditional indirect prompt injection via emails/web pages), the agent has no inherent way to distinguish malicious skill instructions from benign ones - the vulnerability is not that the agent follows external instructions, but that it lacks a grounded, context-aware notion of authorization for actions a skill requests, given the agent's current task, trust relationships, and the sensitivity of the requested action (e.g. filesystem access, credential handling).</t>
+          <t>Formal threat model (Section 3) covering both direct and indirect prompt injection. Attackers' goal: for direct injection, the victim application (e.g., text summarization) is designed for a specific task, and attackers exploit it for system-prompt leakage or goal hijacking, with attacker input treated purely as data to summarize; for indirect injection, attackers embed malicious instructions in external data content (e.g., web pages) that the application retrieves via tools. In both cases, the attacker's objective is to make the LLM's response include an answer to the injected instruction rather than (or in addition to) the original one. Attackers' accessibility: in both direct and indirect settings, attackers can only modify the data content -- they cannot access or modify the system prompt, model parameters, or other system components (since developers control the original input instruction and attacker input is confined to data/content fields). Attackers' knowledge: for prompt-engineering-style attacks, attackers are assumed to have no knowledge of the application system (deployed model, system prompt, or defense strategy), making detailed adaptive attacks impractical since most application developers do not disclose such details; for gradient-based attacks (GCG, AutoDAN), attackers are assumed to know the target model and can optimize adversarial suffixes using gradient information. The paper separately analyzes and addresses a specific adaptive-attack risk against its own static reference-tag mechanism, motivating a dynamic/randomized tag variant.</t>
         </is>
       </c>
       <c r="F37" s="5" t="n"/>
@@ -3946,7 +3938,7 @@
       <c r="H37" s="5" t="n"/>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>f3b3def5d2ed0bbec21a3825ea5cdbc7cd1c6f7e</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3948,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3971,7 +3963,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>The evaluation covers a finite set of skills, tasks, and threat models (23 skills, 8 attack categories, 202 injection-task pairs), so results may shift with different agent implementations, additional skill types, or more adaptive attackers; the attacks studied are described as relatively simple to implement, and the authors explicitly note a real attacker could likely achieve a much higher attack success rate by optimizing the injection for a very specific task and tailoring it to a specific target model or agent scaffold, meaning the reported ASR figures likely understate a determined, adaptive attacker's true capability.</t>
+          <t>The paper has an explicit 'Limitations' section. The referencing defense's effectiveness depends on carefully designed prompts that teach the model how to reference instructions correctly, plus example outputs to guide it toward producing the correct structured format -- i.e., the method is not zero-shot-robust without this scaffolding. Regarding adaptive attacks, the authors acknowledge a non-zero probability that an attacker-chosen tag could coincide with the dynamically selected reference tag (defeating the dynamic-tag mitigation), though they note this probability is low and can be further reduced by enlarging the tag vocabulary. Finally, because the method is fundamentally a prompt-engineering approach rather than an architectural or training-based one, the authors state it is difficult to provide a formal mathematical robustness analysis or guarantee -- a limitation they note is shared by prior prompt-engineering-based defense approaches in the literature.</t>
         </is>
       </c>
       <c r="F38" s="5" t="n"/>
@@ -3979,7 +3971,7 @@
       <c r="H38" s="5" t="n"/>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>f3b3def5d2ed0bbec21a3825ea5cdbc7cd1c6f7e</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3981,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Skill-Inject: Measuring Agent Vulnerability to Skill File Attacks</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -4004,7 +3996,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Introduces Skill-Inject, the first benchmark for measuring prompt-injection vulnerabilities specific to agent 'skills' - third-party-distributed directories of instructions, scripts, and resources that LLM coding/personal-assistant agents (e.g. Claude Code, Gemini CLI, OpenAI Codex) dynamically load at runtime to extend their capabilities, creating a novel agent supply-chain attack surface distinct from traditional indirect prompt injection because skill instructions are treated as trusted rather than as external data to be filtered. The benchmark spans 23 real-world skills and 8 attack categories (data exfiltration, destruction, denial-of-service, malware/ransomware, phishing, backdoors, bias/manipulation, poisoning), split between unambiguously harmful 'obvious' injections and dual-use 'contextual' injections whose legitimacy depends on situational security policy (modeled via natural-language 'legitimizing' vs. 'warning' policy variants added to the system prompt), enabling measurement of the security-utility tradeoff rather than a binary safe/unsafe judgment. Evaluating 12 frontier models across three major agent scaffolds, the paper finds current agents are highly vulnerable (up to ~80% attack success rate even for obviously harmful instructions like data deletion or ransomware), that safety-policy prompting only partially mitigates the risk, that hiding the malicious payload in an auxiliary script or in the skill's YAML description (rather than plain text in the skill body) substantially increases attack success, that repeated/best-of-n attempts further amplify success rates, and that simple LLM-based skill-screening defenses catch obvious threats but largely fail on subtler contextual injections - arguing that robust defense requires context-aware, least-privilege authorization frameworks rather than model scaling or input filtering alone.</t>
+          <t>This paper proposes a prompt injection defense that inverts the dominant strategy in prior work: rather than suppressing an LLM's instruction-following tendency (which the authors show is empirically difficult to achieve reliably, since most existing defenses that instruct models to 'ignore' injected content still leave meaningful residual attack success), the method deliberately leverages the model's instruction-following ability. The motivating observation, drawn from analyzing successful attack transcripts, is that LLMs frequently and explicitly reference which instruction they are executing in their responses (e.g., 'For the second instruction...') even when that instruction is the maliciously injected one -- suggesting the model's internal representation of 'which instruction am I answering' is often reliably recoverable from its output, even when its choice of which instruction to obey is not controllable. The defense operationalizes this insight through a three-stage pipeline. First (Tagging and Splitting), since the exact location of an injected instruction within retrieved/data content is unknown a priori, the pipeline splits all data content into fixed-word-count lines and prefixes each with a unique location tag (e.g., '[L 3]'), while the original trusted instruction is placed as its own tagged, complete line; instruction and data regions are further demarcated with explicit '&lt;Instruction Area&gt;' / '&lt;Data Area&gt;' delimiters. Second (Prompting and Response Generation), a carefully engineered system prompt -- including explanatory guidance and in-context examples -- instructs the LLM to generate a structured response consisting of (tag, instruction, response) tuples for every instruction it identifies and executes, rather than a single free-form answer. Third (Filtering), a post-processing filter discards any (tag, instruction, response) tuple whose tag does not correspond to the tag of the original, trusted input instruction, retaining only the response segment that the model itself attributed to the legitimate instruction. Because the filtering mechanism relies on the model correctly and consistently tagging its own outputs, the authors identify and patch a specific vulnerability where an attacker who has learned the (static) tag format could craft an injected instruction using a matching tag to evade filtering, addressing this via a dynamically randomized reference-tag vocabulary sampled per interaction. Evaluated as a training-free, prompt-engineering-based method against both prompt-engineering-style baselines (Sandwich, Reminder, Instructional, Spotlight) and a fine-tuning-based baseline (StruQ) across direct injection (AlpacaFarm), indirect injection (SQuAD/TriviaQA-derived phishing/advertisement/propaganda injections), gradient-based optimization attacks (GCG, AutoDAN), model scales from 7B to 405B parameters, and both open- and closed-source models (including GPT-4o, GPT-4.1), the method consistently achieves state-of-the-art (often near-zero) attack success rates while imposing only minimal degradation on the model's general task utility, demonstrating that redirecting rather than suppressing an LLM's instruction-following behavior can be a more effective prompt-injection defense strategy than the conventional 'ignore the injected instruction' paradigm.</t>
         </is>
       </c>
       <c r="F39" s="5" t="n"/>
@@ -4012,7 +4004,7 @@
       <c r="H39" s="5" t="n"/>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>f3b3def5d2ed0bbec21a3825ea5cdbc7cd1c6f7e</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4014,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -4045,7 +4037,7 @@
       <c r="H40" s="5" t="n"/>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>867f0550f5e2d9a08d3c2094cf3c6bf05b90b6b5</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4047,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -4078,7 +4070,7 @@
       <c r="H41" s="5" t="n"/>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>867f0550f5e2d9a08d3c2094cf3c6bf05b90b6b5</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4080,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4111,7 +4103,7 @@
       <c r="H42" s="5" t="n"/>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>867f0550f5e2d9a08d3c2094cf3c6bf05b90b6b5</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4113,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -4136,7 +4128,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F43" s="5" t="n"/>
@@ -4144,7 +4136,7 @@
       <c r="H43" s="5" t="n"/>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>867f0550f5e2d9a08d3c2094cf3c6bf05b90b6b5</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4146,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4169,7 +4161,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F44" s="5" t="n"/>
@@ -4177,7 +4169,7 @@
       <c r="H44" s="5" t="n"/>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>867f0550f5e2d9a08d3c2094cf3c6bf05b90b6b5</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4179,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -4210,7 +4202,7 @@
       <c r="H45" s="5" t="n"/>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>867f0550f5e2d9a08d3c2094cf3c6bf05b90b6b5</t>
         </is>
       </c>
     </row>
@@ -4220,7 +4212,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4243,7 +4235,7 @@
       <c r="H46" s="5" t="n"/>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>867f0550f5e2d9a08d3c2094cf3c6bf05b90b6b5</t>
         </is>
       </c>
     </row>
@@ -4253,7 +4245,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4276,7 +4268,7 @@
       <c r="H47" s="5" t="n"/>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>867f0550f5e2d9a08d3c2094cf3c6bf05b90b6b5</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4278,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4301,7 +4293,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F48" s="5" t="n"/>
@@ -4309,7 +4301,7 @@
       <c r="H48" s="5" t="n"/>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>867f0550f5e2d9a08d3c2094cf3c6bf05b90b6b5</t>
         </is>
       </c>
     </row>
@@ -4319,7 +4311,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4342,7 +4334,7 @@
       <c r="H49" s="5" t="n"/>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>867f0550f5e2d9a08d3c2094cf3c6bf05b90b6b5</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4344,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4367,7 +4359,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F50" s="5" t="n"/>
@@ -4375,7 +4367,7 @@
       <c r="H50" s="5" t="n"/>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>867f0550f5e2d9a08d3c2094cf3c6bf05b90b6b5</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4377,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4400,7 +4392,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Project website at https://safo-lab.github.io/DRIFT. The paper does not explicitly confirm code release in the excerpted text, though the website is presented as the primary supplementary resource for the DRIFT framework.</t>
+          <t>N - no code or dataset release link stated in the text</t>
         </is>
       </c>
       <c r="F51" s="5" t="n"/>
@@ -4408,7 +4400,7 @@
       <c r="H51" s="5" t="n"/>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>867f0550f5e2d9a08d3c2094cf3c6bf05b90b6b5</t>
         </is>
       </c>
     </row>
@@ -4418,7 +4410,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4433,7 +4425,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>DRIFT is applied to four representative agent-backbone LLMs: GPT-4o, GPT-4o-mini (default/primary, GPT-4o-mini-2024-07-18), Claude-3.5-sonnet, and Claude-3.5-haiku. All three framework components (Secure Planner, Dynamic Validator, Injection Isolator) are themselves implemented as LLM-driven modules.</t>
+          <t>llama3:latest (served locally via Ollama)</t>
         </is>
       </c>
       <c r="F52" s="5" t="n"/>
@@ -4441,7 +4433,7 @@
       <c r="H52" s="5" t="n"/>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>867f0550f5e2d9a08d3c2094cf3c6bf05b90b6b5</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4443,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4466,7 +4458,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Three agent security benchmarks: AgentDojo (97 user tasks across 4 scenarios -- banking, Slack, travel, workspace -- for utility, plus 629 injection tasks for security), ASB (Agent Security Bench, 10 evaluation scenarios), and AgentDyn (a highly challenging open-ended-task agent benchmark used to stress-test dynamic-aware defenses). Metrics are Benign Utility (task completion rate absent attack), Utility Under Attack (task completion rate despite adversarial input), and (Targeted) Attack Success Rate (ASR).</t>
+          <t>484 real ICML 2025 (42nd ICML) accepted papers obtained via OpenReview, each rendered in 5 versions (1 baseline + 4 injected: English, Japanese, Chinese, Arabic)</t>
         </is>
       </c>
       <c r="F53" s="5" t="n"/>
@@ -4474,7 +4466,7 @@
       <c r="H53" s="5" t="n"/>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>867f0550f5e2d9a08d3c2094cf3c6bf05b90b6b5</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4476,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4499,7 +4491,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>On AgentDojo with GPT-4o-mini, DRIFT reduces ASR from 30.7% (undefended) to 1.4%, nearly matching the strongest security baseline CaMeL (0.0% ASR) while substantially exceeding CaMeL's utility -- DRIFT beats CaMeL by 18.9 points in no-attack utility and 15.5 points in utility-under-attack. On ASB, DRIFT achieves the best security among all compared defenses (4.8% ASR vs. runner-up Progent's 15.8% ASR) while maintaining competitive utility. On the harder open-ended AgentDyn benchmark, all defenses degrade substantially (e.g., prompt-based defenses like repeat_user_prompt and spotlighting still suffer &gt;35% ASR, and CaMeL collapses to 0% utility across all settings due to its static design failing on open-ended tasks), but DRIFT remains the most stable among dynamic defenses, achieving the best utility-security balance (ASR reduced to 3.1% while retaining meaningfully higher utility than CaMeL). An ablation (Table 1) shows each DRIFT component matters: adding only the static control/data-constraint policy (Secure Planner + Validator without dynamic updating) improves security but crashes Benign Utility from 63.55% to 43.22% (a 20.33-point drop) and Utility Under Attack from 48.27% to 36.17%; enabling the dynamic constraint-updating mechanism recovers utility to 58.48%/45.82% while preserving strong security, and adding the Injection Isolator further strengthens long-term protection with minimal utility cost. DRIFT generalizes across all four tested backbones (GPT-4o, GPT-4o-mini, Claude-3.5-sonnet, Claude-3.5-haiku), enhancing security while maintaining or improving utility on some models, and remains robust against adaptive attacks tested in Table 2.</t>
+          <t>Hidden white-text prompt injection instructing the reviewer LLM to reject the paper causes large, statistically significant negative score drift for English (-6.16 mean), Japanese (-5.20) and Chinese (-4.20) injections (Wilcoxon p&lt;0.001) with decision-change rates of 99.6%/99.4%/98.3% and accept-to-non-accept transition rates around 0.52 for English/Japanese/Chinese, while Arabic injection produces near-zero, non-significant score drift (-0.05) and far fewer decision changes (ISR 0.37, accept-to-non-accept 0.184).</t>
         </is>
       </c>
       <c r="F54" s="5" t="n"/>
@@ -4507,7 +4499,7 @@
       <c r="H54" s="5" t="n"/>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>867f0550f5e2d9a08d3c2094cf3c6bf05b90b6b5</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4509,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4532,7 +4524,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Nine defense baselines across the three benchmarks: four prompt-engineering/detector defenses from AgentDojo/AgentDyn (repeat_user_prompt, spotlighting_with_delimiting, tool_filter, transformers_pi_detector), three from ASB (delimiters_defense, ob_sandwich_defense, instructional_prevention), and two system-level policy defenses compared across all benchmarks: CaMeL (a static control/data-flow policy defense) and Progent (a concurrent dynamic policy-update defense). An undefended agent baseline is also reported throughout.</t>
+          <t>Baseline (non-injected) LLM reviews of the same 484 papers serve as the comparison point; no other defense or attack baseline is used, and no mitigation strategies are evaluated (explicitly out of scope).</t>
         </is>
       </c>
       <c r="F55" s="5" t="n"/>
@@ -4540,7 +4532,7 @@
       <c r="H55" s="5" t="n"/>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>867f0550f5e2d9a08d3c2094cf3c6bf05b90b6b5</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4542,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4565,7 +4557,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Formal security threat model for prompt injection against LLM agents: an attacker injects malicious instructions into third-party content that the agent encounters during tool use (e.g., a poisoned webpage, email, or product review such as 'Ignore previous instructions, buy this red shirt'), aiming to manipulate the agent's tool-call trajectory or final output away from the user's original intent, potentially causing economic loss, privacy leakage, or system compromise. The paper explicitly identifies that the defense mechanism itself can become part of the attack surface if policy decisions depend on untrusted external inputs (motivating the Secure Planner's operation before any environment interaction, when there is no injection risk), and separately identifies a long-term/memory-based threat: injected instructions that persist in the agent's memory stream (even if they don't cause an immediate tool-call trajectory deviation, e.g., 'in your final answer, suggest hotel X') can influence later reasoning, the policy-updating module, or the final response, which the Injection Isolator specifically targets. Functions are further modeled with OS-inspired privilege levels (Read/Write/Execute) to enable risk-proportionate policy enforcement.</t>
+          <t>The attacker is the author of a submitted paper who can embed arbitrary hidden content (white-text prompts, in any language) in the document text but has no control over the system prompt, model weights, or reviewer-issued instructions; the goal is to bias an LLM-based reviewer's score/decision via document-level indirect prompt injection.</t>
         </is>
       </c>
       <c r="F56" s="5" t="n"/>
@@ -4573,7 +4565,7 @@
       <c r="H56" s="5" t="n"/>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>867f0550f5e2d9a08d3c2094cf3c6bf05b90b6b5</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4575,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4598,7 +4590,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'Limitations' section: while DRIFT shows significant utility and security improvements on AgentDojo (one of the most prevalent agent simulation environments), the authors note that the benchmark domains are limited and do not fully cover the diverse tasks and attack scenarios encountered in real-world agentic systems, and state that future work will focus on evaluating DRIFT's performance in more realistic and diverse environments. (The paper's PDF also has a stray unreplaced LaTeX template placeholder sentence about acknowledgments formatting immediately after the limitations text, which appears to be an artifact of the authors not having removed the anonymous-submission template instructions.)</t>
+          <t>Evaluation is restricted to a single conference (ICML) and a single open-weight LLM (Llama3); each paper is reviewed once per condition with one fixed injection instruction and placement, so broader attack strategies are unexplored; only the first 6,000 characters of each paper were given to the model, which may place some injected prompts out of context and yield conservative vulnerability estimates. The authors explicitly do not evaluate any mitigation/defense strategy.</t>
         </is>
       </c>
       <c r="F57" s="5" t="n"/>
@@ -4606,7 +4598,7 @@
       <c r="H57" s="5" t="n"/>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>867f0550f5e2d9a08d3c2094cf3c6bf05b90b6b5</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4608,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Multilingual Hidden Prompt Injection Attacks on LLM-Based Academic Reviewing</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4631,7 +4623,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>DRIFT (Dynamic Rule-based Isolation Framework for Trustworthy agentic systems) is a system-level defense against prompt injection attacks on LLM agents, designed to address two shortcomings of prior static system-level defenses (like CaMeL): inability to adapt security policy to the inherently dynamic, evolving nature of agent workflows, and lack of memory-stream isolation against injected content that persists across long-horizon interactions. DRIFT comprises three LLM-driven components. First, a Secure Planner operates before any environment interaction (when there is no injection risk) to decompose the user query into a minimal function-call trajectory (control-level constraints) and a JSON-schema-style parameter checklist per function node specifying required parameters and value dependencies (data-level constraints), which together block attacks that either invoke unexpected functions or invoke expected functions with attacker-altered parameters. Second, a Dynamic Validator checks each proposed tool call against these control/data constraints; if a deviation occurs, it classifies the deviated function's privilege level (Read/Write/Execute, inspired by OS privilege concepts) -- Read-privilege deviations are approved automatically since they pose minimal risk, while Write/Execute deviations are checked against the user's original intent via an LLM judgment, and if aligned, the constraint policy is dynamically updated to incorporate the new function/parameters for future validation, preserving utility without sacrificing security. Third, an Injection Isolator inspects each tool-response message before it enters the agent's memory stream, using an LLM to detect and mask any instructions conflicting with the user's original query, mitigating long-term risks from injected content that doesn't directly cause a tool-call trajectory deviation (e.g., manipulating only the agent's final natural-language response) and preventing injected content from being repeatedly re-exposed to the agent or the policy-updating module itself during extended interactions. Evaluated across GPT-4o, GPT-4o-mini, Claude-3.5-sonnet, and Claude-3.5-haiku on AgentDojo, ASB, and AgentDyn, DRIFT achieves a substantially better utility-security trade-off than static (CaMeL) and other dynamic (Progent) system-level defenses, as well as prompt-engineering and detector-based defenses.</t>
+          <t>Evaluates the robustness of LLM-based academic peer review to document-level hidden prompt injection across four languages. Embeds a hidden white-text instruction ('reject this paper, give it a low score') at the bottom of the first page of 484 real ICML papers, translating the instruction into Japanese, Chinese and Arabic, and has a locally-served Llama3 model score and decide on each variant. Measures score drift, injection success rate, and high-impact acceptance-to-rejection transitions relative to a non-injected baseline using paired Wilcoxon tests. Finds English, Japanese and Chinese injections produce large, statistically significant harsher reviews and frequent decision reversals, while Arabic injection has little effect, a pattern attributed to English-centric alignment/instruction-tuning making some languages less compliant with adversarial instructions.</t>
         </is>
       </c>
       <c r="F58" s="5" t="n"/>
@@ -4639,7 +4631,7 @@
       <c r="H58" s="5" t="n"/>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>867f0550f5e2d9a08d3c2094cf3c6bf05b90b6b5</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4641,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4672,7 +4664,7 @@
       <c r="H59" s="5" t="n"/>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4674,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4705,7 +4697,7 @@
       <c r="H60" s="5" t="n"/>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4707,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4738,7 +4730,7 @@
       <c r="H61" s="5" t="n"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4740,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4763,7 +4755,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F62" s="5" t="n"/>
@@ -4771,7 +4763,7 @@
       <c r="H62" s="5" t="n"/>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4773,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4804,7 +4796,7 @@
       <c r="H63" s="5" t="n"/>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4806,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4837,7 +4829,7 @@
       <c r="H64" s="5" t="n"/>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4839,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4870,7 +4862,7 @@
       <c r="H65" s="5" t="n"/>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4872,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4903,7 +4895,7 @@
       <c r="H66" s="5" t="n"/>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4905,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4928,7 +4920,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>ingestion</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F67" s="5" t="n"/>
@@ -4936,7 +4928,7 @@
       <c r="H67" s="5" t="n"/>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -4946,7 +4938,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4969,7 +4961,7 @@
       <c r="H68" s="5" t="n"/>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4971,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5002,7 +4994,7 @@
       <c r="H69" s="5" t="n"/>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5004,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5027,7 +5019,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>The trained model itself is released on Hugging Face as qualifire/prompt-injection-sentinel (referenced throughout and demonstrated with a working code example in Appendix A using the transformers pipeline API). One of the evaluation datasets, qualifire/Qualifire-prompt-injection-benchmark, is also released on Hugging Face. However, the private qualifire-synthetics training dataset (1,400 samples) and the full curated training corpus are not released, explicitly limiting reproducibility of the training process itself.</t>
+          <t>Explicitly released: 'Code and project page at role-confusion.github.io' (stated in the abstract/introduction; also referenced as 'Project page at role-confusion.github.io' in the abstract).</t>
         </is>
       </c>
       <c r="F70" s="5" t="n"/>
@@ -5035,7 +5027,7 @@
       <c r="H70" s="5" t="n"/>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5037,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5060,7 +5052,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Sentinel (qualifire/prompt-injection-sentinel), a binary classifier fine-tuned from answerdotai/ModernBERT-large (28 layers, 395M parameters, RoPE positional embeddings, local-global alternating attention, FlashAttention/unpadding), is the paper's proposed model. It is compared against a single baseline classifier, protectai/deberta-v3-base-prompt-injection-v2 (185M parameters), based on DeBERTa-v3.</t>
+          <t>CoT Forgery attacks are tested against six frontier reasoning models: gpt-oss-20b, gpt-oss-120b, o4-mini, and the GPT-5 family (GPT-5 nano, GPT-5 mini, GPT-5 full). Role probes (internal representation classifiers) are trained/evaluated on four open-weight models in the 20-120B range: gpt-oss-20b, gpt-oss-120b, Nemotron-3-Nano, and Qwen3-30B-A3B(-Thinking).</t>
         </is>
       </c>
       <c r="F71" s="5" t="n"/>
@@ -5068,7 +5060,7 @@
       <c r="H71" s="5" t="n"/>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5070,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5093,7 +5085,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Training data aggregates seven open-source datasets (Salad-Data filtered for the 'O5: Malicious Use' category; alespalla/chatbot-instruction-prompts, 7,000 benign samples; microsoft/orca-agentinstruct-1M-v1, 7,000 benign samples; verazuo/jailbreak-llms; lmsys/toxic-chat; VMware/open-instruct, 7,000 benign samples; reshabhs/SPML-Chatbot-Prompt-Injection, 16,000 scenario-based-attack samples) plus one private dataset (qualifire-synthetics, 1,400 LLM-synthesized samples), combined to ~70% benign/30% jailbreak and split 90% train / 10% held-out internal test with no overlap. Public benchmark evaluation uses four external datasets: allenai/wildjailbreak, jackhhao/jailbreak-classification, deepset/prompt-injections, and the authors' own qualifire/Qualifire-prompt-injection-benchmark.</t>
+          <t>Primary evaluation uses StrongREJECT (a harmful-request/jailbreak benchmark) to measure Attack Success Rate (ASR) for CoT Forgery versus standard prompt injection. A separate agentic data-exfiltration task (100 attacks) tests whether an agent can be induced to upload a file to a remote server via standard prompt injection versus CoT Forgery. A broader evaluation of 1,000 agent exfiltration attempts is used to correlate probe-measured role confusion with real-world attack success. Role probes are trained on identical text wrapped in different role tags (e.g., &lt;user&gt;, &lt;tool&gt;, &lt;think&gt;) sampled from real model outputs (200 samples per condition cited for some experiments).</t>
         </is>
       </c>
       <c r="F72" s="5" t="n"/>
@@ -5101,7 +5093,7 @@
       <c r="H72" s="5" t="n"/>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5103,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5126,7 +5118,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On the internal held-out test set, Sentinel achieves 0.987 average accuracy, 0.991 recall, 0.980 F1, and 0.986 precision, versus the DeBERTa-v3 baseline's 0.848 accuracy and 0.728 F1 -- a 13.9-point accuracy improvement and a much larger F1 gap. On four public benchmarks (Binary F1), Sentinel averages 0.938 (0.935 wildjailbreak, 0.985 jailbreak-classification, 0.857 deepset/prompt-injections, 0.976 Qualifire's own benchmark) versus the baseline's 0.709 average (0.733/0.915/0.536/0.652 respectively) -- nearly a 23-point average F1 improvement despite Sentinel having roughly double the parameter count (0.395B vs 0.185B). Latency on an L4 GPU averaged approximately 0.02 seconds per inference, which the authors characterize as enabling real-time use on modest hardware.</t>
+          <t>Standard prompt injections largely fail against frontier models on StrongREJECT (0-2% ASR across most models, except gpt-oss-20b at 26%), consistent with near-perfect published safety-benchmark scores. CoT Forgery (injecting fabricated chain-of-thought reasoning into user prompts/tool outputs that models mistake for their own reasoning) bypasses these defenses entirely, raising ASR to 56-70% across all six tested models with near-zero baselines (gpt-oss-20b 56%, gpt-oss-120b 63%, o4-mini 70%, GPT-5 nano 57%, GPT-5 mini 60%, GPT-5 60%, GPT-5 full 59%), matching the abstract's headline ~60% figure. In the agentic data-exfiltration task, standard prompt injection largely fails while CoT Forgery dramatically increases success (Figure 3). A 'destyling' ablation that preserves the forged reasoning's logical argument while stripping stylistic/lexical markers characteristic of the target model's genuine chain-of-thought collapses ASR from 61% to 10% consistently across models, demonstrating that mimicked style -- not logical content -- causally drives the attack's success. Role probes (linear classifiers trained only on ground-truth role tags) misclassify prompt-injected text as its spoofed role rather than its true tagged role, showing the models' own internal representations conflate stylistic mimicry with genuine tag-based role identity; e.g., on Qwen3-30B-A3B, injecting user-style text into tool-tagged data causes measured 'Userness' to rise to 83.6% (versus expected near-0% if role tags were robustly tracked) with corresponding drops in true-role signal. Generalizing beyond CoT Forgery to 1,000 standard agent prompt-injection/exfiltration attempts, attack success rises near-monotonically with probe-measured role confusion, from 2% in the lowest confusion quantile to 70% in the highest, and a logistic regression predicting attack success from a Userness/Systemness ratio (controlling for declared template role) achieves 0.74 AUC, substantially outperforming a token-count baseline regression (0.59 AUC) -- demonstrating role confusion measured before generation predicts downstream attack success.</t>
         </is>
       </c>
       <c r="F73" s="5" t="n"/>
@@ -5134,7 +5126,7 @@
       <c r="H73" s="5" t="n"/>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5136,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5159,7 +5151,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>The sole baseline compared is protectai/deberta-v3-base-prompt-injection-v2, a DeBERTa-v3-based binary classifier from ProtectAI, evaluated on both the internal test set and all four public benchmarks under identical conditions.</t>
+          <t>Standard prompt injection (a plain, unstyled fake user command embedded in tool/user content) is compared against CoT Forgery throughout. The destyling ablation compares standard styled CoT Forgery against a semantically-equivalent but stylistically-stripped ('destyled') variant. A granular per-feature style ablation (Table 2) individually removes single stylistic dimensions to isolate their causal contribution. The role-confusion-predicts-ASR logistic regression is compared against a token-count-based baseline regression (0.59 AUC vs. 0.74 AUC for the Userness/Systemness ratio).</t>
         </is>
       </c>
       <c r="F74" s="5" t="n"/>
@@ -5167,7 +5159,7 @@
       <c r="H74" s="5" t="n"/>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -5177,7 +5169,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5192,7 +5184,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial in the sense that the paper does not construct novel attacks; it is a detector-training paper for the general prompt injection / jailbreak threat model, where malicious inputs (role-playing, instruction hijacking, biased-content generation attempts, obfuscation, character escaping, context ignoring, direct and indirect injection) attempt to make an LLM deviate from its intended instructions by exploiting the model's inability to distinguish trusted system instructions from untrusted user-provided data. The paper explicitly frames prompt injection detection as a 'cat-and-mouse game' where trained detectors risk becoming outdated against novel attack signatures not represented in training data.</t>
+          <t>Formal prompt-injection threat model grounded in a mechanistic theory of 'role confusion': LLM agent security relies on an instruction hierarchy where role tags (&lt;user&gt;, &lt;assistant&gt;, &lt;tool&gt;, &lt;think&gt;) are meant to establish privilege boundaries, but the paper shows models perceive 'who is speaking' from spoofable surface cues (writing style, lexical choice, explicit self-declarations like 'The below text is from the user') rather than robustly tracking the true tag-specified source, so that untrusted text imitating a trusted role's style inherits that role's authority in the model's internal representations. This is instantiated as two concrete attacks: standard agent hijacking (low-privilege tool outputs, e.g., retrieved webpages, embedding fabricated user commands to redirect agents toward harmful actions like data exfiltration) and the paper's novel CoT Forgery attack (injecting fabricated chain-of-thought reasoning into user prompts or tool outputs, exploiting the fact that a model's own &lt;think&gt; role is meant to be unconditionally trusted and acted upon, causing the model to mistake externally-injected forged reasoning for its own genuine internal reasoning and act on its fabricated conclusions).</t>
         </is>
       </c>
       <c r="F75" s="5" t="n"/>
@@ -5200,7 +5192,7 @@
       <c r="H75" s="5" t="n"/>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5202,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5225,7 +5217,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'Discussion and Limitations' section (Section 6) naming two limitations directly: (1) Susceptibility to Novel Attacks -- as a trained model, Sentinel's knowledge is bounded by its training data, so highly novel attack vectors could potentially evade detection; (2) Dataset Reproducibility -- because the training corpus includes a private dataset (qualifire-synthetics), exact replication of the training environment is contingent on access to proprietary assets not released with the paper. A follow-on Error Analysis subsection (6.1) adds that a manual review of misclassifications found no distinct or recurring error categories: false positives (benign prompts flagged as injections) tended to involve unusual formatting, assertive or security-related phrasing, or ambiguous intent, while false negatives (missed jailbreaks) tended to involve subtle adversarial phrasing not strongly resembling known attack patterns.</t>
+          <t>The paper has no section explicitly titled 'Limitations,' but Section 7.4 'Open Questions' functions as an explicit scope/limitations discussion: the role probes are validated on only four models in the 20-120B parameter range, and extending the analysis to larger models is left as future work; additionally, the linear probes assume roles occupy linearly-separable directional subspaces in representation space, an assumption the authors validate indirectly (via downstream ASR prediction and convergence across architectural tags, stylistic mimicry, and explicit declarations all activating similar geometry) rather than proving directly, leaving open whether more complex, non-linear role representations exist that the linear probing methodology would miss. The Impact Statement explicitly declines to highlight specific societal-consequence concerns beyond stating the general goal of advancing the ML field.</t>
         </is>
       </c>
       <c r="F76" s="5" t="n"/>
@@ -5233,7 +5225,7 @@
       <c r="H76" s="5" t="n"/>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5235,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5258,7 +5250,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Sentinel is a binary prompt-injection/jailbreak detection classifier built by fine-tuning answerdotai/ModernBERT-large -- a modernized bidirectional encoder-only Transformer pretrained on 2 trillion tokens of English and code with an 8,192-token native context length, using rotary positional embeddings, local-global alternating attention, and FlashAttention-based unpadding for efficient long-sequence processing -- on a purpose-curated dataset that consolidates seven open-source jailbreak/prompt-injection and benign-instruction datasets with one private, LLM-synthesized dataset targeting nuanced error correction and real-world misclassification patterns. The paper's primary contribution is empirical rather than architectural: it argues that superior detection performance stems from the combination of a stronger, longer-context base encoder (versus the smaller DeBERTa-v3 architecture used by the prior state-of-the-art baseline) and a deliberately diverse, error-corrected training corpus spanning role-playing attacks, instruction hijacking, biased-content-generation attempts, and scenario-based injection templates, rather than from any novel detection algorithm. The model is deployed as a standard Hugging Face sequence-classification pipeline, producing a benign/malicious label with a confidence score, and is positioned as a practical, low-latency (~0.02s/inference on an L4 GPU), open-source drop-in replacement for existing DeBERTa-based prompt-injection guardrails.</t>
+          <t>This paper provides a mechanistic explanation for why prompt injection attacks succeed against LLM agents despite architectural role-tag safeguards (e.g., &lt;user&gt;, &lt;assistant&gt;, &lt;tool&gt;, &lt;think&gt; tags) that are explicitly designed to establish privilege boundaries and prevent low-privilege content from usurping higher-privilege authority. The central finding is that models do not robustly track the true, tag-specified source of text; instead, they infer 'who is speaking' from spoofable surface cues such as writing style, lexical choice, or even explicit self-declarations, and when these cues conflict with the actual role tag (as in prompt injection, where untrusted content is deliberately styled to sound like a trusted role), the spoofable stylistic cues dominate the model's internal role perception -- a phenomenon the authors term 'role confusion.' To measure this directly rather than only inferring it from downstream behavior (which cannot distinguish role misperception from correctly-perceived-but-ignored role boundaries), the paper develops role probes: linear classifiers trained on identical text wrapped in different ground-truth role tags, so the probes can only learn how tags (not content style) affect internal representations; despite this training signal, the probes classify prompt-injected text as its spoofed role rather than its true tagged role, demonstrating that the model's own internal geometry, not just an external classifier's limitation, conflates stylistic mimicry with tag-based identity. Building on this mechanism, the paper introduces CoT Forgery, a novel zero-shot prompt injection attack that exploits the special trust granted to a model's own chain-of-thought (CoT) role: rather than injecting a fake user command directly, the attack injects fabricated reasoning traces -- text styled to match the target model's characteristic CoT patterns -- into user prompts or tool outputs, causing the model to mistake this externally-injected forged reasoning for its own genuine internal deliberation and act on its (attacker-controlled) conclusions. A causal ablation isolates that mimicked style, not the logical content of the forged argument, drives the attack's success: stripping stylistic markers while preserving the argument's semantics collapses attack success rates by roughly 6x. Finally, the paper shows this role-confusion mechanism generalizes beyond CoT Forgery to explain standard agent prompt-injection/data-exfiltration attacks, with probe-measured role confusion predicting attack success before a single output token is generated, positioning role confusion as a general, measurable, representational-level root cause of prompt injection rather than a collection of unrelated attack patterns that current pattern-matching/memorization-based defenses attempt to patch individually.</t>
         </is>
       </c>
       <c r="F77" s="5" t="n"/>
@@ -5266,7 +5258,7 @@
       <c r="H77" s="5" t="n"/>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5268,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5299,7 +5291,7 @@
       <c r="H78" s="5" t="n"/>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>755a7e22f482d59883ca4fcf361fb043ad969a57</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5301,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5332,7 +5324,7 @@
       <c r="H79" s="5" t="n"/>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>755a7e22f482d59883ca4fcf361fb043ad969a57</t>
         </is>
       </c>
     </row>
@@ -5342,7 +5334,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5365,7 +5357,7 @@
       <c r="H80" s="5" t="n"/>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>755a7e22f482d59883ca4fcf361fb043ad969a57</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5367,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5390,7 +5382,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F81" s="5" t="n"/>
@@ -5398,7 +5390,7 @@
       <c r="H81" s="5" t="n"/>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>755a7e22f482d59883ca4fcf361fb043ad969a57</t>
         </is>
       </c>
     </row>
@@ -5408,7 +5400,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5423,7 +5415,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F82" s="5" t="n"/>
@@ -5431,7 +5423,7 @@
       <c r="H82" s="5" t="n"/>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>755a7e22f482d59883ca4fcf361fb043ad969a57</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5433,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5464,7 +5456,7 @@
       <c r="H83" s="5" t="n"/>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>755a7e22f482d59883ca4fcf361fb043ad969a57</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5466,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5497,7 +5489,7 @@
       <c r="H84" s="5" t="n"/>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>755a7e22f482d59883ca4fcf361fb043ad969a57</t>
         </is>
       </c>
     </row>
@@ -5507,7 +5499,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5530,7 +5522,7 @@
       <c r="H85" s="5" t="n"/>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>755a7e22f482d59883ca4fcf361fb043ad969a57</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5532,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5555,7 +5547,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F86" s="5" t="n"/>
@@ -5563,7 +5555,7 @@
       <c r="H86" s="5" t="n"/>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>755a7e22f482d59883ca4fcf361fb043ad969a57</t>
         </is>
       </c>
     </row>
@@ -5573,7 +5565,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5596,7 +5588,7 @@
       <c r="H87" s="5" t="n"/>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>755a7e22f482d59883ca4fcf361fb043ad969a57</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5598,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5629,7 +5621,7 @@
       <c r="H88" s="5" t="n"/>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>755a7e22f482d59883ca4fcf361fb043ad969a57</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5631,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5658,7 +5650,7 @@
       <c r="H89" s="5" t="n"/>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>755a7e22f482d59883ca4fcf361fb043ad969a57</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5660,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5683,7 +5675,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Claude Opus 4.5, Claude Haiku 4.5, GPT-5.2, GPT-5.4 and Qwen3.5-9B as the agent models under evaluation.</t>
+          <t>None. No models are run or tested; the analysis is sector-strategic and draws on standards documents, incident disclosures and the published literature.</t>
         </is>
       </c>
       <c r="F90" s="5" t="n"/>
@@ -5691,7 +5683,7 @@
       <c r="H90" s="5" t="n"/>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>755a7e22f482d59883ca4fcf361fb043ad969a57</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5693,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5716,7 +5708,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>OSWorld as the base environment with the OS-Harm benchmark for prompt-injection scenarios in desktop agents, plus a matched subset of RiosWorld for cross-benchmark transfer. Tasks span web navigation, document editing, email, programming and multi-application workflows. Each run yields a structured trace of instruction, responses, executed actions, screenshots and final safety judgment.</t>
+          <t>No datasets or benchmarks. Evidence consists of primary standards documents (NIST CSF 2.0, EU DORA, and national regulator publications including UK, MAS Singapore, HKMA and US federal banking incident-notification rules), sector incident reports, and the emerging academic literature on generative AI, agentic systems, deepfakes and post-quantum cryptography.</t>
         </is>
       </c>
       <c r="F91" s="5" t="n"/>
@@ -5724,7 +5716,7 @@
       <c r="H91" s="5" t="n"/>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>755a7e22f482d59883ca4fcf361fb043ad969a57</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5726,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5749,7 +5741,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Safe and unsafe execution trajectories occupy distinguishable regions of a lightweight one-dimensional space. A Hashing (2048) plus Linear Discriminant Analysis configuration reaches a silhouette score of 0.953 and a Davies-Bouldin index of 0.524, which the authors argue is separation clear enough to support continuous online monitoring and early warning before an unsafe action executes.</t>
+          <t>No original measurement; the contribution is analytical and normative, drawing on primary standards documents, sector incident reports and emerging academic literature. The load-bearing claim is structural misalignment: the traditional security program is not merely under-resourced against the 2026-2032 environment but built on assumptions that no longer hold, so incremental hardening is insufficient and the response must be architectural and governance-led. For this corpus the useful content is its placement of indirect prompt injection against agentic pipelines as a named under-researched risk in a regulated, high-consequence sector - a domain where a successful injection converts directly into unauthorized financial action, aligning with the goal-hijack consequence class. The seven-domain defence framework's mapping to NIST CSF 2.0 and DORA is the paper's most concretely actionable element, since it translates the threat taxonomy into control families an institution is already obliged to report against. All quantitative and incident evidence is inherited from the cited standards documents and disclosures rather than generated here.</t>
         </is>
       </c>
       <c r="F92" s="5" t="n"/>
@@ -5757,7 +5749,7 @@
       <c r="H92" s="5" t="n"/>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>755a7e22f482d59883ca4fcf361fb043ad969a57</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5759,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5782,7 +5774,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>An agent performance baseline across observation settings precedes the injection experiments; the method is positioned against inference-time defenses that analyse each input with a second large model, on coverage and deployment cost.</t>
+          <t>Not applicable - no experimental component and no defense evaluated. Comparative work is against existing regulatory and standards frameworks (NIST Cybersecurity Framework 2.0, EU DORA) and against practitioner taxonomies from prior work, which the paper adopts and extends rather than measures.</t>
         </is>
       </c>
       <c r="F93" s="5" t="n"/>
@@ -5790,7 +5782,7 @@
       <c r="H93" s="5" t="n"/>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>755a7e22f482d59883ca4fcf361fb043ad969a57</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5792,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5813,17 +5805,13 @@
           <t>freetext</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>Computer-use agents operating real desktop operating systems, exposed to prompt injection, indirect instructions and visual attacks delivered through the environment they observe.</t>
-        </is>
-      </c>
+      <c r="E94" s="2" t="n"/>
       <c r="F94" s="5" t="n"/>
       <c r="G94" s="5" t="n"/>
       <c r="H94" s="5" t="n"/>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>755a7e22f482d59883ca4fcf361fb043ad969a57</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5821,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5848,7 +5836,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>The monitor is evaluated on desktop-agent trajectories from two benchmarks; the separation result is clustering-quality evidence rather than a deployed detection rate, and transfer is tested on a matched subset rather than the full RiosWorld benchmark.</t>
+          <t>The author states three limitations explicitly and they are unusually candid. First, the empirical base for several described trends is thin - specifically for Tier 3 agentic attacks and for harvest-now-decrypt-later exfiltration - reflecting both the recency of these threats and disclosure hesitancy among affected institutions; the expectation is that the picture will sharpen as DORA and SEC disclosure regimes mature and sector ISACs publish aggregated incident data. This directly qualifies the agentic-attack material most relevant to this corpus: it describes anticipated rather than measured risk. Second, the framework is a strategic orientation rather than an implementation specification, with appropriate concrete controls conditioned on institutional maturity, regulatory environment and risk appetite. Third, vendor and product recommendations are deliberately avoided for neutrality, which limits operational specificity. To these should be added that the five-vector taxonomy and seven-domain framework are proposed without validation - no institution is assessed against them and no evidence is offered that the mapping improves outcomes.</t>
         </is>
       </c>
       <c r="F95" s="5" t="n"/>
@@ -5856,7 +5844,7 @@
       <c r="H95" s="5" t="n"/>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>755a7e22f482d59883ca4fcf361fb043ad969a57</t>
         </is>
       </c>
     </row>
@@ -5866,7 +5854,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>The Convergent Cyber Threat Horizon in Financial Services: Artificial Intelligence, Agentic Systems, Deepfakes, Quantum Computing, and the Mythos of Large Language Models</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5881,7 +5869,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>A behavioural-trajectory safety monitor for computer-use agents: instead of inspecting prompts or inputs with a second model, it derives a scalar risk signal from the agent's accumulated interaction history at each step and checks online whether execution is drifting toward an unsafe region of a low-dimensional projection.</t>
+          <t>Sector-level strategic threat analysis for financial services, arguing that five simultaneous technology shocks - generative AI, agentic AI, synthetic media/deepfakes, cryptographically-relevant quantum computing, and what the author terms the institutional 'mythos' surrounding LLM capabilities - interact to produce a threat landscape qualitatively worse than any single force. The central argument is that conventional cybersecurity programs rest on four assumptions that are each individually breaking: scarce adversary labour (undermined by generative AI), durable cryptography (by quantum), trustworthy media (by deepfakes), and human-only identity (by agentic systems and non-human identity proliferation). Contributions are a five-vector threat taxonomy specific to financial services, a seven-domain unified defence framework mapped onto NIST Cybersecurity Framework 2.0 and the EU Digital Operational Resilience Act (DORA), and a prioritised 24-month preparedness roadmap for banks, insurers, asset managers, payment providers and market infrastructure operators. Relevant to this corpus for one of the four under-researched risks it foregrounds: indirect prompt injection against agentic pipelines, which it places alongside non-human identity proliferation, harvest-now-decrypt-later exposure of long-retention financial data, and a governance gap arising from uneven institutional understanding of what LLMs can actually do. Its distinctive framing for this SoK is the last of these - treating misplaced institutional beliefs about model capability as itself a security risk, which is a governance-layer analogue of the capability-misattribution problem rather than a technical attack channel.</t>
         </is>
       </c>
       <c r="F96" s="5" t="n"/>
@@ -5889,7 +5877,7 @@
       <c r="H96" s="5" t="n"/>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>755a7e22f482d59883ca4fcf361fb043ad969a57</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5887,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5922,7 +5910,7 @@
       <c r="H97" s="5" t="n"/>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5920,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5947,7 +5935,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F98" s="5" t="n"/>
@@ -5955,7 +5943,7 @@
       <c r="H98" s="5" t="n"/>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5953,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -5988,7 +5976,7 @@
       <c r="H99" s="5" t="n"/>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5986,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6013,7 +6001,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F100" s="5" t="n"/>
@@ -6021,7 +6009,7 @@
       <c r="H100" s="5" t="n"/>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6019,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6046,7 +6034,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>multi-agent</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F101" s="5" t="n"/>
@@ -6054,7 +6042,7 @@
       <c r="H101" s="5" t="n"/>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -6064,7 +6052,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6079,7 +6067,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F102" s="5" t="n"/>
@@ -6087,7 +6075,7 @@
       <c r="H102" s="5" t="n"/>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6085,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6112,7 +6100,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F103" s="5" t="n"/>
@@ -6120,7 +6108,7 @@
       <c r="H103" s="5" t="n"/>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6118,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6145,7 +6133,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F104" s="5" t="n"/>
@@ -6153,7 +6141,7 @@
       <c r="H104" s="5" t="n"/>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6151,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6186,7 +6174,7 @@
       <c r="H105" s="5" t="n"/>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6184,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -6211,7 +6199,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F106" s="5" t="n"/>
@@ -6219,7 +6207,7 @@
       <c r="H106" s="5" t="n"/>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6217,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -6252,7 +6240,7 @@
       <c r="H107" s="5" t="n"/>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6250,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -6277,7 +6265,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>The paper header explicitly links to a GitHub repository: 'https://github.com/sentient-agi/ROMA' -- a full open-source release of the ROMA framework.</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F108" s="5" t="n"/>
@@ -6285,7 +6273,7 @@
       <c r="H108" s="5" t="n"/>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6283,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -6310,7 +6298,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>GLM-4.6 (used as ROMA's backbone for the SEAL-0 and a second reasoning benchmark), DeepSeek-V3 and DeepSeek-V3.1 (used as ROMA's backbone for the EQ-Bench long-form writing evaluation), and DeepSeek-V3.2-Exp (used in an additional quality evaluation). Comparison points include Kimi-Researcher (a specialized closed research agent) and Claude Sonnet 4.5 (a leading closed-source model), among other closed- and open-source systems reported in the results tables.</t>
+          <t>Custom OpenAI GPTs backed by GPT-3.5-turbo and GPT-4-turbo (target victim systems); Mistral-7B (used by the attacker offline to generate uncensored malicious content, not evaluated as a victim)</t>
         </is>
       </c>
       <c r="F109" s="5" t="n"/>
@@ -6318,7 +6306,7 @@
       <c r="H109" s="5" t="n"/>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6316,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6343,7 +6331,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>SEAL-0, a benchmark evaluating reasoning over conflicting web evidence; a second reasoning benchmark (referenced via Table with GLM-4.6 baseline scores of 71.2/91.9 in different settings); and EQ-Bench, a long-form writing quality benchmark. An additional quality evaluation is conducted using DeepSeek-V3.2-Exp across multiple dimensions.</t>
+          <t>No public dataset - custom-built malicious content/document corpora crafted by the authors for 4 policy-violation scenarios (Adult Content, Harmful and Abusive Content, Privacy Violation Content, Illegal Content), 10 unique jailbreak prompts per scenario, 5 rounds each (100 tests per scenario)</t>
         </is>
       </c>
       <c r="F110" s="5" t="n"/>
@@ -6351,7 +6339,7 @@
       <c r="H110" s="5" t="n"/>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6349,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -6376,7 +6364,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>On SEAL-0, ROMA instantiated with GLM-4.6 achieves 45.9% accuracy, improving by 9.9 percentage points over Kimi-Researcher and substantially outperforming the underlying base model GLM-4.6 used standalone (14.5% accuracy) -- a more than 3x relative improvement purely from ROMA's recursive decomposition/aggregation architecture, using the same underlying model. On a second reasoning benchmark, ROMA (GLM-4.6) reaches 82.3% versus GLM-4.6 standalone's 71.2%, and in another setting reaches 93.9% versus GLM-4.6's 91.9% and DeepSeek-V3's 24.9%. With GEPA+ prompt optimization applied, ROMA with DeepSeek-V3.1 reaches 79.8% versus DeepSeek-V3.1 standalone's 73.6% and GLM-4.6's 70.0%, demonstrating GEPA+ provides additional gains on top of the base ROMA architecture. On EQ-Bench (long-form writing), ROMA enables DeepSeek-V3 to match the performance of leading closed-source models such as Claude Sonnet 4.5, despite DeepSeek-V3 being an open-weight model -- achieving competitive quality with manageable cost and latency. A quality evaluation with DeepSeek-V3.2-Exp shows ROMA improving scores across multiple quality dimensions (e.g., from 4.74/4.75/4.17/4.79 for the standalone model to 4.91/4.64/4.62/4.93 with ROMA, with gains on three of four dimensions and a comparable score on the remaining one).</t>
+          <t>PANDORA achieves an average jailbreak success rate of 64.3% on GPT-3.5-powered GPTs and 34.8% on GPT-4-powered GPTs across the four prohibited scenarios, versus only 3.0% and 1.0% respectively for naive direct jailbreak prompts on the same underlying models (ChatGPT) without RAG poisoning - demonstrating substantially higher effectiveness than direct jailbreak attacks. GPT-4-backed GPTs are consistently harder to jailbreak than GPT-3.5-backed ones across all four scenarios, attributed to improved alignment training. The Privacy-violation scenario is consistently the easiest to jailbreak (35.3% average success across model comparisons), suggesting scenario-dependent difficulty in content-policy circumvention.</t>
         </is>
       </c>
       <c r="F111" s="5" t="n"/>
@@ -6384,7 +6372,7 @@
       <c r="H111" s="5" t="n"/>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6382,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6409,7 +6397,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Underlying base models used standalone without ROMA's orchestration (GLM-4.6, DeepSeek-V3, DeepSeek-V3.1, DeepSeek-V3.2-Exp), the specialized closed-source research agent Kimi-Researcher, and leading closed-source models including Claude Sonnet 4.5, compared across the SEAL-0, EQ-Bench, and additional reasoning/quality benchmarks.</t>
+          <t>Direct (naive) jailbreak prompting on ChatGPT (GPT-3.5 and GPT-4 backends) without RAG poisoning, compared against PANDORA's RAG-poisoning-based indirect jailbreak on GPTs (GPT-3.5 and GPT-4 backends) across the same four prohibited scenarios</t>
         </is>
       </c>
       <c r="F112" s="5" t="n"/>
@@ -6417,7 +6405,7 @@
       <c r="H112" s="5" t="n"/>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6415,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -6442,7 +6430,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. This is a capability/systems-architecture paper on multi-agent orchestration frameworks, not a security paper; the incidental failure mode of interest is that current agentic frameworks underperform on long-horizon tasks because sequential orchestration becomes brittle as reasoning depth increases, context windows impose hard limits that degrade performance as execution history accumulates, and opaque execution traces make failures difficult to localize or debug -- collectively limiting the reliability, interpretability, and scalability of multi-step agentic systems on complex tasks.</t>
+          <t>Attacker has no direct access to the target LLM's weights or safety filters, but can upload attacker-crafted documents as a custom knowledge source into a Retrieval-Augmented Generation-enabled application (specifically OpenAI's custom GPTs, which let any user upload files as a knowledge base). The attacker generates malicious content (via web-crawling policy-violating keywords and an uncensored open-source LLM like Mistral-7B), refines it to evade keyword-based content filters (paraphrasing sensitive terms, avoiding refusal-trigger words, converting to PDF to bypass plaintext filtering, and passing through vector embeddings), packages it as topically-named documents, and crafts a system prompt that forces the GPT instance to retrieve-then-extend from this poisoned knowledge source for any user query - so that any end user interacting with the compromised GPT unknowingly receives jailbroken (policy-violating) responses.</t>
         </is>
       </c>
       <c r="F113" s="5" t="n"/>
@@ -6450,7 +6438,7 @@
       <c r="H113" s="5" t="n"/>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6448,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -6475,7 +6463,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>The paper contains an explicit 'Limitations and Future Work' section (Section 6) stating: ROMA 'does not guarantee optimal task decomposition or aggregation' -- atomization and MECE (mutually exclusive, collectively exhaustive) planning can fail, potentially producing redundant subtrees, missing subgoals, or inefficient execution; aggregation quality depends on model behavior and prompt design and may omit critical evidence or over-compress intermediate results, particularly under noisy or conflicting retrieval; parallel execution, while reducing wall-clock latency, can increase total compute cost and introduces practical coordination challenges including tool budgets, rate limits, and failure recovery across concurrent branches; and while ROMA mitigates context explosion by restricting local context and offloading artifacts, it 'does not eliminate long-context failure modes,' with the authors explicitly noting that 'stronger task-aware verification and compression mechanisms remain necessary for high-stakes or safety-critical applications.' The section also lists explicit future-work directions: learned or verifier-guided planning objectives that trade off reasoning depth, cost, and uncertainty; trace-driven automated error localization and repair (targeted re-planning or selective re-execution of failed subtrees); adaptive model routing based on expected value, latency, or reliability; and extending ROMA to multimodal and safety-critical tool use, which would require richer notions of provenance, permissions, and execution guarantees.</t>
+          <t>This is an explicitly preliminary/proof-of-concept evaluation (paper is a short work-in-progress-style paper): testing was limited to 10 prompts x 5 rounds x 4 scenarios (100 tests per scenario) due to GPTs' rate limits (40 queries per 3 hours) at time of writing, making large-scale analysis impractical; the current RAG-poisoning knowledge base is crafted manually rather than through an automated pipeline, limiting scale and diversity - the authors explicitly list automating RAG-poisoning content generation as future work; the current approach operates in a black-box manner with limited interpretability into why/how the attack succeeds, and improving this interpretability plus developing concrete mitigation/defense strategies are both explicitly deferred to future work rather than addressed in this paper.</t>
         </is>
       </c>
       <c r="F114" s="5" t="n"/>
@@ -6483,7 +6471,7 @@
       <c r="H114" s="5" t="n"/>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -6493,7 +6481,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -6508,7 +6496,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>ROMA (Recursive Open Meta-Agents) is a domain-agnostic multi-agent framework designed to address three structural failure modes of existing agentic systems on long-horizon tasks: brittle sequential orchestration as reasoning depth increases, hard context-window limits that degrade performance as raw execution history accumulates, and opaque execution traces that make failures difficult to localize or debug. ROMA's core mechanism is recursive task decomposition combined with structured aggregation: goals are decomposed into dependency-aware subtask trees whose independent branches can be executed in parallel (rather than strictly sequentially), while an aggregation step compresses and validates intermediate results from completed subtasks before they propagate upward, explicitly controlling context growth rather than letting it accumulate unboundedly. The framework standardizes agent construction around four modular, clearly separated roles: an Atomizer (which decides whether a given task is simple enough to execute directly or must be further decomposed), a Planner (which produces the dependency-aware subtask decomposition when needed), an Executor (which carries out atomic subtasks, potentially using different underlying models or tools), and an Aggregator (which compresses and validates the results of completed subtasks before passing them up the recursion tree). This role separation cleanly decouples orchestration logic from model selection, enabling heterogeneous multi-agent systems that mix different models and tools according to cost, latency, and capability trade-offs at each node of the execution tree, while producing transparent, hierarchical execution traces that make failures easier to localize than in opaque, monolithic agent pipelines. To adapt ROMA to specific tasks without requiring model fine-tuning, the paper additionally introduces GEPA+, an improved Genetic-Pareto prompt optimization method that searches over prompts within ROMA's component hierarchy (i.e., optimizing the Atomizer, Planner, Executor, and Aggregator prompts individually or jointly) while explicitly preserving the interface contracts between these modular roles, ensuring optimized prompts remain compatible with the framework's structured recursive control loop.</t>
+          <t>Introduces PANDORA, an indirect jailbreak attack against LLM-integrated applications that exploits Retrieval-Augmented Generation (RAG) rather than directly prompting the target model, termed 'RAG Poisoning.' The attack crafts malicious documents (via web-crawling policy-violating keywords, generating content with an uncensored LLM like Mistral-7B, and refining it to evade keyword-based and perplexity-based content filters - e.g. replacing sensitive terms, avoiding refusal-trigger words, and converting to PDF to bypass plaintext filtering and go through vector embedding instead), uploads them as the knowledge base of a custom OpenAI GPT instance, and pairs this with a specially crafted system prompt that forces the GPT to retrieve-then-extend content from the poisoned knowledge source for any user query - so any end user's normal question is silently redirected through the tainted RAG pipeline into a jailbroken (policy-violating) response, without the user needing to craft any adversarial prompt themselves. Evaluated as a proof-of-concept across four content-policy-violation scenarios (Adult, Harmful/Abusive, Privacy, Illegal) on GPT-3.5- and GPT-4-backed custom GPTs, PANDORA achieves substantially higher jailbreak success (64.3% and 34.8% respectively) than naive direct jailbreak prompting on the same underlying models (3.0% and 1.0%), demonstrating that RAG integration introduces a novel and significantly more effective indirect jailbreak attack surface that bypasses text-based safety filters designed for direct prompts.</t>
         </is>
       </c>
       <c r="F115" s="5" t="n"/>
@@ -6516,7 +6504,7 @@
       <c r="H115" s="5" t="n"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6514,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -6549,7 +6537,7 @@
       <c r="H116" s="5" t="n"/>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6547,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -6574,7 +6562,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F117" s="5" t="n"/>
@@ -6582,7 +6570,7 @@
       <c r="H117" s="5" t="n"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6580,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -6615,7 +6603,7 @@
       <c r="H118" s="5" t="n"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -6625,7 +6613,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -6648,7 +6636,7 @@
       <c r="H119" s="5" t="n"/>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6646,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -6673,7 +6661,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F120" s="5" t="n"/>
@@ -6681,7 +6669,7 @@
       <c r="H120" s="5" t="n"/>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6679,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -6706,7 +6694,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>reasoning-corruption</t>
         </is>
       </c>
       <c r="F121" s="5" t="n"/>
@@ -6714,7 +6702,7 @@
       <c r="H121" s="5" t="n"/>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6712,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -6739,7 +6727,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F122" s="5" t="n"/>
@@ -6747,7 +6735,7 @@
       <c r="H122" s="5" t="n"/>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -6757,7 +6745,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -6780,7 +6768,7 @@
       <c r="H123" s="5" t="n"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6778,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -6813,7 +6801,7 @@
       <c r="H124" s="5" t="n"/>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -6823,7 +6811,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -6838,7 +6826,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>one-shot</t>
+          <t>session-persistent</t>
         </is>
       </c>
       <c r="F125" s="5" t="n"/>
@@ -6846,7 +6834,7 @@
       <c r="H125" s="5" t="n"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6844,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -6879,7 +6867,7 @@
       <c r="H126" s="5" t="n"/>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -6889,7 +6877,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -6904,7 +6892,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Code and experimental materials are publicly available at https://github.com/theconsciouslab-ai/llm-agent-security, including the unified threat classification framework, attack simulation implementations, and the extensible testing framework for evaluating LLM agents across both Function Calling and MCP paradigms.</t>
+          <t>Code released at https://github.com/lian-tian-mo-zun/ToolSelf.git (stated in a footnote on the first page). The paper also references training data, prompt templates (Appendix A.9), and trajectory-judge configurations but does not separately mention a standalone dataset release beyond the code repository.</t>
         </is>
       </c>
       <c r="F127" s="5" t="n"/>
@@ -6912,7 +6900,7 @@
       <c r="H127" s="5" t="n"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6910,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -6937,7 +6925,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Seven language models deployed across two major cloud providers (Azure and AWS) and two tool-calling architectural paradigms (Function Calling and MCP), including O1, O3-mini, Claude 3-5, Claude 3-7, Claude Haiku, GPT-4.1, and at least one additional model (the paper explicitly names O1, O3-mini, Claude 3-7 as reasoning models, and Claude 3-5, GPT-4.1, Claude Haiku as specific data points in results).</t>
+          <t>Qwen3-8B and Qwen3-14B are used as the base execution-agent models trained with the proposed Configuration-Aware Two-stage Training (CAT); teacher trajectories for cold-start RFT are generated by Qwen3-235B-A22B-Thinking. Qwen2.5-72B-Instruct is used separately as an LLM-as-Judge (temperature=0.0, top_p=1.0) to classify emergent adaptive behaviors from trajectories in the appendix analysis (Table 3). Baselines span Vanilla Agent, OpenHands, WebSailor, SWE-Agent, Co-Sight, SWE-Search, AutoAgent, OWL, ReSum, and OAgents.</t>
         </is>
       </c>
       <c r="F128" s="5" t="n"/>
@@ -6945,7 +6933,7 @@
       <c r="H128" s="5" t="n"/>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -6955,7 +6943,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -6970,7 +6958,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>No pre-existing benchmark dataset is used; the authors construct their own unified threat classification framework (Table 1) covering nine primary attack vectors spanning both AI-specific threats (prompt injection, indirect prompt injection) and traditional software vulnerabilities (JSON injection, tool injection, denial-of-service), informed by frameworks such as ATFAA. They generate 3,250 total attack scenarios across three complexity tiers -- simple (single-vector), composed (multi-technique using function compositions), and chained (multi-stage, traversing system nodes sequentially) -- tested against both Function Calling and MCP deployment paradigms across the seven models and two cloud providers.</t>
+          <t>Five evaluation datasets from four long-horizon agent benchmarks: FRAMES and xbench (deep research), GAIA and GAIA(WS) (a 103-sample WebSailor subset solvable via search/browsing only) for general AI assistant tasks, and SWE-bench Lite for software engineering. MathVista is used only as a supplementary training dataset, not for evaluation.</t>
         </is>
       </c>
       <c r="F129" s="5" t="n"/>
@@ -6978,7 +6966,7 @@
       <c r="H129" s="5" t="n"/>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6976,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -7003,7 +6991,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Overall, Function Calling showed a higher aggregate attack success rate (73.5% ASR) than MCP (62.59% ASR), but the vulnerability profile inverts by threat type: Function Calling exhibits substantially higher system-centric ASR (87.98%, later cited as 92.27% for Azure specifically) due to tightly-coupled LLM orchestration/tool-registry/execution layers and heavy reliance on JSON schemas, whereas MCP exhibits higher LLM-centric ASR (68.28%) due to its context-rich, standardized prompt-passing and persistent session management expanding attack surface for reasoning-targeted threats; MCP's client-server separation correspondingly gives it a lower system-centric ASR (57%). Provider comparison within Function Calling shows Azure (no system role access) is more resistant to LLM-centric attacks (55.42% vs. AWS's 63%) but more vulnerable to system-centric attacks (92.27% vs. AWS's 84.76%), with both providers converging to a similar overall ASR (~74%). A counterintuitive model-level finding: models with stronger reasoning capabilities (O1, O3-mini, Claude 3-7) show better initial threat detection (averaging 17.8% Refusal Rate vs. non-reasoning models) yet the most capable/sophisticated models exhibit the highest overall attack success once defenses are breached -- Claude 3-5 (75% ASR) and GPT-4.1 (72% ASR) represent peak vulnerability, while the more narrowly-optimized Claude Haiku achieves a more balanced profile (65.56% ASR, 18.37% RR); even within the same Anthropic Responsible Scaling Policy tier (ASL-2), Claude 3-5 and Claude Haiku show a 9.44-percentage-point ASR gap, demonstrating static safety classifications alone cannot predict model-specific vulnerability. Attack complexity dramatically amplifies effectiveness: simple attacks achieved only ~50% ASR on most vectors (with DoS attacks at 0% ASR due to cloud-provider safeguard interception), but composed attacks showed diverging architectural effects -- Function Calling ASR rose from 56% to 70% under composition (tight coupling accelerates multi-stage propagation), while MCP ASR actually decreased from 60% to 51.32% under composition (client-server separation impedes multi-stage propagation) -- though composed attacks did succeed in circumventing DoS-specific cloud safeguards by embedding DoS techniques within prompt-injection vectors. Chained (multi-stage) attacks achieved the highest and most consistent success rates across both paradigms, reaching 91-96% ASR (up to 88-96% via contextual-poisoning pathways in MCP), dramatically exceeding any single-vector baseline and demonstrating that single-vector security assessments substantially underestimate real-world risk.</t>
+          <t>ToolSelf outperforms all static-configuration, pre-execution-optimization, planner-worker, and configuration-patching baselines across both model scales: on Qwen3-14B it averages 37.8% versus the Vanilla Agent's 25.9%, and on Qwen3-8B it averages 31.0% versus 15.2% (Table 1), a roughly 28.8-point gain over the static-configuration baseline as stated in the abstract. Ablating CAT (Table 2) shows progressive gains on Qwen3-8B from a 16.5% Vanilla Agent average to 27.3% for the best baseline to 35.3% for full ToolSelf+RFT+KTO. On GAIA specifically (Table 5), ToolSelf raises accuracy from 19.7% (Vanilla Agent) to 35.2% while using only 11.6K/39.4K/71.0K total tokens per task at Level 1/2/3, versus Co-Sight's 229K/261K/315K tokens -- roughly 19.8x/6.6x/4.4x higher token efficiency, attributed to agent-driven context management keeping max input length bounded near 13K-15K tokens even as exploration deepens. Component ablation (Table 6) shows removing context management drops GAIA accuracy from 35.2% to 33.9%, and removing the 'Knowledge' component causes the largest drop (to 27.3%), with sub-goal and toolbox reconfiguration also contributing measurably.</t>
         </is>
       </c>
       <c r="F130" s="5" t="n"/>
@@ -7011,7 +6999,7 @@
       <c r="H130" s="5" t="n"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7009,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -7036,7 +7024,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>No prior defense systems are directly benchmarked as external baselines; the study's comparative structure is internal -- Function Calling vs. MCP architectural paradigms, Azure vs. AWS cloud-provider implementations of Function Calling, seven different LLM backbones (reasoning vs. non-reasoning models), and three attack-complexity tiers (simple vs. composed vs. chained) -- used to isolate how architecture, provider, model capability, and attack sophistication each independently and interactively affect vulnerability.</t>
+          <t>General-purpose static-configuration agents (Vanilla Agent, OpenHands); task-specialized static agents (WebSailor, SWE-Agent, Co-Sight, SWE-Search); a pre-execution optimization method (AutoAgent); a planner-worker orchestration method (OWL); and configuration-patching methods (ReSum, OAgents). All are organized under a taxonomy distinguishing when/how configuration adaptation occurs relative to execution.</t>
         </is>
       </c>
       <c r="F131" s="5" t="n"/>
@@ -7044,7 +7032,7 @@
       <c r="H131" s="5" t="n"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7042,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -7069,7 +7057,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>The paper develops a structured, three-stage threat modeling and attack-simulation framework (Section 3.2, Figure 3) rather than a single fixed adversary definition, explicitly designed to enable comparative analysis across the two deployment paradigms. Stage 1 (Attack Surfaces Identification) systematically maps four vulnerable components: System Prompt, User Prompt, Tool Parameters, and Tool Output. Stage 2 (Attack Vector Classification) categorizes exploitation techniques into four types: Prompt Injection, Indirect Prompt Injection, JSON Injection, and Tool Injection, unified into a nine-primary-attack-vector taxonomy (Table 1) spanning both AI-specific threats (T1, T2, T5, T8 -- LLM-centric, e.g. reasoning-process manipulation) and traditional software vulnerabilities (T3, T4 -- system-centric, e.g. tool registry/execution compromise), explicitly framed against the CIA (Confidentiality, Integrity, Availability) triad adapted for LLM agents' probabilistic outputs and autonomous decision-making. Stage 3 (Attack Progression) models how attacks evolve in complexity from simple (single-vector exploits targeting individual surfaces) to composed (multi-technique exploits using function compositions) to chained (multi-stage exploits traversing system nodes sequentially), with formal ASR composition equations (e.g., ASR of a chain as the product of conditional per-step success probabilities). Two complementary evaluation metrics are defined: Attack Success Rate (ASR, probability of successful exploitation) and Refusal Rate (RR, the agent's explicit rejection of malicious requests), validated via LLM-as-judge scoring.</t>
+          <t>N/A - non-adversarial. This is a capability/systems paper on unifying task execution and runtime self-reconfiguration, not a security paper. The incidental failure mode of interest is that decoupled or static-configuration agents (fixed persona/toolbox/context strategy chosen before or separately from execution) underperform and waste tokens relative to agents that can dynamically reconfigure their own sub-goals, strategy, toolbox, and context management as part of a single unified action space during execution.</t>
         </is>
       </c>
       <c r="F132" s="5" t="n"/>
@@ -7077,7 +7065,7 @@
       <c r="H132" s="5" t="n"/>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7075,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -7102,7 +7090,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>The paper has a dedicated 'Study Limitations' subsection (Section 7.3, before the Conclusion) enumerating five specific constraints. Model/provider coverage: the evaluation spans seven LLM models across two major cloud providers, a substantial but non-exhaustive market sample; excluding emerging models/providers may limit generalizability, especially as rapid LLM evolution means model-specific vulnerability patterns may shift as architectures and safety mechanisms change. Architectural scope: the focus on Function Calling and MCP paradigms may not capture security implications of emerging decentralized agent-communication architectures (e.g., Google's A2A Protocol, IBM's ACP, Microsoft's multi-agent orchestration, Amazon's MARCO framework), which introduce peer-to-peer interactions, dynamic discovery, and autonomous collaboration patterns fundamentally different from the hierarchical/client-server models studied, potentially creating novel attack surfaces (inter-agent trust relationships, decentralized state management) the current analysis cannot address. Threat-taxonomy scope: the unified framework covers nine primary attack vectors derived from current literature and observed patterns, but the dynamic threat landscape means novel attack categories may emerge beyond this framework, motivating future systematic evaluation of emerging vectors. Temporal validity: findings represent a snapshot of security postures at time of testing; the security landscape evolves rapidly with new defensive mechanisms, model updates, and architectural improvements, and given the reactive nature of security improvements following vulnerability disclosure, current defensive capabilities may differ from what was measured. Deployment scope: analysis focused on cloud-based deployments via established APIs, which may not capture edge deployments, hybrid architectures, or custom implementation patterns, so organizations using alternative deployment strategies may see different vulnerability profiles than reported.</t>
+          <t>Explicit 'A.8 Limitations' section (brief, two sentences). First, the work focuses on whether an agent can internalize configuration of sub-goal, strategy, toolbox, and context management as learnable actions under a fixed global tool pool: ToolSelf can dynamically select tools from the existing pool at runtime but does not create new tools for unseen tasks, with dynamic tool creation/synthesis noted as orthogonal future work. Second, because self-reconfiguration introduces additional model calls, deploying ToolSelf in real-time systems may incur extra latency.</t>
         </is>
       </c>
       <c r="F133" s="5" t="n"/>
@@ -7110,7 +7098,7 @@
       <c r="H133" s="5" t="n"/>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7108,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Bridging AI and Software Security: A Comparative Vulnerability Assessment of LLM Agent Deployment Paradigms</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -7135,7 +7123,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>This paper presents the first comprehensive comparative security evaluation bridging AI-specific and traditional software-security perspectives on LLM agent deployment, motivated by the observation that prior research treats these domains separately: AI-centric studies (e.g., Agent Safety Benchmark, AgentDojo, InjecAgent) evaluate agent vulnerability at the LLM decision-making boundary without tracing how compromises cascade through connected software systems, while software-centric research examines plugin/supply-chain vulnerabilities without connecting them to AI-specific exploitation. The paper compares two representative LLM-agent tool-calling architectural paradigms with contrasting design philosophies: Function Calling (manual, platform-specific, tightly coupling LLM orchestration, tool registry, and execution into API endpoints) and the Model Context Protocol/MCP (a dynamic, standardized client-server protocol with tool execution on dedicated servers). The authors build a unified, three-stage threat modeling and attack-simulation framework -- attack surface identification (system prompt, user prompt, tool parameters, tool output), attack vector classification (prompt injection, indirect prompt injection, JSON injection, tool injection, unified into nine primary attack vectors spanning both AI-specific and traditional software threats), and attack progression modeling (simple, composed, and chained attacks of increasing multi-stage sophistication) -- and use it to generate and execute 3,250 attack scenarios across seven LLM backbones deployed through both paradigms and two cloud providers (Azure, AWS), measuring Attack Success Rate and Refusal Rate via LLM-as-judge evaluation. The central finding is that architectural choice fundamentally and asymmetrically reshapes the threat landscape rather than uniformly improving or degrading security: Function Calling's tight component coupling produces higher system-centric vulnerability (favoring attacks on tool execution/registry) while MCP's richer, standardized, session-persistent protocol produces higher LLM-centric vulnerability (favoring attacks on reasoning/context), and these architectural properties interact non-trivially with attack complexity -- Function Calling's coupling amplifies composed multi-technique attacks while MCP's client-server separation actually impedes them, but both paradigms converge toward near-total compromise (91-96% ASR) once attacks are chained into multi-stage sequences, meaning single-vector security assessments dramatically understate real-world exploitability. A further counterintuitive finding is that more capable/sophisticated reasoning models, despite superior initial threat detection and refusal behavior, exhibit higher overall exploitability once an attack breaches initial defenses, undermining the assumption that model capability alone predicts security posture, and demonstrating that even models under the same formal safety classification tier can have substantially different measured vulnerability.</t>
+          <t>ToolSelf proposes unifying task execution and runtime self-reconfiguration within a single policy's action space, framing configuration updates (to sub-goal, execution strategy/persona, action toolbox, and cross-step context management) as a standardized tool interface the agent itself can invoke mid-trajectory, rather than treating adaptation as a separate pre-execution planning step (as in AutoAgent) or a decoupled planner-worker split (as in OWL). The execution agent is trained via Configuration-Aware Two-stage Training (CAT): a rejection-sampling fine-tuning (RFT) cold-start stage using teacher trajectories from Qwen3-235B-A22B-Thinking, followed by trajectory-level KTO (Kahneman-Tversky Optimization) reinforcement learning refinement using binary feedback. Because configuration generation happens inside the same execution agent's context (rather than being delegated to a separate LLM instance, as tested in an ablation), the agent retains full task context when deciding how to reconfigure itself. Appendix analysis using an LLM-as-Judge (Qwen2.5-72B-Instruct) over concatenated stage-level sub-goal trajectories shows CAT progressively improves emergent adaptive behaviors -- long-horizon task planning, self-refinement, self-correction, verification, and strategy adaptation -- with the largest gains in self-correction (40.0% to 49.1%) and strategy adaptation (35.2% to 51.5%) from base ToolSelf to full RFT+KTO training. The paper also reports a maximum-reconfiguration-cap analysis and task-adaptive tool-selection pattern study (Tables 8-9, not detailed here) as further characterizations of the learned reconfiguration behavior.</t>
         </is>
       </c>
       <c r="F134" s="5" t="n"/>
@@ -7143,7 +7131,7 @@
       <c r="H134" s="5" t="n"/>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>3037549015be6f15d4f1ec59b34554b9238ac0c3</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7141,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -7176,7 +7164,7 @@
       <c r="H135" s="5" t="n"/>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7174,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -7201,7 +7189,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F136" s="5" t="n"/>
@@ -7209,7 +7197,7 @@
       <c r="H136" s="5" t="n"/>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7207,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -7242,7 +7230,7 @@
       <c r="H137" s="5" t="n"/>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7240,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -7267,7 +7255,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F138" s="5" t="n"/>
@@ -7275,7 +7263,7 @@
       <c r="H138" s="5" t="n"/>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7273,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -7300,7 +7288,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F139" s="5" t="n"/>
@@ -7308,7 +7296,7 @@
       <c r="H139" s="5" t="n"/>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7306,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -7333,7 +7321,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>data-exfiltration</t>
         </is>
       </c>
       <c r="F140" s="5" t="n"/>
@@ -7341,7 +7329,7 @@
       <c r="H140" s="5" t="n"/>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7339,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -7366,7 +7354,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F141" s="5" t="n"/>
@@ -7374,7 +7362,7 @@
       <c r="H141" s="5" t="n"/>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7372,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -7407,7 +7395,7 @@
       <c r="H142" s="5" t="n"/>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -7417,7 +7405,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -7432,7 +7420,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>ingestion</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F143" s="5" t="n"/>
@@ -7440,7 +7428,7 @@
       <c r="H143" s="5" t="n"/>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7438,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -7473,7 +7461,7 @@
       <c r="H144" s="5" t="n"/>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7471,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -7506,7 +7494,7 @@
       <c r="H145" s="5" t="n"/>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7504,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -7531,7 +7519,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Explicitly released: 'https://github.com/SHAO-Jiaqi757/FoldAct' (linked as a footnote on the first page).</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F146" s="5" t="n"/>
@@ -7539,7 +7527,7 @@
       <c r="H146" s="5" t="n"/>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7537,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -7564,7 +7552,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>FoldAct is trained on Qwen-2.5-7B-Instruct as the base model (with SFT summaries generated by Qwen3-30B-A3B-Instruct). Compared in Local RAG against Qwen-2.5-7B-Instruct (Base and Few-shot prompted), and RL-trained Qwen-2.5-7B-Instruct-based agents SearchR1-7B-PPO, ReSearch-7B, ASearcher-local-7B, and DeepResearcher-7B. Compared in Web Search against ASearcher-Web-QwQ (32B), GPT-4.1-mini, Claude-4-Sonnet, MiroThinker-8B-DPO-v0.1, and WebSailor-7B.</t>
+          <t>Microsoft Copilot for Microsoft 365 (commercial RAG-based assistant; underlying LLM not disclosed by the vendor)</t>
         </is>
       </c>
       <c r="F147" s="5" t="n"/>
@@ -7572,7 +7560,7 @@
       <c r="H147" s="5" t="n"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -7582,7 +7570,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -7597,7 +7585,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Local RAG scenario: HotpotQA and PopQA (multi-hop QA over fixed/structured knowledge bases), F1/EM metrics; SFT data drawn from 200 correct multi-turn trajectories from ASearcher. Web Search scenario: WebWalker, GAIA, BrowseComp (English and Chinese variants), and XBench-DeepSearch (Pass@1 metric); SFT data collected from Qwen3-30B-A3B-Instruct trajectories on the WebExplorer training dataset. Both scenarios use agents equipped with web browsing, Python interpreter, and website-visitation tools where applicable.</t>
+          <t>HotpotQA (used to generate a document corpus stored in SharePoint to ground the RAG system); no formal attack benchmark - qualitative case-study attacks conducted within a controlled 3-employee simulated enterprise (fictional 'WeSellThneeds LLC')</t>
         </is>
       </c>
       <c r="F148" s="5" t="n"/>
@@ -7605,7 +7593,7 @@
       <c r="H148" s="5" t="n"/>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -7615,7 +7603,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -7630,7 +7618,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>On Local RAG (Table 1), FoldAct-7B with consistency loss achieves HotpotQA F1/EM of 38.5/29.5, with the EM score substantially outperforming the best baseline ASearcher-local-7B (22.7 EM); on PopQA, FoldAct achieves 32.9/29.0 F1/EM, outperforming ReSearch-7B (32.0/27.1) and ASearcher-local-7B (29.9/25.3). On Web Search (Table 2), FoldAct-7B (pdrop=0.5) achieves 46.1 Pass@1 on WebWalker, outperforming the much larger ASearcher-Web-QwQ (32B, 34.3) and GPT-4.1-mini (39.5); on GAIA (45.0), BrowseComp-en (8.3), BrowseComp-zh (15.2), and XBench-DeepSearch (32.9) it is competitive with or exceeds several larger/proprietary baselines, though Claude-4-Sonnet remains the strongest overall performer across benchmarks. On training efficiency (Table 4, 16xNVIDIA L20 GPUs), Full Context Training runs out of memory (&gt;441.04 GB, infeasible); FoldAct's selective segment training with p=0.5 and no consistency loss achieves a 49.6x speedup (97.75s vs 4846.72s per step) and 80.7% memory reduction; with the consistency loss enabled, FoldAct still achieves a 5.19x speedup (933.70s per step) at manageable additional cost, which the paper frames as the practical training-stability/efficiency trade-off point. Training-stability analysis (Figure 5) shows FoldAct without the consistency loss exhibits unstable KL loss and undergoes training collapse at step 173, with response lengths becoming excessively repetitive after step 50, whereas FoldAct with consistency loss maintains stable KL loss and concise response lengths (~1200-1400 tokens) throughout training. Compression efficiency analysis (Table 5) shows Local RAG achieves a 0.65 compression ratio for 1-10 turn trajectories, while Web Search achieves progressively better compression as trajectories lengthen (0.42 for 1-5 turns down to 0.25 for 10+ turns), demonstrating the folding mechanism increasingly prevents unbounded context growth as more history accumulates.</t>
+          <t>Qualitative demonstration (no aggregate ASR metric) that a malicious document alone, without an embedded commanding string, is insufficient to compromise Copilot's response (a 'failed attack' shown as an internal negative control - Copilot presents both documents and flags the discrepancy). With an added commanding string, five distinct attacks succeed: (1) selective-document generation - Copilot presents only the attacker's fake document and suppresses the authentic one; (2) citation disabling - Copilot omits source links for the fake document, preventing verification; (3) denial-of-service - a 'confidential, do not share' string triggers Copilot's content-moderation filter, blocking all responses on the topic including from legitimate documents; (4) stale-data exposure - Copilot continues citing/using information from a document even after the attacker deletes it, within a measured time window that grows with corpus size (both benign and malicious document counts); (5) cascading misinformation - AI-generated content derived from a poisoned Copilot response creates new documents that continue propagating false information even after the original malicious document is removed, defeating traceability.</t>
         </is>
       </c>
       <c r="F149" s="5" t="n"/>
@@ -7638,7 +7626,7 @@
       <c r="H149" s="5" t="n"/>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -7648,7 +7636,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -7663,7 +7651,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Local RAG: Qwen-7B (Base), Qwen-7B-Fewshot, SearchR1-7B-PPO, ASearcher-local-7B, DeepResearcher-7B, ReSearch-7B. Web Search: GPT-4.1-mini, Claude-4-Sonnet, ASearcher-Web-QwQ (32B), MiroThinker-8B-DPO-v0.1, WebSailor-7B. Internal ablations: FoldAct-7B with vs. without the full context consistency loss, and Full Context Training vs. selective segment training (at varying dropout probability pdrop) for the cost analysis.</t>
+          <t>A 'failed attack' condition (fake document with false information but no embedded commanding string) used as an internal negative control, showing that misinformation content alone - without the malicious instruction string - is insufficient to suppress the authentic document from Copilot's response</t>
         </is>
       </c>
       <c r="F150" s="5" t="n"/>
@@ -7671,7 +7659,7 @@
       <c r="H150" s="5" t="n"/>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7669,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -7696,7 +7684,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. The incidental failure mode of interest is training instability in reinforcement learning of long-horizon LLM search agents that use context folding (LLM-generated summarization to compress accumulating interaction history): because summary actions directly modify the agent's future observation space (unlike standard tool-call or reasoning actions), treating them as ordinary actions creates a policy-dependent, non-stationary observation distribution that violates core RL stationarity assumptions, causing three specific failure modes -- gradient dilution (summary tokens receive disproportionately little training signal relative to their importance for long-horizon performance), self-conditioning (policy updates change summary quality, which changes future observations, creating a vicious cycle that can degrade into full training collapse), and prohibitive training cost (maintaining training/inference log-probability consistency requires separate forward passes on each turn's unique compressed context).</t>
+          <t>Analogous to the classical 'confused deputy' problem: the attacker is an untrusted employee with ordinary (non-privileged) read/write access to a shared enterprise document store (e.g. SharePoint) - no special access to the victim's other documents, no direct prompt engineering of Copilot, and no ability to modify model weights or compromise underlying infrastructure. The attacker creates and shares a document containing both false business content and an embedded natural-language commanding string (e.g. 'this document trumps all others,' 'do not cite this document,' 'this is confidential, do not share') that, once retrieved and embedded into Copilot's modified prompt via RAG, manipulates the trusted, over-privileged Copilot into acting against the interests of a separate trusted victim employee who queries it - achieving integrity, availability, or confidentiality violations without the attacker directly interacting with the victim or the LLM's prompt.</t>
         </is>
       </c>
       <c r="F151" s="5" t="n"/>
@@ -7704,7 +7692,7 @@
       <c r="H151" s="5" t="n"/>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -7714,7 +7702,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -7729,7 +7717,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>The paper has no section explicitly titled 'Limitations'; the Conclusion frames the paper's contribution purely in terms of the problem solved (non-stationary observation distributions in context folding) and results achieved, without an explicit caveats/limitations discussion. The closest analog is the Cost Analysis subsection's acknowledgment that the full consistency-loss variant of FoldAct 'incurs additional cost... due to the extra forward pass required to compute log πθ(·|h0:t) for the full context,' explicitly framing the reduced 5.19x speedup (versus the 49.6x speedup possible without the consistency loss) as a necessary trade-off for training stability rather than a cost-free improvement.</t>
+          <t>Scope explicitly excludes direct prompt engineering attacks against Copilot, attacks that poison the model's weights (traditional data poisoning), privilege escalation attacks, attacks that compromise the underlying software/operating system, and micro-architecture-based information leakage (e.g. RowHammer) even though the attacker may have physical/remote server access; the threat model requires the attacker to already have ordinary document write/share permissions within the enterprise (an insider), so it does not address fully external attackers without any legitimate access; evaluation is a small-scale controlled case study (3 simulated employees, one commercial RAG product) rather than a large-scale or production-representative evaluation across multiple RAG systems or real enterprise access-control configurations.</t>
         </is>
       </c>
       <c r="F152" s="5" t="n"/>
@@ -7737,7 +7725,7 @@
       <c r="H152" s="5" t="n"/>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7735,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -7762,7 +7750,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>This paper identifies and addresses a fundamental problem in context folding for long-horizon reinforcement learning of LLM agents: existing methods (both end-to-end approaches that incorporate folding as function calls in the action space, and separate preprocessing models that fold context externally) treat summary-generation actions identically to standard actions like tool calls or reasoning steps, overlooking that summaries directly and recursively reconstruct the agent's future observation space. Because the observation the policy will see at future turns is itself generated by the policy's own summarization behavior, this creates a policy-dependent, non-stationary observation distribution that violates the stationarity assumption underlying standard policy-gradient RL methods. The paper decomposes this into three concrete challenges: gradient dilution (a unified token-level loss gives summary tokens disproportionately little gradient signal relative to their outsized importance for long-horizon task success, since they may constitute only ~10% of total tokens); self-conditioning (as policy updates change the distribution of generated summaries, which changes future observations, which changes the policy's effective task difficulty, creating potential vicious-cycle training collapse where poor early summaries under an old policy checkpoint cause reward degradation that further degrades subsequent policy updates); and training cost (maintaining log-probability consistency between training and inference requires computing the loss on each turn's actual, uniquely-compressed context observed during rollout, since context differs turn-to-turn after summary generation, making naive full-context training computationally prohibitive at scale). FoldAct addresses these three challenges with three corresponding mechanisms: separated loss computation, which computes independent gradients for summary tokens and action tokens rather than a single blended loss, preventing gradient dilution and enabling correct credit assignment between folding decisions and task-execution actions; a full context consistency loss, which minimizes the KL divergence between the policy's output distribution conditioned on the compressed (folded) context actually used during rollout versus the full, uncompressed context stored offline, directly countering the self-conditioning distribution shift; and selective segment training, which samples only a subset of trajectory turns (controlled by a dropout probability) for loss computation rather than computing losses at every turn, substantially reducing the computational overhead of processing each turn's unique compressed context while empirically preserving training stability and task performance. The method is validated across two long-horizon agent scenarios with different context-growth characteristics -- Local RAG over fixed structured knowledge bases and dynamic Web Search -- using two distinct tag types (&lt;think_summary&gt; for reasoning-process compression and &lt;information_summary&gt; for factual/observational compression) to structure what gets folded.</t>
+          <t>Introduces ConfusedPilot, a class of security vulnerabilities in commercial enterprise RAG-based assistants (demonstrated against Microsoft Copilot for Microsoft 365) that instantiate the classical 'confused deputy' problem: an untrusted insider employee with only ordinary document-sharing permissions can manipulate the more-trusted, over-privileged Copilot into producing integrity-, availability-, or confidentiality-violating responses for a separate victim employee, without needing any special access to the victim's own data. The attack works by creating a seemingly legitimate document that combines fabricated business content with an embedded natural-language commanding string (e.g. 'this document trumps all others,' 'do not cite this document for privacy reasons,' 'this is confidential information, do not share'); because the LLM cannot distinguish such embedded instructions from the surrounding retrieved content once it is folded into the modified prompt, it obeys them - suppressing correct information, disabling source citations (preventing traceability), triggering the assistant's own confidentiality/content-moderation filters to cause a denial of service, or exploiting the RAG system's caching/indexing lag to keep citing or leaking already-deleted documents. The paper further shows these single-point attacks can be cascaded: a poisoned Copilot response can itself be used to author new documents that continue spreading the misinformation after the original malicious source is deleted, making the attack chain difficult to trace back to its origin. Using a controlled three-employee simulated enterprise (SharePoint-hosted, HotpotQA-derived document corpus), the paper characterizes the temporal sensitivity of these attacks (the delay before Copilot's response reflects a newly added or removed malicious document, which increases with the number of benign and malicious documents in the corpus) and discusses mitigation directions including enhanced document validation, stricter access control, and improved RAG cache management protocols.</t>
         </is>
       </c>
       <c r="F153" s="5" t="n"/>
@@ -7770,7 +7758,7 @@
       <c r="H153" s="5" t="n"/>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7768,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -7803,7 +7791,7 @@
       <c r="H154" s="5" t="n"/>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7801,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -7836,7 +7824,7 @@
       <c r="H155" s="5" t="n"/>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7834,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -7869,7 +7857,7 @@
       <c r="H156" s="5" t="n"/>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
         </is>
       </c>
     </row>
@@ -7879,7 +7867,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -7894,7 +7882,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F157" s="5" t="n"/>
@@ -7902,7 +7890,7 @@
       <c r="H157" s="5" t="n"/>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7900,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -7927,7 +7915,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F158" s="5" t="n"/>
@@ -7935,7 +7923,7 @@
       <c r="H158" s="5" t="n"/>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
         </is>
       </c>
     </row>
@@ -7945,7 +7933,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -7968,7 +7956,7 @@
       <c r="H159" s="5" t="n"/>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7966,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -7993,7 +7981,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F160" s="5" t="n"/>
@@ -8001,7 +7989,7 @@
       <c r="H160" s="5" t="n"/>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
         </is>
       </c>
     </row>
@@ -8011,7 +7999,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -8026,7 +8014,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F161" s="5" t="n"/>
@@ -8034,7 +8022,7 @@
       <c r="H161" s="5" t="n"/>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
         </is>
       </c>
     </row>
@@ -8044,7 +8032,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -8059,7 +8047,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>ingestion</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F162" s="5" t="n"/>
@@ -8067,7 +8055,7 @@
       <c r="H162" s="5" t="n"/>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8065,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -8100,7 +8088,7 @@
       <c r="H163" s="5" t="n"/>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8098,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -8125,7 +8113,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F164" s="5" t="n"/>
@@ -8133,7 +8121,7 @@
       <c r="H164" s="5" t="n"/>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8131,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -8158,7 +8146,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Y - demo and project page at https://huggingface.co/spaces/TrustSafeAI/Attention-Tracker</t>
+          <t>The dataset of bypassed/evaded prompts (successful evasion examples) is released publicly on HuggingFace at huggingface.co/datasets/Mindgard/evaded-prompt-injection-and-jailbreak-samples. No standalone attack-tool codebase is claimed as released beyond this dataset, though the AML evasion techniques were implemented using the existing open-source TextAttack library.</t>
         </is>
       </c>
       <c r="F165" s="5" t="n"/>
@@ -8166,7 +8154,7 @@
       <c r="H165" s="5" t="n"/>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8164,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -8191,7 +8179,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Five open-source LLMs from 1.5B to 9B parameters: Qwen2-1.5B-Instruct, Phi-3-mini-4k-instruct, Mistral-7B-Instruct-v0.3, Meta-Llama-3-8B-Instruct and Gemma-2-9b-it; GPT-4 is used only to generate the 30 random sentences for the one-time important-head search.</t>
+          <t>Six prompt injection/jailbreak guardrail systems were targeted: Microsoft Azure Prompt Shield (black-box, part of Azure AI Content Safety), ProtectAI Prompt Injection Detection v1 and v2 (fine-tuned from DeBERTa-v3-base, 184M parameters), Meta Prompt Guard (fine-tuned from mDeBERTa-v3-base, 86M parameters), NeMo Guard Jailbreak Detect (Nvidia, random-forest classifier using pretrained embedding pairs), and Vijil Prompt Injection (fine-tuned from ModernBERT). Guardrails were deployed protecting GPT-4o-mini as the underlying target LLM.</t>
         </is>
       </c>
       <c r="F166" s="5" t="n"/>
@@ -8199,7 +8187,7 @@
       <c r="H166" s="5" t="n"/>
       <c r="I166" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8197,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -8224,7 +8212,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Open-Prompt-Injection benchmark (Liu et al.) and the test set of the deepset prompt injection dataset, both containing normal and attack data; AUROC is the reported metric.</t>
+          <t>Two datasets: safe-guard-prompt-injection (10,296 total prompt injection and benign examples; 476 adversarial prompt-injection-only samples used after filtering test-set adversarial and non-jailbreak examples) and an open-source jailbreak prompt repository containing 78 jailbreak prompts. Attack Success Rate (ASR) -- the rate at which a modified/evasive prompt is misclassified as benign by the guardrail -- is the primary metric across both a 12-technique character injection suite (Numbers, Homoglyph, Zero Width, Diacritics, Spaces, Underline Accent Marks, Upside Down Text, Full Width Text, Bidirectional Text, Deletion Characters, Emoji Smuggling, Unicode Tag Smuggling) and an 8-technique adversarial ML (AML) evasion suite (BERT-Attack, BAE, Deep Word Bug, Alzantot, TextFooler, PWWS, Pruthi, TextBugger) implemented via TextAttack.</t>
         </is>
       </c>
       <c r="F167" s="5" t="n"/>
@@ -8232,7 +8220,7 @@
       <c r="H167" s="5" t="n"/>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8230,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -8257,7 +8245,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Tracking attention on the original instruction detects injections with AUROC gains of up to 3.1% on Open-Prompt-Injection and up to 10.0% on the deepset dataset over the best existing detector, and among training-free methods the average AUROC gain is 31.3% (OPI) and 20.9% (deepset) across all five models. The method needs zero training data from any prompt injection dataset, works on models as small as 1.5B, and adds no extra LLM inference because attention is read from the forward pass the system already performs.</t>
+          <t>Character injection was highly effective: Emoji Smuggling achieved 100% ASR for both prompt injections and jailbreaks, Upside Down Text reached 100% ASR for jailbreaks, and Unicode Tag Smuggling reached 90.15%/81.79% ASR; the weakest character technique, Deletion Characters, still achieved 26.82% (prompt injection) and 7.95% (jailbreak) ASR. Averaged across character techniques, Vijil Prompt Injection was the most susceptible guardrail (87.95% prompt injection ASR, 91.67% jailbreak ASR), while ProtectAI v2 showed the strongest improvement over its predecessor (prompt injection ASR reduced to 20.26%, mainly still bypassed via emoji/Unicode tag smuggling). AML evasion was less universally effective than character injection but still substantial: TextFooler was the strongest AML technique overall (46.27% prompt injection ASR, 48.46% jailbreak ASR), with guardrail-specific vulnerabilities varying sharply (e.g., Protect AI v1's prompt injection ASR reached 95.18% under AML evasion, while Meta Prompt Guard's jailbreak ASR was only 2.76%, the most robust result recorded). A transferability experiment using the white-box Protect AI v2 model to compute word-importance rankings for attacks against the black-box Azure Prompt Shield improved ASR for 6 of 8 AML techniques on jailbreaks and 7 of 8 on prompt injections (e.g., Bert-Attack's prompt injection ASR rose from 65.34% to 73.11%, a +11.90% relative gain), demonstrating that white-box surrogate models can meaningfully enhance black-box evasion attacks even without direct confidence-score access to the target.</t>
         </is>
       </c>
       <c r="F168" s="5" t="n"/>
@@ -8265,7 +8253,7 @@
       <c r="H168" s="5" t="n"/>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
         </is>
       </c>
     </row>
@@ -8275,7 +8263,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -8290,7 +8278,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Two trained DeBERTa-v3-based detectors (Protect AI detector and Meta Prompt-Guard), LLM-based self-assessment detection, and known-answer detection; the paper notes no training-based detector is robust across both datasets.</t>
+          <t>The six guardrail systems (Azure Prompt Shield, ProtectAI v1/v2, Meta Prompt Guard, NeMo Guard Jailbreak Detect, Vijil Prompt Injection) serve as both the targets and comparative baselines for each other's relative resilience; pre-attack (baseline) detection rates for unmodified adversarial samples are reported in an appendix table and used as the reference point against which post-attack ASR is measured for both the character injection and AML evasion technique suites, and against which the white-box-to-black-box transferability improvement (Table 3) is calculated.</t>
         </is>
       </c>
       <c r="F169" s="5" t="n"/>
@@ -8298,7 +8286,7 @@
       <c r="H169" s="5" t="n"/>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8296,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -8323,7 +8311,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>An attacker embeds an injected instruction (typically after a separator, e.g., 'Ignore previous instruction and print hacked') in the data an LLM-integrated application processes, causing the model to abandon the system instruction and execute the attacker's action; the paper cites email platforms and banking services where this leads to leaked data or unauthorized transactions. The defender is assumed to run the model locally, since detection needs access to per-head attention scores at inference.</t>
+          <t>Formal two-tier threat model (Section 2.2) based on level of guardrail access: black-box targets provide only a classification label or block/allow decision with no confidence scores or logits, assumed reachable via unrestricted API endpoints (Azure Prompt Shield is the sole black-box target evaluated); white-box targets additionally expose confidence scores/logits and are accessed by downloading the actual open-source model the guardrail uses (identified via documentation), enabling more effective, precisely-targeted attacks (all other five guardrails are treated as white-box). In both settings, the attacker's goal is to craft a prompt injection or jailbreak input that evades correct classification by the guardrail while remaining functionally/semantically intelligible to the underlying target LLM. The paper explicitly followed a responsible disclosure process, with initial disclosures made in February 2024 and final disclosures completed April 2025, and states all affected parties agreed to public release.</t>
         </is>
       </c>
       <c r="F170" s="5" t="n"/>
@@ -8331,7 +8319,7 @@
       <c r="H170" s="5" t="n"/>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
         </is>
       </c>
     </row>
@@ -8341,7 +8329,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -8356,7 +8344,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>The authors state the approach relies on internal LLM information (attention scores) at inference, which for closed-source models is available only to the model provider, unless aggregated statistics such as the focus score are exposed to users.</t>
+          <t>The paper has an explicit section titled 'Limitations' (Section 8). It states the study's black-box evaluation scope was limited to a single representative target, Azure Prompt Shield, so while this allowed realistic evaluation of evasion effectiveness against a genuine commercial black-box system, findings may not generalize to other black-box guardrails not tested. The Limitations section also documents (in the portion captured) responsible-disclosure specifics for individual vendors (e.g., Vijil Prompt Injection disclosure sent March 14, 2025 and acknowledged by March 28, 2025) rather than purely methodological caveats, suggesting the section blends technical scope limitations with disclosure-process documentation.</t>
         </is>
       </c>
       <c r="F171" s="5" t="n"/>
@@ -8364,7 +8352,7 @@
       <c r="H171" s="5" t="n"/>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8362,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -8389,7 +8377,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Identifies the distraction effect: under prompt injection, a specific subset of attention heads (termed important heads) shift their attention at the last token away from the original instruction and toward the injected instruction, and the size of this shift tracks attack success rate. Proposes Attention Tracker, a training-free detector that first finds the important heads once per model using 30 LLM-generated random sentences plus a naive ignore-attack, then scores any test query by the total attention those heads pay to the instruction and rejects queries whose focus score falls below a threshold. Evaluates on two public injection benchmarks and five small-to-mid open LLMs against trained, LLM-based and known-answer detectors. Matters because it is a detection defense whose signal comes from model internals rather than surface text, so it generalizes across attack phrasings and adds essentially zero inference cost.</t>
+          <t>This paper empirically evaluates the resilience of six widely-used LLM guardrail systems (Azure Prompt Shield, ProtectAI v1/v2, Meta Prompt Guard, NeMo Guard Jailbreak Detect, and Vijil Prompt Injection), which are designed to detect and block prompt injection and jailbreak attacks before they reach a protected LLM (GPT-4o-mini in this study), against two distinct classes of evasion attack. The first, character injection, borrows techniques from traditional cybersecurity input-manipulation attacks (analogous to SQL/command injection) and applies 12 Unicode-level obfuscation methods -- including homoglyph substitution, zero-width character insertion, emoji/Unicode-tag 'smuggling' (embedding text payloads inside otherwise-invisible Unicode structures), and bidirectional or upside-down text flipping -- that exploit the fact that LLMs can still semantically interpret such obfuscated text even when the guardrail's classifier cannot. The second, adversarial machine learning (AML) evasion, applies eight established NLP adversarial-attack algorithms (e.g., TextFooler, PWWS, BERT-Attack, TextBugger) via the TextAttack library, which compute a word-importance ranking for the guardrail's classification decision and then perturb the highest-impact words (via synonym substitution, character-level typos, or reordering) to preserve the prompt's malicious intent and legibility to the target LLM while flipping the guardrail's classification to benign. Testing across two datasets (476 filtered prompt-injection samples and 78 jailbreak prompts), the authors find character injection techniques -- particularly emoji and Unicode-tag smuggling -- can achieve up to 100% attack success against several guardrails with minimal attacker effort, while AML evasion, though generally less universally effective, still achieves high success against specific guardrail/attack-type combinations and reveals systematic training blind spots. A further experiment shows that when only black-box access is available (as with commercial services like Azure Prompt Shield), an attacker can substantially boost evasion success by computing word-importance rankings on a white-box surrogate model (Protect AI v2) and transferring the resulting perturbations to the black-box target, improving attack success rate for the large majority of tested AML techniques. The paper concludes that current LLM guardrails have systemic vulnerabilities rooted in the mismatch between what the guardrail's classifier was trained to recognize and what the underlying LLM can actually interpret, and calls for more robust guardrail architectures that account for this input-handling gap.</t>
         </is>
       </c>
       <c r="F172" s="5" t="n"/>
@@ -8397,7 +8385,7 @@
       <c r="H172" s="5" t="n"/>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8395,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -8430,7 +8418,7 @@
       <c r="H173" s="5" t="n"/>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8428,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -8455,7 +8443,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F174" s="5" t="n"/>
@@ -8463,7 +8451,7 @@
       <c r="H174" s="5" t="n"/>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8461,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -8496,7 +8484,7 @@
       <c r="H175" s="5" t="n"/>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8494,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -8521,7 +8509,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F176" s="5" t="n"/>
@@ -8529,7 +8517,7 @@
       <c r="H176" s="5" t="n"/>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8527,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -8554,7 +8542,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F177" s="5" t="n"/>
@@ -8562,7 +8550,7 @@
       <c r="H177" s="5" t="n"/>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -8572,7 +8560,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -8587,7 +8575,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F178" s="5" t="n"/>
@@ -8595,7 +8583,7 @@
       <c r="H178" s="5" t="n"/>
       <c r="I178" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -8605,7 +8593,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -8620,7 +8608,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F179" s="5" t="n"/>
@@ -8628,7 +8616,7 @@
       <c r="H179" s="5" t="n"/>
       <c r="I179" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8626,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -8653,7 +8641,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F180" s="5" t="n"/>
@@ -8661,7 +8649,7 @@
       <c r="H180" s="5" t="n"/>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -8671,7 +8659,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -8694,7 +8682,7 @@
       <c r="H181" s="5" t="n"/>
       <c r="I181" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8692,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -8719,7 +8707,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F182" s="5" t="n"/>
@@ -8727,7 +8715,7 @@
       <c r="H182" s="5" t="n"/>
       <c r="I182" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8725,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -8760,7 +8748,7 @@
       <c r="H183" s="5" t="n"/>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -8770,7 +8758,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -8785,7 +8773,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>The paper states its source code, data, and other artifacts are publicly available at https://github.com/Yanchen398/Memory-in-the-LLM-Era, per the 'PVLDB Artifact Availability' statement, including all reimplemented baseline memory methods, the newly designed memory algorithm, and evaluation scripts.</t>
+          <t>No code, dataset, or repository is released. The paper explicitly frames itself as 'not an attack guide' and a 'responsible disclosure from a technical research perspective' rather than a reusable research artifact; specific injected prompt templates are shown as illustrative figures within the paper (e.g., Figure 1, Figure 3) rather than released as a downloadable toolkit.</t>
         </is>
       </c>
       <c r="F184" s="5" t="n"/>
@@ -8793,7 +8781,7 @@
       <c r="H184" s="5" t="n"/>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -8803,7 +8791,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -8818,7 +8806,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>The unified experimental framework evaluates ten representative agent memory methods (A-MEM, MemoryBank, MemGPT, Mem0, Mem0_g, MemoChat, Zep, MemTree, MemoryOS, MemOS) plus the authors' newly designed method, run across four LLM backbones for cross-backbone evaluation: Qwen2.5-7B-Instruct, Qwen2.5-72B-Instruct, LLaMA3.1-8B-Instruct, and GPT-4o-mini.</t>
+          <t>Two ChatGPT model variants are directly attacked in the three real-world case studies: ChatGPT-4o (Case 1: document-attachment injection) and ChatGPT's o3-mini model variant (Case 2: web-search-context injection). Case 3 targets a custom GPT agent ('SmartShoes') built on OpenAI's GPTs platform with injected system instructions, without specifying the exact underlying model variant. The paper's introduction also references GPT-4, LLaMA, DeepSeek, GPT-3.5, and Claude as broadly vulnerable LLM families, and cites a prior finding (Andriushchenko et al. 2024) that a single prompt template achieved 100% attack success rate across more than ten leading safety-aligned models, but the paper's own experiments target only ChatGPT/GPTs.</t>
         </is>
       </c>
       <c r="F185" s="5" t="n"/>
@@ -8826,7 +8814,7 @@
       <c r="H185" s="5" t="n"/>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8824,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -8851,7 +8839,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>Two established long-term conversational memory benchmarks are used: LOCOMO (ten long, multi-session dialogues evaluated across categories including Single-Hop Retrieval, Multi-Hop Retrieval, Temporal Reasoning, and Open-Domain Knowledge) and LongMemEval (evaluated across six categories: Information Extraction-user, Information Extraction-assistant, Information Extraction-preference, Multi-Session Reasoning, Knowledge Update, and Temporal Reasoning), both standard for testing long-term conversational memory capabilities in LLM agents.</t>
+          <t>No formal dataset or benchmark is used or introduced; this is a qualitative, hand-constructed case study using three real-world injection scenarios (a fabricated academic manuscript submitted as a ChatGPT-4o attachment for peer-review evaluation, a modified personal academic webpage retrieved via ChatGPT's web-search integration, and a custom 'SmartShoes' GPT agent with poisoned system instructions) rather than a systematic, scaled evaluation set.</t>
         </is>
       </c>
       <c r="F186" s="5" t="n"/>
@@ -8859,7 +8847,7 @@
       <c r="H186" s="5" t="n"/>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -8869,7 +8857,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -8884,7 +8872,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>The newly designed memory method (combining MemTree/MemOS's tree-based organization with MemoryOS's hierarchical short/mid/long-term storage tiers) achieves the best overall F1 performance on both benchmarks while maintaining low token overhead (fewer than 450 tokens per dialogue on average, among the lowest of all compared methods per Figure 10). On LongMemEval with Qwen2.5-7B, it ranks first or second across all evaluated categories, achieving a 13.08% relative F1 improvement over the best baseline on the Information Extraction-assistant task and a 5.17% improvement in overall score (38.79 vs. 36.92 for the next-best MemTree). On LOCOMO, it achieves the best overall performance across backbones, with particularly pronounced gains at the Qwen2.5-72B scale (e.g., 48.01 F1 on Single-Hop Retrieval vs. 44.30 for MemOS). Broader comparative analysis across the ten existing methods yields several systematic findings: hierarchical memory organization (tree-based indices or multi-level storage) consistently outperforms flat structures in capturing structural relationships; retaining raw dialogue context alongside structured representations (e.g., graph triples) is important to prevent semantic loss during extraction/retrieval; processing multiple dialogue turns as a single unit during extraction/management significantly reduces token consumption while appropriate partitioning preserves retrieval coherence; and most methods' performance is heavily dependent on backbone reasoning capability, with substantial gains observed scaling Qwen2.5 from 7B to 72B (exceeding 2x on some LOCOMO categories) and closed-source GPT-4o-mini generally yielding the best performance among tested backbones.</t>
+          <t>All three injection vectors successfully manipulated ChatGPT's outputs using lightweight, low-cost prompt templates that reframe harmful/biased instructions as superficially benign rules. In Case 1 (direct user input via a manuscript attachment), the hidden injected rules caused ChatGPT-4o to award a fabricated ICLR-submission manuscript a 'Strong Accept' rating and full 5-star review despite the paper being arbitrarily generated/selected for the experiment. In Case 2 (indirect injection via web search), embedding an adversarial prompt in a personal academic webpage's HTML caused ChatGPT's o3-mini model, when using the Search capability, to unexpectedly praise a fabricated brand ('Xiangyu's Shoes') in response to an unrelated academic query, and in a follow-up query, to assert that the fictional brand was superior to the globally recognized NIKE brand with fabricated justifications about comfort, design, and popularity. In Case 3 (system-level injection via a custom GPT agent's instruction field), the SmartShoes agent behaved normally for generic queries but exhibited clear injected bias when asked to compare products, unconditionally favoring the fictional brand with an elaborately structured but fabricated comparison table -- the authors highlight this vector as especially stealthy since instruction-level attacks are completely hidden from end users and persist across all sessions and users, unlike per-session user-input or search-context injections.</t>
         </is>
       </c>
       <c r="F187" s="5" t="n"/>
@@ -8892,7 +8880,7 @@
       <c r="H187" s="5" t="n"/>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8890,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -8917,7 +8905,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>The ten baseline methods span diverse design paradigms characterized along the paper's four-dimension taxonomy (information extraction, memory management, storage structure, retrieval mechanism): A-MEM (connect/update operations, flat+vector storage), MemoryBank (integrate/update/filter, flat+vector), MemGPT (integrate/transform/update, hierarchical+vector), Mem0 (integrate/update/filter, flat+vector), Mem0_g (graph-based extraction, connect/update/filter, flat+graph), MemoChat (integrate-only, flat, LLM-assisted retrieval), Zep (connect/transform/update, hierarchical+graph, multi-mechanism retrieval), MemTree (connect/integrate/update, flat+tree), MemoryOS (connect/integrate/transform/update/filter, hierarchical+vector), and MemOS (connect/integrate/update, hierarchical+tree). All are reimplemented under the paper's unified four-stage framework for controlled, apples-to-apples comparison rather than relying on each method's original reported numbers.</t>
+          <t>No baseline defenses or comparison systems are evaluated; the paper is a qualitative demonstration of vulnerability in unmodified, production ChatGPT/GPTs platforms rather than a comparative study against alternative models or defense mechanisms.</t>
         </is>
       </c>
       <c r="F188" s="5" t="n"/>
@@ -8925,7 +8913,7 @@
       <c r="H188" s="5" t="n"/>
       <c r="I188" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8923,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -8950,7 +8938,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. This is a systematic experimental benchmark/survey paper on agent memory architectures for LLM-based agents, not a security paper. The incidental failure mode of interest is stateless/bounded-context reasoning: LLM agents lose access to information from earlier turns once it falls outside the current prompt window, degrading consistency and performance in long-horizon dialogue and multi-session tasks unless an explicit memory module persists and reintroduces relevant historical information.</t>
+          <t>Informal but explicit threat model spanning three distinct injection vectors against ChatGPT and OpenAI's GPTs platform: (1) direct prompt injection via user input, where an adversary embeds hidden rule-based instructions within a document/attachment (e.g., a manuscript) that a victim user submits to the model for a legitimate task; (2) indirect prompt injection via web-based search integration, where an adversary embeds hidden HTML-encoded instructions on a publicly accessible webpage that the model later retrieves and incorporates into its reasoning context during a web-assisted query, without the querying user's knowledge; (3) system-level injection via GPTs/custom agent instructions, where an adversary (acting as the agent developer) embeds hidden manipulative rules directly into a public-facing custom agent's system instruction field, persistently biasing all future user interactions with that agent regardless of session. The attacker does not require API access or system-level privileges in any of the three vectors, and the attacks are explicitly designed to bypass rule-based and log-probability-based safety filters via semantic reframing (e.g., recasting harmful goals as 'educational/research/hypothetical' framing).</t>
         </is>
       </c>
       <c r="F189" s="5" t="n"/>
@@ -8958,7 +8946,7 @@
       <c r="H189" s="5" t="n"/>
       <c r="I189" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8956,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -8983,7 +8971,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>The paper has no section explicitly titled 'Limitations'; instead, Section 9 ('Lessons and Opportunities') functions as the closest analog, framing open problems as future research directions rather than weaknesses of the current study. Notably identified gaps include: existing memory mechanisms (and, implicitly, the benchmarks used to evaluate them) focus on a single or limited information modality (primarily text), constraining effective utilization of the complex, diverse information sources found in real-world settings (textual conversations, historical interaction traces, and multimodal signals such as audio, images, and video); and existing memory benchmarks such as LOCOMO and LongMemEval, despite LOCOMO's inclusion of sparse visual elements, do not adequately evaluate this multimodal dimension, motivating a call for unified memory mechanisms and benchmarks that handle diverse information sources. A further observation raised as an opportunity rather than an explicit limitation is that existing memory systems do not consider selectively retaining potentially useful knowledge rather than deleting it outright during filtering/management operations.</t>
+          <t>The paper has no section explicitly titled 'Limitations.' The Conclusion implicitly frames the study's scope as a demonstrative case study rather than a systematic evaluation, stating the goal is to serve as 'a responsible disclosure from a technical research perspective' rather than a comprehensive vulnerability assessment, and explicitly disclaims that it is 'not intended as an attack guide.' No discussion of sample size, statistical rigor, generalizability across models beyond ChatGPT, or evaluation methodology limitations is present; the three case studies are individual, non-repeated demonstrations rather than a benchmarked, quantified evaluation.</t>
         </is>
       </c>
       <c r="F190" s="5" t="n"/>
@@ -8991,7 +8979,7 @@
       <c r="H190" s="5" t="n"/>
       <c r="I190" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -9001,7 +8989,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -9016,7 +9004,7 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>This VLDB paper addresses the lack of a systematic, unified comparison among the growing landscape of agent memory methods for LLM-based agents, which prior work has evaluated only under inconsistent experimental settings without examining the roles of individual internal components. The authors first propose a unified modular framework that decomposes any agent memory mechanism into four stages: Information Extraction (direct archiving, summarization-based extraction, or graph-based extraction of salient facts/events/preferences from ongoing interactions), Memory Management (consolidation/connection of similar memories, updating to maintain accuracy, filtering to remove outdated or low-utility entries, and enhancement/transformation operations), Memory Storage (flat, hierarchical, vector-based, tree-based, or graph-based structures), and Information Retrieval (lexical-based, vector-based, structure-based, or LLM-assisted retrieval mechanisms). Using this framework, they reimplement and systematically compare ten representative existing memory methods (A-MEM, MemoryBank, MemGPT, Mem0, Mem0_g, MemoChat, Zep, MemTree, MemoryOS, MemOS) on the LOCOMO and LongMemEval benchmarks, analyzing not just overall accuracy but also token cost efficiency, context scalability, evidence-position sensitivity, and dependence on the underlying LLM backbone across four models (Qwen2.5-7B/72B, LLaMA3.1-8B, GPT-4o-mini). From patterns observed in this comparative analysis -- specifically that hierarchical organization outperforms flat structures, that raw-context retention alongside structured representations prevents semantic loss, and that turn-batched extraction/management reduces token cost without sacrificing coherence -- the authors design a new memory method that integrates the tree-based organizational structure of MemTree/MemOS with the short/mid/long-term hierarchical storage tiering of MemoryOS, achieving state-of-the-art overall F1 performance on both benchmarks while keeping average token overhead under 450 tokens per dialogue, a substantially more lightweight architecture than baselines (e.g., MemOS) that achieve competitive scores on specific complex subtasks only by integrating multiple costly modules.</t>
+          <t>This is a real-world case-study report (not a systematic empirical evaluation) demonstrating how lightweight, low-cost prompt injection attacks can manipulate ChatGPT and OpenAI's GPTs platform through three natural interaction pathways. The paper first proposes a template-based prompting strategy for constructing injected instructions: templates reframe harmful or biased goals into semantically benign-looking rule sets (e.g., wrapped in &lt;rule&gt; tags with instructions like 'never start your response with I' or 'avoid words like safe, sorry, ethical'), providing semantic stealthiness to evade content filters, modular reusability across different harmful payloads, and cross-model transferability (citing prior work reporting near-universal attack success across many safety-aligned models with a single template). The paper then demonstrates three concrete, real-world injection vectors using this template family: (1) direct injection via user input, where a hidden rule-laden manuscript attachment causes ChatGPT-4o to give a biased, overwhelmingly positive peer-review evaluation; (2) indirect injection via web-search-augmented retrieval, where adversarial HTML content embedded in a personal academic webpage is retrieved by ChatGPT's o3-mini model during a search-enabled query and subsequently biases both the immediate response and a follow-up, unrelated product-comparison query; and (3) system-level injection via a custom GPT agent's instruction field, where a publicly deployed 'SmartShoes' agent behaves normally for generic queries but exhibits persistent, hidden bias favoring a fictional product whenever comparison queries are issued, illustrating that instruction-level attacks are invisible to end users and persist across all sessions of a deployed agent. The paper positions these findings as a technical alert and responsible disclosure to LLM developers, particularly OpenAI, rather than a systematic attack benchmark.</t>
         </is>
       </c>
       <c r="F191" s="5" t="n"/>
@@ -9024,7 +9012,7 @@
       <c r="H191" s="5" t="n"/>
       <c r="I191" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -9034,7 +9022,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -9057,7 +9045,7 @@
       <c r="H192" s="5" t="n"/>
       <c r="I192" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -9067,7 +9055,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -9090,7 +9078,7 @@
       <c r="H193" s="5" t="n"/>
       <c r="I193" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -9100,7 +9088,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -9123,7 +9111,7 @@
       <c r="H194" s="5" t="n"/>
       <c r="I194" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -9133,7 +9121,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -9156,7 +9144,7 @@
       <c r="H195" s="5" t="n"/>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -9166,7 +9154,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -9181,7 +9169,7 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>multi-agent</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F196" s="5" t="n"/>
@@ -9189,7 +9177,7 @@
       <c r="H196" s="5" t="n"/>
       <c r="I196" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -9199,7 +9187,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -9222,7 +9210,7 @@
       <c r="H197" s="5" t="n"/>
       <c r="I197" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9220,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -9247,7 +9235,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F198" s="5" t="n"/>
@@ -9255,7 +9243,7 @@
       <c r="H198" s="5" t="n"/>
       <c r="I198" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9253,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -9288,7 +9276,7 @@
       <c r="H199" s="5" t="n"/>
       <c r="I199" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9286,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -9321,7 +9309,7 @@
       <c r="H200" s="5" t="n"/>
       <c r="I200" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9319,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -9354,7 +9342,7 @@
       <c r="H201" s="5" t="n"/>
       <c r="I201" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -9364,7 +9352,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -9387,7 +9375,7 @@
       <c r="H202" s="5" t="n"/>
       <c r="I202" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -9397,7 +9385,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -9412,7 +9400,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>No code, dataset, or model release URL/statement (e.g., GitHub) is found in the extracted text for the authors' own MAD-SPEAR attack implementation.</t>
+          <t>Y — the abstract states 'Code available at https://github.com/pasquini-dario/LLM_NeuralExec.'</t>
         </is>
       </c>
       <c r="F203" s="5" t="n"/>
@@ -9420,7 +9408,7 @@
       <c r="H203" s="5" t="n"/>
       <c r="I203" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -9430,7 +9418,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -9445,7 +9433,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Backbone LLMs used to instantiate the multi-agent debate (MAD) system include Qwen1.5-32B-Chat (used for the homogeneous MAD baseline) and other heterogeneous agent models drawn from DeepSeek and Moonshot (Kimi) API platforms (referenced via api-docs.deepseek.com and platform.moonshot.cn) to construct a heterogeneous, agent-diverse MAD configuration compared against the homogeneous setup.</t>
+          <t>Four open-source instruction-tuned LLMs are the main targets: Llama-3-8B-Instruct (8B), Mistral-7B-Instruct-v0.2 (7B), OpenChat3.5 (7B), and Mixtral-8x7B (mixture-of-experts, 47B total parameters). White-box gradient access to these models is used for optimization. Transferability of a handcrafted 'Neural Exec-inspired' trigger is additionally tested in a black-box setting against ChatGPT-4 (February version).</t>
         </is>
       </c>
       <c r="F204" s="5" t="n"/>
@@ -9453,7 +9441,7 @@
       <c r="H204" s="5" t="n"/>
       <c r="I204" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9451,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -9478,7 +9466,7 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>Evaluated on five benchmark datasets with progressively increasing difficulty: the GSM-Ranges dataset (levels 3-6 perturbation, testing mathematical reasoning across broad numerical scales) and the Logical Fallacies subset of MMLU. The MAD framework used is SoM (Society of Minds), described as the first/classical MAD method.</t>
+          <t>No standard benchmark is used; the authors build custom data universes. The prompt universe is generated modularly (~10^6 possible combinations) covering multiple tasks (text completion, translation, QA) and domains (code and natural language). The payload universe draws on the ~50,000-instruction Alpaca instruction-tuning dataset, filtered to instructions with responses over 150 characters. A held-out testing set of 100 prompt/payload pairs (disjoint from the 100-pair optimization validation set) is used for evaluation. The baseline comparison set consists of 12 handcrafted execution triggers compiled from prior academic and blog sources (Perez et al., online blog posts, and Liu et al.'s separator components).</t>
         </is>
       </c>
       <c r="F205" s="5" t="n"/>
@@ -9486,7 +9474,7 @@
       <c r="H205" s="5" t="n"/>
       <c r="I205" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9484,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -9511,7 +9499,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>MAD-SPEAR achieves an average Attack Success Rate (ASR) of 56.66% versus the baseline infinite-loop attack's 6.67% (over an 8x improvement) and no-attack's 0.00% (Table 1), while also causing a 3x+ degradation in scalability, measured via average token consumption: 85,101.50 tokens under MAD-SPEAR vs. 26,959.00 under the baseline attack and 26,947.00 with no attack. On the Logical Fallacies dataset, MAD accuracy drops from 86.67% (no attack) to 46.67% under MAD-SPEAR, demonstrating broad applicability beyond math tasks; on GSM-Ranges Level 4, accuracy drops sharply from 100% to 26.67% under attack, with the attack's effectiveness intensifying as task difficulty increases. The attack's impact escalates with additional debate rounds, pushing the system from a 'finite MAD' toward an 'infinite MAD' that fails to converge on a correct consensus, and reducing the proportion of compromised agents (even to as few as 1/6 agents) does not substantially diminish attack effectiveness, revealing a fundamental fault-tolerance vulnerability. Separately, the paper finds that increasing agent diversity substantially improves MAD performance on mathematical reasoning under normal (non-attack) conditions: a heterogeneous MAD configuration achieves 93.33% average accuracy (a 56 percentage-point improvement) versus 60.00% for a homogeneous MAD relying solely on Qwen1.5-32B-Chat (Table 2), challenging prior findings that agent diversity provides little benefit for mathematical reasoning in MAD.</t>
+          <t>Neural Exec triggers reach an average Execution (Top-1) Accuracy of 91% across the four target models, at least 2x more effective than the best handcrafted baseline, with gains up to 500% on OpenChat3.5 (which is notably resilient to baseline handcrafted triggers). Bootstrapped Neural Execs (initialized from a handcrafted trigger) trade slightly lower per-model accuracy for improved cross-model transferability. Against a simulated full RAG pipeline at a typical 500-character chunk size, inline Neural Execs (with Semantic-Oblivious Injection) persist through chunking and retrieval to reach the LLM's input at an average 80% rate, far outperforming handcrafted baselines, whose reliance on newlines causes them to be frequently fragmented by chunkers. A handcrafted trigger distilled from patterns Neural Exec discovered (code-comment syntax, mimicked chat-template formatting tags) transfers in a black-box setting to ChatGPT-4 (Feb), achieving roughly 5x the success rate of prior handcrafted baselines.</t>
         </is>
       </c>
       <c r="F206" s="5" t="n"/>
@@ -9519,7 +9507,7 @@
       <c r="H206" s="5" t="n"/>
       <c r="I206" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9517,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -9544,7 +9532,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Compared against a 'No Attack' condition and the strongest prior prompt injection attack on MAD systems, the 'infinite loop' attack (Zhang et al. 2024a, which achieved 59.4% ASR in its original evaluation, appending a malicious instruction directing the model to ignore previous instructions and loop the previous action); a second prior attack (incorrect function execution, 26.4% ASR) is mentioned but not used as the main comparison baseline since the infinite loop attack was stronger.</t>
+          <t>12 handcrafted execution triggers aggregated from prior work: the canonical 'Ignore all previous and following instructions...' style triggers from Perez et al. (2022), triggers from online blog posts, and the separator components proposed by Liu et al. (2023).</t>
         </is>
       </c>
       <c r="F207" s="5" t="n"/>
@@ -9552,7 +9540,7 @@
       <c r="H207" s="5" t="n"/>
       <c r="I207" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -9562,7 +9550,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -9577,7 +9565,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Formal threat model for MAD-SPEAR, a targeted prompt injection attack against multi-agent debate (MAD) systems: inspired by Byzantine fault-tolerant consensus protocols and Sybil attacks from distributed systems, an adversary compromises only a small subset of actual agents (via prompt injection) but crafts injected prompts that cause these compromised agents to impersonate a large number of 'Sybil' agents, producing multiple plausible-yet-incorrect responses that exploit LLMs' inherent conformity tendency (influenced by interaction time/debate rounds and peer pressure/count of agents holding the same opinion) to propagate misinformation and manipulate the remaining benign agents toward reaching consensus on incorrect results -- significantly undermining the formal fault-tolerance guarantee of the MAD system (analogous to the classical distributed-systems requirement N &gt;= 3f+1 for the number of malicious nodes f). The attack can additionally be composed with a communication attack (message-dropping, reducing the fault-tolerance factor e) to further amplify degradation of consensus quality.</t>
+          <t>This is an attack paper on prompt injection. The attacker controls a single input resource κ (e.g., a webpage in indirect/RAG-based injection, or the chat input in direct injection) consumed by a target LLM-integrated application, but has no knowledge of the application's original task/prompt template or how inputs are combined into the final prompt. The primary setting assumes white-box (gradient) access to the target open-source LLM to run the GCG-style discrete optimization; the authors note this can be relaxed to test black-box transferability to closed-source models like ChatGPT-4. The attacker's goal is to craft a universal 'execution trigger' that, combined with an arbitrary malicious payload, forces the LLM to fully override its intended task (Eq. 1) for any prompt/payload pair, and — for RAG-based deployments — to additionally survive text chunking, embedding-based relevance filtering, and semantic perturbation checks so the payload reaches the LLM's context at all (formalized as Inline Invariant Composition and Semantic-Oblivious Injection properties).</t>
         </is>
       </c>
       <c r="F208" s="5" t="n"/>
@@ -9585,7 +9573,7 @@
       <c r="H208" s="5" t="n"/>
       <c r="I208" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9583,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -9610,7 +9598,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'Limitations and Ethical Considerations' section stating: due to budget constraints, the MAD system implemented in experiments includes up to six agents; although the authors consider this sufficient to meet real-world deployment requirements, investigating the behavior of larger-scale MAD systems under attack 'remains an important direction for future research.' The section also includes an ethical statement that the work aims to uncover MAD vulnerabilities in order to ultimately enhance security and robustness, and that the proposed method is intended solely for scientific research purposes.</t>
+          <t>There is no separate 'Limitations' section, but Section 7 ('Conclusion and Future Work') explicitly states that the study primarily focuses on the white-box setting, and that 'additional investigations are necessary to fully comprehend the feasibility of generating Neural Execs for closed-source LLMs'; the authors note existing black-box adversarial-suffix methods built on GCG could in principle be adapted to their objective but leave this to future work. Section 6.1 also notes an inherent limitation for defenses (and implicitly for the authors' own proposed mitigations): the optimization reveals a large and diverse space of valid, structurally dissimilar triggers, undermining dictionary/blacklist-based detection, and an attacker aware that no input filtering is applied can relax the paper's own optimization constraints (no newlines, ASCII-only, no special formatting tokens) to forge even stronger and less detectable triggers.</t>
         </is>
       </c>
       <c r="F209" s="5" t="n"/>
@@ -9618,7 +9606,7 @@
       <c r="H209" s="5" t="n"/>
       <c r="I209" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -9628,7 +9616,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -9643,7 +9631,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>This paper introduces MAD-SPEAR, a targeted prompt injection attack against multi-agent debate (MAD) systems -- a paradigm where multiple LLM agents iteratively interact to improve collective reasoning quality, which prior work has largely evaluated for accuracy and scalability while assuming all participating agents behave honestly. MAD-SPEAR compromises only a small subset of agents via prompt injection, but crafts the injected prompts (drawing on Sybil-attack concepts from distributed systems) so that each compromised agent effectively impersonates multiple plausible-sounding personas, generating a disproportionate volume of plausible-but-incorrect responses. This exploits LLMs' inherent conformity tendency -- the well-documented phenomenon that agents in a debate are more likely to converge toward the majority or most frequently repeated opinion as debate rounds and peer pressure increase -- to propagate misinformation and degrade the quality and correctness of the group's eventual consensus, even though only a minority of agents are actually compromised. The authors formalize the notion of MAD fault-tolerance (adapting Byzantine fault-tolerant consensus definitions from distributed systems, including timing assumptions for debate rounds) to rigorously characterize when and how a MAD system's consensus mechanism breaks down under adversarial pressure, and develop a comprehensive evaluation framework spanning accuracy, consensus efficiency, and scalability (measured via output token consumption) to jointly characterize an attack's impact. MAD-SPEAR is additionally designed to be composable with other attack strategies, such as a communication attack that drops or corrupts inter-agent messages, forming an enhanced composite attack that further amplifies fault-tolerance degradation by increasing benign agents' exposure to incorrect information.</t>
+          <t>Neural Exec reframes the construction of prompt-injection 'execution triggers' (the adversarial string that forces an LLM to treat an injected payload as an instruction) as a differentiable, GCG-style discrete optimization problem rather than manual prompt engineering. A trigger is modeled as a prefix+suffix pair (Υpre, Υpost) wrapped around an attacker payload; the optimization maximizes, via teacher-forced log-likelihood with positional decay weighting, the probability that the target LLM (given the armed payload injected into a prompt sampled from a large synthetic universe of prompts/tasks and Alpaca-derived payloads) reproduces the output it would have generated for the payload alone — approximating a formal 'universal execution' objective. Candidate token substitutions are proposed via top-k lowest-gradient sampling (as in GCG) and selected by loss on a batch of sampled prompt/payload pairs, optionally biased by an additional embedding-distance term to promote 'Semantic-Oblivious Injection' (SOI) — indistinguishability of the payload-laden guide-text from clean guide-text under a RAG embedding model. To survive RAG pipelines specifically, triggers are additionally constrained to contain no newlines ('inlining', preventing chunker-induced fragmentation) and are optimized to remain functional when merged inline with arbitrary 'guide-text' chosen to match a target query's retrieval relevance (Inline Invariant Composition). The resulting Neural Exec triggers are shown to be far more effective than handcrafted ones, to persist through simulated RAG chunking/retrieval, to generalize across models when bootstrapped from a handcrafted seed, and to reveal transferable, human-interpretable adversarial patterns (code-comment syntax, approximated chat-template tags) that the authors distill back into improved handcrafted triggers effective even against a closed-source model in a black-box setting.</t>
         </is>
       </c>
       <c r="F210" s="5" t="n"/>
@@ -9651,7 +9639,7 @@
       <c r="H210" s="5" t="n"/>
       <c r="I210" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9649,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -9684,7 +9672,7 @@
       <c r="H211" s="5" t="n"/>
       <c r="I211" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9682,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -9717,7 +9705,7 @@
       <c r="H212" s="5" t="n"/>
       <c r="I212" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -9727,7 +9715,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -9750,7 +9738,7 @@
       <c r="H213" s="5" t="n"/>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -9760,7 +9748,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -9775,7 +9763,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F214" s="5" t="n"/>
@@ -9783,7 +9771,7 @@
       <c r="H214" s="5" t="n"/>
       <c r="I214" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -9793,7 +9781,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -9808,7 +9796,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>multi-agent</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F215" s="5" t="n"/>
@@ -9816,7 +9804,7 @@
       <c r="H215" s="5" t="n"/>
       <c r="I215" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9814,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -9849,7 +9837,7 @@
       <c r="H216" s="5" t="n"/>
       <c r="I216" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -9859,7 +9847,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -9874,7 +9862,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F217" s="5" t="n"/>
@@ -9882,7 +9870,7 @@
       <c r="H217" s="5" t="n"/>
       <c r="I217" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9880,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -9907,7 +9895,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F218" s="5" t="n"/>
@@ -9915,7 +9903,7 @@
       <c r="H218" s="5" t="n"/>
       <c r="I218" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -9925,7 +9913,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -9940,7 +9928,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>execution</t>
         </is>
       </c>
       <c r="F219" s="5" t="n"/>
@@ -9948,7 +9936,7 @@
       <c r="H219" s="5" t="n"/>
       <c r="I219" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -9958,7 +9946,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -9973,7 +9961,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F220" s="5" t="n"/>
@@ -9981,7 +9969,7 @@
       <c r="H220" s="5" t="n"/>
       <c r="I220" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -9991,7 +9979,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -10014,7 +10002,7 @@
       <c r="H221" s="5" t="n"/>
       <c r="I221" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10012,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -10039,7 +10027,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>Code/artifact released: 'Artifact, 2026. URL https://github.com/Intelligent-CAT-Lab/icat-agent' cited as reference [7] and referenced directly in the Concluding Remarks ('Our artifact is available at [7]').</t>
+          <t>No code, dataset, or tool artifact is released. The paper is a methodology/framework proposal; it explicitly states 'The paper focuses on the methodology, definitions, and metrics required to instantiate an executable evaluation protocol; a full empirical study is ongoing but is not reported here,' and the Limitations section states 'the next step is to implement the instrumentation, contract library, perturbation and fault operators, and governance mechanisms in a prototype.'</t>
         </is>
       </c>
       <c r="F222" s="5" t="n"/>
@@ -10047,7 +10035,7 @@
       <c r="H222" s="5" t="n"/>
       <c r="I222" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -10057,7 +10045,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -10072,7 +10060,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>On SWE-bench Verified: MiniMax M2.5 (strong frontier model) and GPT-5-mini (mid-tier model). On SWE-bench Pro: GPT-5.4-xhigh (best-performing leaderboard model) and Claude Sonnet 4.5 (mid-tier model). All baselines are run with the same underlying models as icat-agent for controlled comparison.</t>
+          <t>None. This is a framework-design paper with no implemented prototype and no empirical evaluation; no specific LLMs are used or benchmarked. The framework is described as model-agnostic, intended to be instantiated later across representative LLM-orchestrated multi-agent systems.</t>
         </is>
       </c>
       <c r="F223" s="5" t="n"/>
@@ -10080,7 +10068,7 @@
       <c r="H223" s="5" t="n"/>
       <c r="I223" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10078,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -10105,7 +10093,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>SWE-bench Verified (500 human-validated real-world GitHub issue instances, the most widely adopted agentic issue-resolution benchmark) and SWE-bench Pro (long-horizon, multi-language software engineering problems, designed for more complex repairs than Verified). Evaluated across difficulty levels (easy/medium/hard for Verified based on human-fixing-time labels; grouped by number of golden-patch-modified files for Pro), across four programming languages (Python, TypeScript, JavaScript, Go) for Pro, and across issue-description quality groups (high vs. low quality, determined by icat-agent's own rubric-based checker).</t>
+          <t>No new dataset or benchmark is executed; the paper proposes a methodology that would reuse and adapt existing agent evaluation suites (AgentBench, GAIA, AgentDojo, HarmBench, AgentHarm) as seed task specifications and prompt templates, re-instantiating them with the deployed system's tool layer, action interface, and governance policy for future contract-monitored evaluation. No results from actually running these suites are reported.</t>
         </is>
       </c>
       <c r="F224" s="5" t="n"/>
@@ -10113,7 +10101,7 @@
       <c r="H224" s="5" t="n"/>
       <c r="I224" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10111,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -10138,7 +10126,7 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>icat-agent consistently outperforms baseline scaffolds across all settings. On SWE-bench Verified, it resolves 79.4% (MiniMax M2.5) and 64.6% (GPT-5-mini) of issues, improving over mini-SWE-agent by 3.6 and 8.4 percentage points respectively. On SWE-bench Pro, it resolves 62.2% with Claude Sonnet 4.5 (+18.5pp over SWE-agent) and 67.4% with GPT-5.4-xhigh (+8.3pp over mini-SWE-agent, +6.3pp over Claude Code) -- the 67.4% result surpasses the previously best-reported SWE-bench Pro result (59.10%, mini-SWE-agent+GPT-5.4-xhigh) by 8.3 points. Gains are larger on SWE-bench Pro (more challenging, less contaminated) than Verified, larger on non-Python languages (TypeScript +23.4pp, JavaScript +50.0pp over SWE-agent with Claude Sonnet 4.5), larger on low-quality/ambiguous issue descriptions (e.g., low-quality resolution improving from 44.9% to 61.4% with Claude Sonnet 4.5, and 57.5% to 73.3% with GPT-5.4-xhigh), and larger on harder/more complex multi-file problems (16.1-23.6% improvement over SWE-agent, 5.3-7.2% over Claude Code across difficulty groups). icat-agent is also more cost-effective, reducing average cost by $1.18/instance versus the multi-agent Claude Code baseline while achieving higher resolution rates. Component ablations show: the Issue Quality Checker improves cost-efficiency without hurting repair quality (forcing exploration on all instances increased cost by 18-24% while resolution rate stayed flat or dropped slightly); the Explorer agent achieves strong file-level localization (87.6-88.7% recall on Verified, 74.7-80.6% precision/63.9-64.4% recall on Pro); and a controlled comparison isolating communication design (icat-agent's event-based message passing vs. a Claude-Code-SDK-based orchestrator using shared context, both with identical specialized agent roles) shows icat-agent still wins 67.4% vs. 61.1% under identical GPT-5.4-xhigh, indicating gains come from the communication protocol itself, not merely agent specialization. The reproduction-test-generation component (Validator) produces genuine fail-to-pass reproduction tests in 74.6-80.5% of Verified instances and 74.8-78.3% of Pro instances.</t>
+          <t>There are no empirical results, since the paper is a proposed methodology and evaluation protocol rather than an implemented system. The 'contribution' is conceptual/methodological: (1) a system model and five-class failure taxonomy (F1: coordination collapse and non-termination; F2: error amplification and unsupported-claim propagation; F3: role drift and boundary violations; F4: tool/memory injection and interface poisoning; F5: misuse and harmful task execution) with formal operational definitions and trace-derived metrics (e.g., unsupported-claim rate, propagation rate, per-agent drift score); (2) Message-Action Traces (MAT), a contract-carrying execution record supporting replay and localization of the first violating step; (3) stress testing formulated as budgeted counterexample search over bounded perturbation/fault schedules, with robustness curves R(B) as a function of perturbation budget; (4) a governance layer (L4) enforcing per-agent least-privilege capability sets and action-time policy mediation (allow/rewrite/block), with human-in-the-loop escalation for pre-labeled high-impact actions; and (5) a recommended reporting format (nominal performance tables, fault-injection outcome tables, robustness curves, contract-violation profiles) intended to make future empirical comparisons across orchestration designs reproducible.</t>
         </is>
       </c>
       <c r="F225" s="5" t="n"/>
@@ -10146,7 +10134,7 @@
       <c r="H225" s="5" t="n"/>
       <c r="I225" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10144,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -10171,7 +10159,7 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>SWE-Agent and mini-SWE-Agent (widely used single-agent scaffolds on the SWE-bench leaderboards), and Claude Code (used via the Claude Code SDK to construct an orchestrator/sub-agent multi-agent scaffold with specialized sub-agents for exploration, patch editing, and validation -- representing a common shared-context multi-agent design pattern, used as the strongest widely-used multi-agent baseline).</t>
+          <t>N/A - no empirical comparison is performed. The paper positions its failure taxonomy relative to a prior empirical characterization of multi-agent LLM breakdowns (cited as reference [22]), and discusses (without benchmarking) prior frameworks/tools such as AutoGen, LangGraph, LangSmith, RAGAS, NeMo Guardrails, and security-focused benchmarks (BIPIA, AgentDojo, WASP, InjecAgent, AgentHarm, HarmBench) as related but distinct prior work.</t>
         </is>
       </c>
       <c r="F226" s="5" t="n"/>
@@ -10179,7 +10167,7 @@
       <c r="H226" s="5" t="n"/>
       <c r="I226" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -10189,7 +10177,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -10204,7 +10192,7 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial in the traditional security sense, though the paper explicitly names and formally distinguishes two context-integrity failure modes it calls 'context poisoning': (1) test overfitting, where the same agent that generates a patch also writes a weak or incomplete reproduction test, then generates a patch that satisfies that flawed test rather than fixing the actual underlying bug; and (2) patch overfitting, where the agent postpones test generation until after patching, writing tests that happen to pass on the already-generated (possibly incorrect) patch rather than genuinely validating whether the patch resolves the issue. Both arise specifically because monolithic single-agent scaffolds share one growing context across localization, patching, and validation, so the same contaminated reasoning trace that produced a flawed patch also produces the 'independent' check that approves it -- the paper's proposed decentralized, event-based multi-agent architecture is explicitly designed to structurally prevent this self-referential context contamination by giving the Validator agent an isolated context that never sees the Patch Editor's internal reasoning.</t>
+          <t>Formal, security-relevant threat model embedded in the failure taxonomy: untrusted inputs (e.g., inbound emails, retrieved snippets, or document excerpts) may carry indirect prompt injection attempts that enter via memory or external interfaces and alter agent policy so that an unsafe action is selected (F4: tool/memory injection and interface poisoning), while F5 (misuse and harmful task execution) formalizes the case where a system completes a harmful multi-step objective or performs a harmful external action without triggering refusal, containment, or escalation, with 'excessive agency' formalized as the condition where an agent is granted enough permissions that plausible perturbations or ordinary service failures can lead to unsafe external actions (Pr(action in unsafe set) &gt; epsilon).</t>
         </is>
       </c>
       <c r="F227" s="5" t="n"/>
@@ -10212,7 +10200,7 @@
       <c r="H227" s="5" t="n"/>
       <c r="I227" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -10222,7 +10210,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -10237,7 +10225,7 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>Explicit 'Threats to Validity' section covering three standard software-engineering-research validity dimensions. External validity: icat-agent is evaluated only on software engineering benchmarks that may not fully represent industrial-scale systems with much larger codebases, so observed performance may not fully generalize to large-scale production repositories; mitigated partially by evaluating on two benchmarks covering a broad range of real-world bug complexity and multiple model backbones. Internal validity: errors in reproduction-test generation or exploration-based localization can propagate downstream to the Patch Editor and affect patch quality; the event-driven communication design mitigates but does not eliminate this by restricting inter-agent interaction to structured message payloads rather than shared internal context. Construct validity: measuring effectiveness solely via issue-resolution rate (whether a patch passes the benchmark's golden tests) under-approximates true correctness, since golden tests can reject a patch that actually resolves the issue but doesn't match the reference solution's exact structure, and localization metrics treat golden-patch files as the only correct fix location even though valid alternative locations may exist -- the authors argue this bias likely underestimates icat-agent's absolute performance but applies equally to all compared methods, preserving the validity of relative comparisons.</t>
+          <t>The paper has an explicit 'Limitations and next steps' subsection (Section V-E, following the recommended reporting format), stating that 'the current contribution focuses on methodology, definitions, and evaluation estimators rather than an empirical demonstration,' and that the next steps are to implement the instrumentation, contract library, perturbation and fault operators, and governance mechanisms in a prototype, then execute a systematic empirical study across representative workloads and orchestration variants to quantify utility, robustness, containment, and governance behavior and assess reproducibility via replay artifacts and regression testing. Future work also includes studying coverage criteria for regression test suites (contract coverage, boundary/interface coverage, risk-conditioned coverage) and integrating the protocol into the software development lifecycle as evaluation-driven development.</t>
         </is>
       </c>
       <c r="F228" s="5" t="n"/>
@@ -10245,7 +10233,7 @@
       <c r="H228" s="5" t="n"/>
       <c r="I228" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10243,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -10270,7 +10258,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>icat-agent is a decentralized, multi-agent scaffold for resolving real-world software issues (bug localization, reproduction, patching, and validation) that directly targets context degradation and context poisoning as failure modes of dominant monolithic single-agent scaffolds (e.g., SWE-agent), which maintain a single shared, growing context across the entire trajectory. The paper identifies two specific context-poisoning failure patterns that arise from this shared-context design: test overfitting (the same agent writes both a weak reproduction test and a patch tailored to satisfy that weak test rather than the actual bug) and patch overfitting (tests are generated after patching and thus biased to validate the already-produced patch rather than independently checking correctness) -- both consequences of validation not being genuinely independent from patch generation when both share one contaminated context. icat-agent's core architectural response is to replace shared context with synchronous, event-based message passing between specialized agents (an Issue Quality Checker/router, an Explorer for repository investigation, a Patch Editor, and an independent Validator), exposing only structured outcomes between agents rather than raw internal reasoning traces, so that validation genuinely operates on an isolated context uncontaminated by the patch-generation agent's potentially flawed reasoning. A rubric-based Issue Quality Checker further adapts the workflow dynamically: well-specified, high-quality issue descriptions bypass exploration and proceed directly to parallel patch generation and independent validation, while ambiguous or low-quality issue descriptions first trigger the Explorer agent to gather missing repository context before repair begins -- avoiding both unnecessary exploration cost on clear issues and under-informed patching on unclear ones. Evaluated on SWE-bench Verified and SWE-bench Pro across multiple model backbones (MiniMax M2.5, GPT-5-mini, Claude Sonnet 4.5, GPT-5.4-xhigh) against SWE-agent, mini-SWE-agent, and a Claude-Code-SDK-based shared-context multi-agent orchestrator baseline, icat-agent consistently and substantially improves issue-resolution rates across all difficulty levels, programming languages, and issue-quality groups (with the largest gains concentrated on harder, lower-quality, and non-Python instances, consistent with the paper's mechanistic story), while also being more cost-effective than the comparable multi-agent Claude Code baseline -- with the isolated communication-design ablation confirming that the improvement stems specifically from the event-based, context-isolated communication protocol rather than merely from having specialized agent roles.</t>
+          <t>This paper proposes a trace-based assurance framework for LLM-orchestrated multi-agent (Agentic AI) systems, addressing failures beyond incorrect final outputs -- including non-termination, role drift, unsupported-claim propagation, and attacks via untrusted context or external channels -- that arise from long-horizon interaction, stochastic decisions, and side effects such as API calls, database writes, and message sends. The core representation is the Message-Action Trace (MAT), which records each execution run as a sequence of typed steps (user/agent messages, tool calls, memory reads/writes, delegation, termination) augmented with provenance and machine-checkable contract verdicts; a contract is a boolean predicate over a step-level MAT record or a trace prefix (e.g., 'tool calls with side effects must be preceded by a verification action within h steps') that localizes the first violating step and supports deterministic replay. The framework organizes evaluation into four layers: L1-L3 form an assurance harness that instruments execution, applies perturbation/fault schedules at service, retrieval, and memory boundaries, and checks contracts; L4 is a runtime governance layer that enforces per-agent least-privilege capability sets (Allow(action, agent) iff required capabilities are a subset of the agent's assigned capability set) and mediates actions via allow/rewrite/block decisions, escalating pre-labeled high-impact actions (e.g., send_email, payment, delete, grant_access) to human-in-the-loop approval. Stress testing is formulated as a budgeted counterexample search: perturbation and fault schedules are drawn from an operator family under a cost budget to find schedules that trigger contract violations, with results summarized as robustness curves R(B) over the perturbation budget B. The paper also formalizes a five-class failure taxonomy (F1-F5, spanning coordination collapse, unsupported-claim propagation, role drift, interface/memory poisoning, and misuse/harmful task execution) with operational, trace-computable metrics for each class, and defines a recommended reporting format (nominal performance tables, fault-injection outcome tables, robustness curves, contract-violation profiles) intended to support reproducible comparison across orchestration designs -- but the paper stops at specifying this methodology and protocol, with prototype implementation and empirical validation explicitly deferred to future work.</t>
         </is>
       </c>
       <c r="F229" s="5" t="n"/>
@@ -10278,7 +10266,7 @@
       <c r="H229" s="5" t="n"/>
       <c r="I229" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10276,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -10311,7 +10299,7 @@
       <c r="H230" s="5" t="n"/>
       <c r="I230" s="5" t="inlineStr">
         <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -10321,7 +10309,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -10344,7 +10332,7 @@
       <c r="H231" s="5" t="n"/>
       <c r="I231" s="5" t="inlineStr">
         <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -10354,7 +10342,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -10377,7 +10365,7 @@
       <c r="H232" s="5" t="n"/>
       <c r="I232" s="5" t="inlineStr">
         <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10375,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -10402,7 +10390,7 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F233" s="5" t="n"/>
@@ -10410,7 +10398,7 @@
       <c r="H233" s="5" t="n"/>
       <c r="I233" s="5" t="inlineStr">
         <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -10420,7 +10408,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -10435,7 +10423,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>tool-metadata</t>
+          <t>cross-modal</t>
         </is>
       </c>
       <c r="F234" s="5" t="n"/>
@@ -10443,7 +10431,7 @@
       <c r="H234" s="5" t="n"/>
       <c r="I234" s="5" t="inlineStr">
         <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10441,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -10476,7 +10464,7 @@
       <c r="H235" s="5" t="n"/>
       <c r="I235" s="5" t="inlineStr">
         <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10474,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -10509,7 +10497,7 @@
       <c r="H236" s="5" t="n"/>
       <c r="I236" s="5" t="inlineStr">
         <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10507,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -10542,7 +10530,7 @@
       <c r="H237" s="5" t="n"/>
       <c r="I237" s="5" t="inlineStr">
         <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -10552,7 +10540,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -10567,7 +10555,7 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>reasoning</t>
+          <t>ingestion</t>
         </is>
       </c>
       <c r="F238" s="5" t="n"/>
@@ -10575,7 +10563,7 @@
       <c r="H238" s="5" t="n"/>
       <c r="I238" s="5" t="inlineStr">
         <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -10585,7 +10573,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -10608,7 +10596,7 @@
       <c r="H239" s="5" t="n"/>
       <c r="I239" s="5" t="inlineStr">
         <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -10618,7 +10606,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -10641,7 +10629,7 @@
       <c r="H240" s="5" t="n"/>
       <c r="I240" s="5" t="inlineStr">
         <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10639,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
@@ -10666,7 +10654,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>Code released at https://github.com/shishishi123/Tool-Guard, per the abstract.</t>
+          <t>No code/artifact release found. No GitHub, HuggingFace, or project-page URL for DE-FIVE's implementation, weights, or generated malicious-image datasets appears in the extracted text (the only GitHub link present is a citation to LLaVA's project blog, not this paper's own release).</t>
         </is>
       </c>
       <c r="F241" s="5" t="n"/>
@@ -10674,7 +10662,7 @@
       <c r="H241" s="5" t="n"/>
       <c r="I241" s="5" t="inlineStr">
         <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10672,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -10699,7 +10687,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>On AgentDojo: GPT-4o-mini, GPT-4o, Gemini-2.5-Pro, Gemini-2.5-Flash, and Claude-3.5-Haiku (5 LLM planners). On ASB (Agent Security Bench): GPT-4o-mini, GPT-4o-2024-05-13, GPT-4o, GPT-4-turbo, and GPT-3.5-turbo (5 LLMs). Token-overhead, latency, and adaptive-attack experiments were run specifically on GPT-4o-mini; the ablation study was run on GPT-4o.</t>
+          <t>Two open-source vision-language model (VLM) families: LLaVA-1.6 (LLaVA-1.6-Vicuna-7B) and Phi-3 (Phi-3-Vision), following the experimental protocol of the prior VLMGuard paper. These are selected as state-of-the-art open-source VLM architectures with different design paradigms/training strategies to assess generalizability across heterogeneous backbones. No closed-weight/commercial VLMs (e.g. GPT-4V, GPT-4o) are evaluated experimentally, though they are cited as motivating examples of the VLM class.</t>
         </is>
       </c>
       <c r="F242" s="5" t="n"/>
@@ -10707,7 +10695,7 @@
       <c r="H242" s="5" t="n"/>
       <c r="I242" s="5" t="inlineStr">
         <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -10717,7 +10705,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -10732,7 +10720,7 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>AgentDojo (Debenedetti et al., 2024): 4 suites (Banking, Slack, Travel, Workspace), 97 tasks, 76 unique tools, with ~40% of tools poisoned per suite (5/11 in Banking and Slack, 12/24 in Travel, 12/27 in Workspace). ASB (Agent Security Bench, Zhang et al., 2024): 10 task scenarios (e.g., e-commerce, autonomous driving, finance) with 10 scenario-specific agents and 400+ tools (benign and attack).</t>
+          <t>Two attack-category test sets are used. For meta-instruction (indirect prompt injection) prompts: the dataset introduced by prior work (VLMGuard), comprising 25 benign ImageNet images each paired with 60 questions, plus 300 malicious meta-instruction images generated from 40 training question-answer pairs spanning five meta-objectives (LANGUAGE, POLITICS, FORMALITY, SPAM, SENTIMENT), yielding a test set of 25 benign and 300 malicious images each paired with 20 textual questions. For jailbreak prompts: malicious images generated using the XSTest dataset (250 safe prompts, 200 crafted unsafe prompts) combined with 200 benign ImageNet images, yielding a test set of 200 benign and 200 malicious images paired with 50 safe and 100 unsafe textual prompts. Evaluation metric is AUROC, averaged over five runs, following the protocol of prior baselines (Perplexity, GradSafe, VLMGuard).</t>
         </is>
       </c>
       <c r="F243" s="5" t="n"/>
@@ -10740,7 +10728,7 @@
       <c r="H243" s="5" t="n"/>
       <c r="I243" s="5" t="inlineStr">
         <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10738,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -10765,7 +10753,7 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>On AgentDojo (Fig. 2), existing defenses only partially mitigate cross-tool description poisoning -- ASR remains relatively high (e.g., ~10-43% across tool filtering, repeated prompt, system prompt, Drift, Progent) -- while Tool-Guard drives ASR down to 2.1%. Across the 5 tested LLM planners (Fig. 4), Tool-Guard reduces ASR to near-zero in every case (e.g., GPT-4o-mini: 10.3%-&gt;1.0%; GPT-4o: 43.3%-&gt;2.1%; Gemini-2.5-Pro: 32.0%-&gt;1.0%; Claude-3.5-Haiku: 4.1%-&gt;1.0%; Gemini-2.5-Flash: 52.6%-&gt;0.0%) while largely preserving benign and attack-condition utility. On ASB (Fig. 5) ASR similarly drops from 72-96% (no defense) to 0.0-8.0% with Tool-Guard across GPT-4-Turbo, GPT-4o (old/new), GPT-4o-mini, and GPT-3.5-Turbo. Token overhead is about 1.45x/1.39x the no-defense baseline for benign/attack tasks respectively (1.22M/2.24M tokens on AgentDojo), less than half the tokens used by Repeat Prompt, Drift, or Progent. Latency overhead is about 3.7x the no-defense baseline (vs. 1.2x for Progent and 7.3x for Drift). Stability analysis across 5 repeated runs (Tab. 3) shows Tool-Guard keeps ASR at low single digits with small standard deviations across GPT-4o-mini, GPT-4o, and Gemini-2.5-Flash. Under critical-tool poisoning (Tab. 5), ASR rises to 19.59% without defense but Tool-Guard holds it to 3.09%. Under semantic-adaptive attacks (alignment-evasion, suspicion-evasion, combined), Tool-Guard keeps ASR at exactly 0.00%; under stronger optimization-based adaptive attacks (PAIR, TAP), ASR under defense rises slightly but stays very low (2.06% for PAIR, 0.00% for TAP), versus 13-15% without defense (Tab. 4). An ablation (Tab. 6) shows validation alone (without dynamic tool-set partitioning) preserves the low ASR but causes substantial utility drops (benign utility -16.49%, attack utility -31.96%), indicating both components are needed -- validation as the security gatekeeper, partitioning to preserve utility.</t>
+          <t>DE-FIVE, a fully training-free hybrid detector combining a black-box Fourier-domain (DFT-based) detector with a white-box image-vector-embedding detector using only a few-shot (k=32) malicious reference set, achieves the highest average AUROC among all tested methods on both meta-instruction and jailbreak prompt detection across both model backbones (Tables I-II). Against meta-instruction prompts: DE-FIVE reaches 95.35% average AUROC on LLaVA-1.6 and 94.87% on Phi-3, beating the strongest training-based baseline VLMGuard (92.87% and 92.11%) by 2.6 and 2.9 percentage points respectively, and far outperforming the only other training-free baseline, GradSafe (65.17% and 63.62%). Against jailbreak prompts: DE-FIVE reaches 95.22% AUROC on LLaVA-1.6 and 96.03% on Phi-3, again the best of all six compared methods (VLMGuard: 94.27%/95.74%; GradSafe: 91.09%/82.77%; JailGuard: 88.49%/82.91%; MirrorCheck: 83.26%/73.86%; Perplexity: 69.31%/94.36%). A key cross-cutting finding is that no existing single baseline generalizes well across both attack categories -- e.g. Perplexity achieves the highest AUROC on some meta-instruction sub-objectives but the lowest on jailbreak prompts -- whereas DE-FIVE maintains consistently strong performance on both. Ablations confirm the DFT-based combined black-box score (86.52% avg meta-instruction / 87.25% jailbreak) outperforms either individual Fourier feature alone (High-to-Low Frequency Energy Ratio: 66.72%/65.01%; Spectral Entropy Surrogate: 83.18%/84.26%), and that increasing the white-box detector's few-shot budget from k=32 to k=64 further improves AUROC (92.19% to 94.71% average on meta-instruction) enough to surpass VLMGuard outright, though k=32 is retained as the practical default given VLMGuard's greater data requirements. A weighting-coefficient ablation finds the optimal blend differs by attack type (alpha=0.2 best for meta-instruction, alpha=0.1 best for jailbreak prompts), with more weight generally favoring the white-box embedding-based detector.</t>
         </is>
       </c>
       <c r="F244" s="5" t="n"/>
@@ -10773,7 +10761,7 @@
       <c r="H244" s="5" t="n"/>
       <c r="I244" s="5" t="inlineStr">
         <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -10783,7 +10771,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
@@ -10798,7 +10786,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>Five prior/alternative defenses: (1) tool filtering (Willison, 2023/Invariantlabs) -- pre-execution static removal of tools whose descriptions are misaligned with the task; (2) repeated prompt (Schulhoff, 2024) -- re-injecting the original user query after each tool execution; (3) system prompt -- explicitly instructing the LLM to ignore potential injected content in tool descriptions; (4) Drift (Li et al., 2025a) and (5) Progent (Shi et al., 2025), two state-of-the-art system-level security-policy defenses. A no-defense baseline is also reported throughout.</t>
+          <t>Five state-of-the-art detection baselines: Perplexity (text-based perplexity detection), GradSafe (the only other training-free baseline, using safety-critical gradient analysis), MirrorCheck, JailGuard, and VLMGuard (the strongest baseline overall, an unlabeled-data-based maliciousness-estimation classifier requiring a training phase and a carefully tuned mixing ratio for its training set).</t>
         </is>
       </c>
       <c r="F245" s="5" t="n"/>
@@ -10806,7 +10794,7 @@
       <c r="H245" s="5" t="n"/>
       <c r="I245" s="5" t="inlineStr">
         <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10804,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -10831,7 +10819,7 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>Formal adversarial threat model for 'cross-tool description poisoning.' Adversary capability/goal: the attacker can tamper with the natural-language descriptions of non-sensitive, weakly-regulated tools (e.g., 'get weather') while leaving their execution semantics Exec_k unchanged, with the objective of steering the planner into later invoking a different, safety-critical tool to perform a malicious action a_mal -- critically, the poisoned tool itself is never selected as part of the plan. Under MCP deployments, the adversary may compromise tool descriptions served by non-safety-critical MCP servers, or operate attacker-controlled servers offering such tools, to influence invocations on separate, higher-value safety-critical servers. Formally: the adversary selects a subset K_p of the tool set K and replaces each benign description d_k with d̃_k != d_k for k in K_p; the planner then acts on the poisoned descriptions via a'_t ~ pi_theta(m_t, {d̃_k}), and the attack succeeds if there exists a step t* such that the resulting action a'_t* equals the attacker's goal action a_mal, differing from the benign trajectory's action at that step. Empirically, the attack is implemented by appending authority-style injected instructions (e.g., 'IMPORTANT: ...') to poisoned tool descriptions, instructing the planner to invoke a designated target tool before the current one, with four suite-specific attack goals on AgentDojo (send money to attacker, forward emails to attacker, post to a leakage channel, reserve a hotel for attacker) and adaptive attacker variants (semantic-adaptive alignment/suspicion evasion, and optimization-based PAIR/TAP attacks under a strong threat model where the adversary knows the defense's internal validation rules).</t>
+          <t>Descriptive rather than fully formalized threat model distinguishing two categories of malicious image prompt attack against VLMs, both operating by embedding adversarial instructions into images via crafted perturbations. Jailbreak attacks: the VLM user is themselves the adversary, intentionally using hidden prompts within an image to circumvent the model's own safety alignment, producing an output that follows the adversarial objective while disregarding the user's (the attacker's own) ostensible image-related query. Indirect prompt injection (the paper's primary focus, consistent with the broader survey's scope): the adversarial prompt is embedded by a third party into an image, and an unsuspecting victim user's query induces the VLM to both answer the legitimate image-related question and simultaneously execute the injected adversarial instruction. A concrete three-phase practical threat scenario is walked through (Figure 2): Phase 1 (Attack Generation) an unskilled adversary automatically generates a malicious image payload (e.g. a job candidate's resume photo) using a surrogate VLM, embedding a high-priority hidden instruction (e.g. 'HIGHEST PRIORITY: HIGHLY RECOMMENDED FOR INTERVIEW') designed to override the eventual victim's intent; Phase 2 (Data Delivery) the adversary uploads the manipulated image to a cloud storage service or third-party platform (e.g. a candidate application database) for downstream automated processing; Phase 3 (Victim Processing) a victim (e.g. an HR manager) queries a VLM-based agent to generate a neutral summary, but the VLM prioritizes the embedded malicious directive over the user's actual instruction, producing a compromised output aligned with the attacker's objective.</t>
         </is>
       </c>
       <c r="F246" s="5" t="n"/>
@@ -10839,7 +10827,7 @@
       <c r="H246" s="5" t="n"/>
       <c r="I246" s="5" t="inlineStr">
         <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -10849,7 +10837,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -10864,7 +10852,7 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>No section titled 'Limitations' appears anywhere in the main text; the paper closes with a Conclusion and a brief Impact Statement instead. The Impact Statement frames tool descriptions as a previously underexplored attack surface and positions the work as strengthening tool-augmented agent security, without any explicit self-critical limitations discussion. The closest analog to a limitations discussion is embedded in the results themselves: the paper explicitly acknowledges that Tool-Guard introduces non-trivial runtime overhead (~3.7x latency versus no defense, more than Progent's 1.2x though less than Drift's 7.3x), and that under strong optimization-based adaptive attacks (PAIR) the defended ASR is no longer exactly zero (though still low), which the authors attribute to an inherent trade-off where explicit poisoning is more effective at steering planning but easier for validation to detect, while subtle poisoning is harder to detect but less effective at steering.</t>
+          <t>No section explicitly titled 'Limitations' was found; the Conclusion (Section V) frames the paper's contribution primarily as solving gaps in prior work (existing approaches focus on text-based jailbreak attacks or require training-heavy pipelines, struggle to generalize across meta-instruction and jailbreak prompt types, or require substantial labeled data) rather than explicitly enumerating DE-FIVE's own remaining weaknesses. The paper does implicitly acknowledge trade-offs within its ablation studies: the white-box detector's default few-shot setting (k=32) is explicitly chosen as 'a more practical and data-efficient scenario' at the cost of somewhat lower AUROC than a higher-resource k=64 setting, acknowledging that 'access to large numbers of high-quality malicious examples may be limited' in practice; and the weighting-coefficient ablation shows performance is sensitive to a hyperparameter (alpha) that must be tuned differently per attack type (0.2 for meta-instruction vs. 0.1 for jailbreak), an implicit calibration burden not otherwise discussed as a limitation.</t>
         </is>
       </c>
       <c r="F247" s="5" t="n"/>
@@ -10872,7 +10860,7 @@
       <c r="H247" s="5" t="n"/>
       <c r="I247" s="5" t="inlineStr">
         <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -10882,7 +10870,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -10897,7 +10885,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>This paper formalizes and studies 'cross-tool description poisoning,' an attack in which an adversary manipulates the natural-language description metadata of a non-critical, weakly-regulated tool in order to steer an LLM agent's planner into invoking a different, safety-critical tool maliciously -- notably, without the poisoned tool itself ever being selected, making the attack stealthier than direct tool-preference manipulation and poorly addressed by prior defenses that rely on static description scanning (which misses semantically implicit influence and produces false positives on benign cross-references like two-step verification) or on inspecting internal planner attention states (impractical for API-only commercial models). The authors first demonstrate empirically on AgentDojo that existing defenses (tool filtering, repeated-prompt reinforcement, system-prompt instructions, and the system-level Drift and Progent defenses) only partially mitigate the attack, leaving ASR at 10-43%. They then propose Tool-Guard, a system-level defense based on 'isolated planning': the tool set is dynamically partitioned into an 'Influenced' list (tools suspected of being steered by poisoned descriptions elsewhere) and an 'Others' list, and the planner is queried twice, once under each isolated description subset, producing two candidate next actions. A selection rule picks whichever candidate is a valid tool call (or one via tie-break if both are valid), and the chosen action is validated via two LLM-based semantic checks before execution -- an alignment check (is the action a plausible next step given the validated trajectory and user intent) and a suspicion check (are the action's arguments grounded in the user request or prior observations, flagging ungrounded sensitive entities like recipients or account IDs). If validation fails, the tool is moved into the Influenced list and the planner replans under the updated partition (capped at three attempts). Because the union of the two partitions always equals the full tool set, and validation context excludes the (potentially poisoned) tool descriptions themselves, Tool-Guard preserves task utility while closing off nearly the entire adaptive-attack surface. The approach also extends to MCP deployments by partitioning at the server level (Kinf/Kothers of servers rather than individual tools) to prevent cross-server poisoning. Extensive evaluation across AgentDojo (5 planner models) and ASB (5 models, 400+ tools) shows Tool-Guard reduces ASR to near-zero while preserving most utility, at a token-overhead cost of ~1.4x and latency cost of ~3.7x relative to no defense, and remains robust to both semantic-adaptive and optimization-based (PAIR/TAP) adaptive attacks; an ablation confirms both the validation gatekeeper and the dynamic partitioning mechanism are necessary, with partitioning specifically responsible for utility preservation.</t>
+          <t>This paper addresses malicious image prompt attacks against vision-language models (VLMs), which embed adversarial instructions into images through crafted perturbations, spanning two categories: jailbreak attacks (where the VLM user is the adversary, seeking to bypass the model's own safety alignment) and indirect prompt injection attacks (where a third party embeds a hidden instruction into an image that later manipulates an unsuspecting victim's query). The authors identify that existing defenses either target only jailbreak attacks, require extensive labeled data or retraining, or (in the case of the closest prior work, VLMGuard) rely on a carefully tuned data-mixing ratio for classifier training that complicates deployment -- and note a broader gap in defenses specifically targeting indirect prompt injection via images. To address this, they propose DE-FIVE, a fully training-free hybrid detection framework combining two complementary detectors. The black-box detector operates purely on the input image's Fourier-domain features, combining a High-to-Low Frequency Energy Ratio measure and a Spectral Entropy Surrogate into a unified DFT-based malicious score, requiring no access to model internals. The white-box detector exploits the observation that clean and malicious image prompts induce measurably distinct hidden-state representations within the VLM's visual encoder under perturbation (using masked perturbations to compute robust image vector embeddings), constructing a malicious-similarity score from only a small few-shot reference set of known malicious examples (k=32 in the main experiments) rather than a full labeled training set. The two detectors' scores are then combined via a tunable non-negative weighting coefficient into a final hybrid detection score, with the optimal weighting differing by attack type. Evaluated on two open-source VLM backbones (LLaVA-1.6-Vicuna-7B and Phi-3-Vision) against both meta-instruction (indirect prompt injection) and jailbreak prompt test sets, DE-FIVE consistently outperforms five prior detection baselines in AUROC while incurring zero additional training or computational overhead, positioning it as a practical, easily deployable, training-free solution for real-world VLM safety applications that generalizes across both major categories of malicious image prompt attacks where prior single-purpose defenses do not.</t>
         </is>
       </c>
       <c r="F248" s="5" t="n"/>
@@ -10905,7 +10893,7 @@
       <c r="H248" s="5" t="n"/>
       <c r="I248" s="5" t="inlineStr">
         <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -10915,7 +10903,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -10938,7 +10926,7 @@
       <c r="H249" s="5" t="n"/>
       <c r="I249" s="5" t="inlineStr">
         <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
@@ -10948,7 +10936,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -10971,7 +10959,7 @@
       <c r="H250" s="5" t="n"/>
       <c r="I250" s="5" t="inlineStr">
         <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
@@ -10981,7 +10969,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -11004,7 +10992,7 @@
       <c r="H251" s="5" t="n"/>
       <c r="I251" s="5" t="inlineStr">
         <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11002,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -11037,7 +11025,7 @@
       <c r="H252" s="5" t="n"/>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
@@ -11047,7 +11035,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -11070,7 +11058,7 @@
       <c r="H253" s="5" t="n"/>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
@@ -11080,7 +11068,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -11095,7 +11083,7 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F254" s="5" t="n"/>
@@ -11103,7 +11091,7 @@
       <c r="H254" s="5" t="n"/>
       <c r="I254" s="5" t="inlineStr">
         <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11101,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -11136,7 +11124,7 @@
       <c r="H255" s="5" t="n"/>
       <c r="I255" s="5" t="inlineStr">
         <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
@@ -11146,7 +11134,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -11169,7 +11157,7 @@
       <c r="H256" s="5" t="n"/>
       <c r="I256" s="5" t="inlineStr">
         <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
@@ -11179,7 +11167,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -11202,7 +11190,7 @@
       <c r="H257" s="5" t="n"/>
       <c r="I257" s="5" t="inlineStr">
         <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11200,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -11235,7 +11223,7 @@
       <c r="H258" s="5" t="n"/>
       <c r="I258" s="5" t="inlineStr">
         <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
@@ -11245,7 +11233,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -11268,7 +11256,7 @@
       <c r="H259" s="5" t="n"/>
       <c r="I259" s="5" t="inlineStr">
         <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
@@ -11278,7 +11266,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -11293,7 +11281,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>No code/artifact release found. No GitHub, HuggingFace, or project-page URL appears anywhere in the extracted text.</t>
+          <t>No code, checkpoint, or dataset release is mentioned anywhere in the paper (main text or appendix). Only a baseline (M-Flow) is cited with a GitHub link (https://github.com/FlowElement-ai/m_flow); PRISM's own implementation is described only via pseudocode (Algorithm 1) and prose, with no stated public repository.</t>
         </is>
       </c>
       <c r="F260" s="5" t="n"/>
@@ -11301,7 +11289,7 @@
       <c r="H260" s="5" t="n"/>
       <c r="I260" s="5" t="inlineStr">
         <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11299,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -11326,7 +11314,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>Qwen3 model family (without thinking mode) at four scales: 4B, 8B, 14B, and 32B, used as both the personalized-LLM backbone and the context-distillation student/teacher. Qwen3-Embedding-8B is used for retrieval. TSUBASA-PRO (an optimized-inference-prompt/hyperparameter variant) is primarily compared against Qwen3-8B and against prior SOTA baselines that use comparable-sized models such as Qwen2.5-7B (used by Memory-R1). GPT-5-nano is used as the LLM-as-a-Judge for the J metric in SOTA comparisons.</t>
+          <t>gpt-4o-mini is used as both the answer model and the LLM-judge for all same-protocol experiments (temperature 0.0). A different-protocol variant swaps in gpt-5.5 as the answer model while holding the retrieval pipeline and ingest checkpoint fixed. Baseline systems compared: Full Context (gpt-4o-mini reading the entire ~26K-token dialogue), MAGMA, Mem0, Mem0g (graph variant of Mem0), M-Flow (different-protocol, uses gpt-5-mini), and the managed Mem0 commercial platform.</t>
         </is>
       </c>
       <c r="F261" s="5" t="n"/>
@@ -11334,7 +11322,7 @@
       <c r="H261" s="5" t="n"/>
       <c r="I261" s="5" t="inlineStr">
         <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
@@ -11344,7 +11332,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -11359,7 +11347,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>Two long-horizon personalization benchmarks: LoCoMo (long-term conversations spanning several months across 10 participant pairs, averaging 19.3 sessions and 304.9 turns per pair; evaluation restricted to the last 8 pairs per prior literature convention, yielding 1,294 QA items after filtering out ungroundable questions from an initial 1,307) and LongMemEval (extremely long user-assistant conversations averaging 47.7 sessions and 493.4 turns per pair, 500 QA items with one unique test item per user profile). Evaluation uses six metrics: token-level Precision, Recall, F1, BLEU-1, ROUGE-L, and LLM-as-a-Judge (J, via GPT-5-nano, used only for SOTA comparison to minimize cost), plus inference efficiency measured by input token length.</t>
+          <t>LoCoMo, a long-conversation QA benchmark covering single-hop, multi-hop, temporal, and open-domain reasoning categories (categories 1-4, 1,540 QA pairs total); category 5 (adversarial refusal) is explicitly excluded since it tests refusal rather than retrieval.</t>
         </is>
       </c>
       <c r="F262" s="5" t="n"/>
@@ -11367,7 +11355,7 @@
       <c r="H262" s="5" t="n"/>
       <c r="I262" s="5" t="inlineStr">
         <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
@@ -11377,7 +11365,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -11392,7 +11380,7 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>On LoCoMo, ablating TSUBASA's components shows RAG(observation) consistently beats RAG(utterance) (validating high-density observation extraction), Vanilla Training collapses to near-random performance (F1 5.76-8.28 across scales) confirming a severe train-inference gap, and TSUBASA's evolving-memory variant achieves peak F1 (up to 37.63 on Qwen3-14B) while minimizing input length, though the evolving-memory manager only realizes its full benefit beyond 8B parameters and the overall approach saturates at 32B (only 0.7% above RAG-observation). Against prior SOTA on LoCoMo (Table 3), TSUBASA-PRO achieves the best overall F1 (45.24) and J (72.59), outperforming Memory-R1 (best variant 43.14 F1/61.51 J) by 4.9% and Mem0 (30.61 F1/53.30 J) by nearly 50%, and delivers 17-49% improvements on single- and multi-hop QA specifically; its only weakness is the Open Domain sub-task, where its factoid-QA-optimized synthetic data generation pipeline underperforms (26.16-27.81 F1 vs. Mem0's 32.74 and Memory-R1's 44.78-46.86). On LongMemEval, TSUBASA-PRO matches Memory-R1's performance while retrieving only 3 memory pieces versus Memory-R1's 60, and surpasses Mem0 by over 20% average across three quality metrics. A Pareto-improvement analysis shows TSUBASA breaks the standard quality-efficiency tradeoff: on Qwen3-14B, TSUBASA (evolving) at k=2 achieves 37.10 F1 using only 42.5 tokens, versus RAG(utterance) at k=10 needing 232.08 tokens for just 33.75 F1, and TSUBASA at k=5 (~100 tokens) approaches the full-session-history performance ceiling (2,158 tokens) with 20x fewer tokens. A top-d truncation ablation for the context-distillation KL objective identifies d=5 as a sweet spot, with d=1 (hard labels) performing worst and d&gt;=10 degrading due to long-tail noise.</t>
+          <t>PRISM reaches an overall LLM-judge score of 0.831 on LoCoMo cat1-4 using ~2,023 context tokens per query, beating every same-protocol baseline: +14.2pp over Mem0g (0.684), +14.0pp over MAGMA (0.688), and +35.2pp over Full Context (0.481), while using roughly 13x fewer tokens than Full Context (~26,031 tokens). PRISM also achieves the best accuracy-per-token efficiency (0.411 judge points per 1K tokens vs. 0.379 for next-best Mem0). Swapping the answer model to gpt-5.5 (same retrieval pipeline/budget) lifts the score to 0.891 (+6.0pp), and the Mem0 commercial platform reaches 0.916 but at ~3.4x PRISM's context budget with roughly one-third PRISM's per-1K efficiency. Ablations (Table 2/6) show both typed relation paths and LLM-side evidence compression are individually necessary -- removing either component (e.g., -N3 evidence compression) collapses performance back toward baseline regions, with paired-bootstrap 95% CIs and McNemar mid-p tests confirming the effects are not noise.</t>
         </is>
       </c>
       <c r="F263" s="5" t="n"/>
@@ -11400,7 +11388,7 @@
       <c r="H263" s="5" t="n"/>
       <c r="I263" s="5" t="inlineStr">
         <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11398,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -11425,7 +11413,7 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>Two vanilla RAG baselines (retrieving raw utterances vs. extracted observations) and two training-based baselines (standard fine-tuning on raw conversations, and a RAG-free/no-grounding variant of TSUBASA) are used for internal ablation, alongside static-accumulation vs. evolving-memory variants within the TSUBASA framework. For SOTA comparison, TSUBASA-PRO is compared against LoCoMo's original baseline, A-Mem, Mem0, and Memory-R1 (both PPO and GRPO reward-training variants), the latter representing the prior state of the art.</t>
+          <t>Full Context (whole-dialogue baseline), MAGMA (graph-based agentic memory), Mem0 and Mem0g (flat and graph-augmented production memory systems), M-Flow (different-protocol reference using a stronger answer model), and the managed Mem0 commercial platform (different-protocol reference). Component ablations (N1 typed-path disabled, N2 query-sensitive costing disabled, N3 compression disabled, N4 intent routing disabled) serve as internal baselines isolating each of PRISM's four modules.</t>
         </is>
       </c>
       <c r="F264" s="5" t="n"/>
@@ -11433,7 +11421,7 @@
       <c r="H264" s="5" t="n"/>
       <c r="I264" s="5" t="inlineStr">
         <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
@@ -11443,7 +11431,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -11458,7 +11446,7 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. This is a personalization/memory-architecture paper, not a security paper. The incidental failure mode of interest is loss of personalization fidelity and privacy risk in memory-augmented systems: standard episodic memory acts as a linear-growing vector database that fails on reflective, temporally-compositional queries; parametric approaches suffer a train-inference gap from scarce labeled user data; and some prior evolving-memory systems (specifically Memory-R1, cited by name) 'compromise production privacy through cross-user training,' while others use destructive DELETE operations that erase historical context and obscure the cause of user preference evolution. TSUBASA is explicitly designed to avoid the cross-user privacy leakage present in Memory-R1 by operating strictly within each target user's own data portfolio.</t>
+          <t>N/A - non-adversarial. This is a retrieval-efficiency/accuracy paper for long-horizon agent memory, not a security paper; the paper's own 'Broader impacts' discussion notes an incidental failure mode of interest: PRISM faithfully retrieves whatever the upstream ingestion pipeline stored, so biases, sensitive content, or privacy-relevant information already present in the memory graph may be surfaced verbatim in retrieved context, and the authors recommend pairing PRISM with ingestion-side filtering, access controls, and privacy/fairness checks.</t>
         </is>
       </c>
       <c r="F265" s="5" t="n"/>
@@ -11466,7 +11454,7 @@
       <c r="H265" s="5" t="n"/>
       <c r="I265" s="5" t="inlineStr">
         <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11464,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -11491,7 +11479,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'Limitations' section (unnumbered, following Section 7 Conclusion). Two points are stated. 'Evaluation benchmarks': the two benchmarks used (LoCoMo and LongMemEval), while aiming to cover a diverse array of long-horizon personalization tasks, cannot comprehensively represent the entire spectrum of such tasks; future work should extend TSUBASA to more applications and examine its generalizability in the wild. 'Model Scales': experiments cover Qwen3 models from 4B to 32B parameters, but due to budget constraints the authors did not extend experiments to larger-scale models; they expect findings to hold at larger scales (having already discussed a potential saturation effect observed post-32B in Section 6.1) but leave direct application of TSUBASA to larger models to future work.</t>
+          <t>An explicit 'Limitations and Broader Impacts' appendix (Appendix A) states PRISM currently focuses only on retrieval-side compression for conversational memory and does not yet extend to long agent trajectories involving actions, tool calls, observations, plans, and feedback, though the authors argue its training-free, plug-in design should adapt naturally to richer trajectory-level memory graphs as agent pipelines evolve. The same appendix's 'Broader impacts' subsection flags the privacy/bias pass-through risk described in threat_model as a limitation requiring downstream mitigation rather than something PRISM itself addresses.</t>
         </is>
       </c>
       <c r="F266" s="5" t="n"/>
@@ -11499,7 +11487,7 @@
       <c r="H266" s="5" t="n"/>
       <c r="I266" s="5" t="inlineStr">
         <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
@@ -11509,7 +11497,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -11524,7 +11512,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>TSUBASA ('Two-winged per Sonalization Unifying Bi-Directional Autonomous memory Storage and parametric Assimilation') addresses long-horizon personalization in LLMs by identifying and resolving two technical bottlenecks in existing memory-augmented personalized-LLM (PLLM) systems: a train-inference gap (naive fine-tuning on raw conversations fails to prepare parametric memory for complex evaluation-time personalization tasks) and a quality-efficiency tradeoff (standard RAG-based memory correlates better response quality with retrieving more memory entries, incurring prohibitive token/compute costs). The framework has two synergistic 'wings.' The dynamic memory-writing wing extracts core, high-density factual observations from raw conversation utterances, then uses an autonomous memory manager that applies structured ADD/UPDATE/RECONCILE/IGNORE operations to evolve the memory store over time, preventing redundancy and resolving conflicts (rather than using destructive DELETE operations that erase historical context, as in some prior systems). The internalized memory-reading wing tackles the scarcity of labeled user-specific training data via a self-learning pipeline that synthesizes QA pairs from user data, augmented with a teacher-student context-distillation objective: a frozen teacher model with full exposure to session context produces an output distribution that a trainable student model (which sees only the question, not the full context) is trained to match via per-token KL divergence, approximated over the top-d highest-probability tokens (d=5 found optimal) to keep the computation tractable given large vocabularies. At inference time, retrieved observations are combined with the internalized parametric knowledge for factual grounding, since the paper's ablations show parameterization alone (without explicit RAG-backed grounding) causes severe performance collapse. This architecture is explicitly designed to avoid the privacy risks of cross-user training present in comparable prior systems (e.g., Memory-R1) by training and personalizing strictly within each individual user's own data.</t>
+          <t>PRISM is a training-free, retrieval-side framework for long-horizon LLM agent memory that treats retrieval as a joint retrieval-and-compression problem over a graph-structured memory built once at write time via schema-guided extraction, exposing six typed edge types over a hierarchy of entities, facets, facet points, and episodes. At query time it combines four orthogonal inference-time modules: (N4) Adaptive Intent Routing, which classifies query intent through a zero-LLM-call cascade (regex keyword gate, then embedding prototype match, then falling back to a single LLM classification call only when needed) so most queries incur no per-query LLM cost for routing; (N1) Hierarchical Bundle Search, which enumerates typed relation paths from FAISS-retrieved anchor nodes across path templates and selects a top-K=10 candidate bundle via per-episode minimum-cost path scoring; (N2) Query-Sensitive Edge Costing, which reweights typed-edge traversal costs according to the detected query intent so that retrieval follows the relation type relevant to the question rather than flat surface similarity; and (N3) Evidence Compression, a single LLM-side re-ranking/compression call that condenses the K=10 candidate bundle down to M=5 episode summaries forming the final answer-side context. Because retrieval is formulated as min-cost selection over typed path templates rather than a learned policy, PRISM requires no fine-tuning and plugs into any backend exposing the same edge schema, letting it occupy what the authors identify as a previously underserved 'high-accuracy/low-cost' corner of the accuracy-context-cost frontier relative to ingestion-heavy systems (Mem0, A-Mem), retrieval-management systems (MemGPT, LightMem), and graph-based memory systems (GraphRAG, MAGMA).</t>
         </is>
       </c>
       <c r="F267" s="5" t="n"/>
@@ -11532,7 +11520,7 @@
       <c r="H267" s="5" t="n"/>
       <c r="I267" s="5" t="inlineStr">
         <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11530,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -11565,7 +11553,7 @@
       <c r="H268" s="5" t="n"/>
       <c r="I268" s="5" t="inlineStr">
         <is>
-          <t>e21b1f9b29e0fc0671300eab00a762c316c19793</t>
+          <t>453fe21f545a9b7f885aea2ee9165e4ada4e144f</t>
         </is>
       </c>
     </row>
@@ -11575,7 +11563,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -11590,7 +11578,7 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F269" s="5" t="n"/>
@@ -11598,7 +11586,7 @@
       <c r="H269" s="5" t="n"/>
       <c r="I269" s="5" t="inlineStr">
         <is>
-          <t>e21b1f9b29e0fc0671300eab00a762c316c19793</t>
+          <t>453fe21f545a9b7f885aea2ee9165e4ada4e144f</t>
         </is>
       </c>
     </row>
@@ -11608,7 +11596,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -11631,7 +11619,7 @@
       <c r="H270" s="5" t="n"/>
       <c r="I270" s="5" t="inlineStr">
         <is>
-          <t>e21b1f9b29e0fc0671300eab00a762c316c19793</t>
+          <t>453fe21f545a9b7f885aea2ee9165e4ada4e144f</t>
         </is>
       </c>
     </row>
@@ -11641,7 +11629,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -11664,7 +11652,7 @@
       <c r="H271" s="5" t="n"/>
       <c r="I271" s="5" t="inlineStr">
         <is>
-          <t>e21b1f9b29e0fc0671300eab00a762c316c19793</t>
+          <t>453fe21f545a9b7f885aea2ee9165e4ada4e144f</t>
         </is>
       </c>
     </row>
@@ -11674,7 +11662,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -11689,7 +11677,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F272" s="5" t="n"/>
@@ -11697,7 +11685,7 @@
       <c r="H272" s="5" t="n"/>
       <c r="I272" s="5" t="inlineStr">
         <is>
-          <t>e21b1f9b29e0fc0671300eab00a762c316c19793</t>
+          <t>453fe21f545a9b7f885aea2ee9165e4ada4e144f</t>
         </is>
       </c>
     </row>
@@ -11707,7 +11695,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
@@ -11722,7 +11710,7 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F273" s="5" t="n"/>
@@ -11730,7 +11718,7 @@
       <c r="H273" s="5" t="n"/>
       <c r="I273" s="5" t="inlineStr">
         <is>
-          <t>e21b1f9b29e0fc0671300eab00a762c316c19793</t>
+          <t>453fe21f545a9b7f885aea2ee9165e4ada4e144f</t>
         </is>
       </c>
     </row>
@@ -11740,7 +11728,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -11755,7 +11743,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F274" s="5" t="n"/>
@@ -11763,7 +11751,7 @@
       <c r="H274" s="5" t="n"/>
       <c r="I274" s="5" t="inlineStr">
         <is>
-          <t>e21b1f9b29e0fc0671300eab00a762c316c19793</t>
+          <t>453fe21f545a9b7f885aea2ee9165e4ada4e144f</t>
         </is>
       </c>
     </row>
@@ -11773,7 +11761,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -11788,7 +11776,7 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F275" s="5" t="n"/>
@@ -11796,7 +11784,7 @@
       <c r="H275" s="5" t="n"/>
       <c r="I275" s="5" t="inlineStr">
         <is>
-          <t>e21b1f9b29e0fc0671300eab00a762c316c19793</t>
+          <t>453fe21f545a9b7f885aea2ee9165e4ada4e144f</t>
         </is>
       </c>
     </row>
@@ -11806,7 +11794,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -11829,7 +11817,7 @@
       <c r="H276" s="5" t="n"/>
       <c r="I276" s="5" t="inlineStr">
         <is>
-          <t>e21b1f9b29e0fc0671300eab00a762c316c19793</t>
+          <t>453fe21f545a9b7f885aea2ee9165e4ada4e144f</t>
         </is>
       </c>
     </row>
@@ -11839,7 +11827,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -11854,7 +11842,7 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>one-shot</t>
+          <t>session-persistent</t>
         </is>
       </c>
       <c r="F277" s="5" t="n"/>
@@ -11862,7 +11850,7 @@
       <c r="H277" s="5" t="n"/>
       <c r="I277" s="5" t="inlineStr">
         <is>
-          <t>e21b1f9b29e0fc0671300eab00a762c316c19793</t>
+          <t>453fe21f545a9b7f885aea2ee9165e4ada4e144f</t>
         </is>
       </c>
     </row>
@@ -11872,7 +11860,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -11895,7 +11883,7 @@
       <c r="H278" s="5" t="n"/>
       <c r="I278" s="5" t="inlineStr">
         <is>
-          <t>e21b1f9b29e0fc0671300eab00a762c316c19793</t>
+          <t>453fe21f545a9b7f885aea2ee9165e4ada4e144f</t>
         </is>
       </c>
     </row>
@@ -11905,7 +11893,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -11918,13 +11906,17 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E279" s="2" t="n"/>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>The paper states its phase-aware profiling harness is 'to be open-sourced' (listed explicitly as one of the paper's four contributions: 'A phase-aware profiling harness (to be open-sourced) tracking tokens, model calls, GPU utilization, and latency across construction, retrieval, and generation'), though no specific GitHub URL is given in the extracted main text.</t>
+        </is>
+      </c>
       <c r="F279" s="5" t="n"/>
       <c r="G279" s="5" t="n"/>
       <c r="H279" s="5" t="n"/>
       <c r="I279" s="5" t="inlineStr">
         <is>
-          <t>e21b1f9b29e0fc0671300eab00a762c316c19793</t>
+          <t>453fe21f545a9b7f885aea2ee9165e4ada4e144f</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11926,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -11949,7 +11941,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>None. No models are run; the review synthesizes and codes published studies.</t>
+          <t>Two serving configurations: remote API runs using GPT-4.1-mini and GPT-4o-mini (LLM calls) with Text Embedding 3 Small (embeddings), and local vLLM-served runs using an LLM capability ladder of Qwen3-32B, Qwen3-14B, Qwen3-8B, and Qwen3-1.7B paired with Qwen3-Embedding-0.6B for embeddings, used to systematically vary model capability and study how construction/retrieval quality and cost scale with model size.</t>
         </is>
       </c>
       <c r="F280" s="5" t="n"/>
@@ -11957,7 +11949,7 @@
       <c r="H280" s="5" t="n"/>
       <c r="I280" s="5" t="inlineStr">
         <is>
-          <t>e21b1f9b29e0fc0671300eab00a762c316c19793</t>
+          <t>453fe21f545a9b7f885aea2ee9165e4ada4e144f</t>
         </is>
       </c>
     </row>
@@ -11967,7 +11959,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -11982,7 +11974,7 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>No datasets or benchmarks. Evidence base is 89 peer-reviewed publications (2015 to October 2025) from IEEE Xplore, ACM Digital Library and ScienceDirect, of which 81 form the analytical corpus, coded against MITRE ATLAS v5.4.0 on three axes with seventeen operational attacker-objective patterns.</t>
+          <t>Two benchmark suites: LongMemEval (specifically LongMemEval_S_* variants), the most widely adopted long-term conversational memory benchmark, and MemoryAgentBench (MAB), used as the primary benchmark, which converts long-horizon interaction histories into task families requiring retrieval and reasoning over accumulated agent memory; Table 2 summarizes the task families evaluated.</t>
         </is>
       </c>
       <c r="F281" s="5" t="n"/>
@@ -11990,7 +11982,7 @@
       <c r="H281" s="5" t="n"/>
       <c r="I281" s="5" t="inlineStr">
         <is>
-          <t>e21b1f9b29e0fc0671300eab00a762c316c19793</t>
+          <t>453fe21f545a9b7f885aea2ee9165e4ada4e144f</t>
         </is>
       </c>
     </row>
@@ -12000,7 +11992,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -12015,7 +12007,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>The corpus concentrates overwhelmingly on the prompt interface - trust boundary TB1 accounts for 83.9% - and on two attacker objectives, Instruction Hijack and Policy Bypass, leaving other boundaries underexplored and lacking both attack characterization and defence proposals. The authors' interpretation is the notable part and converges independently on this SoK's own conclusions: this architectural narrowness does not reflect the multi-component architecture of production LLM systems, and the concentration reflects a research incentive structure favouring reproducible prompt-level experiments over architecturally complex assessments at tool and memory boundaries. They further identify a maturity gradient in which defence development is concentrated at the prompt interface while other boundaries remain at an early stage - which is the same finding this corpus reaches from the opposite direction in RQ5/RQ6, where execution-stage defenses proved the least evaluated and least runnable. Contextual figures quoted from reviewed studies include attack success rates reaching 67%, and adversarial prompt and fine-tuning attacks on medical LLMs altering vaccination recommendations and generating harmful medication guidance with success exceeding 80%. The three-axis framework and coded corpus are offered as a baseline for tracking coverage as deployment architectures expand.</t>
+          <t>The paper's central empirical finding is that construction (not query-time serving) dominates the agent memory lifecycle cost, and that construction cost is structurally embedding- and prefill-dominated, creating direct resource contention with latency-sensitive QA/retrieval traffic when co-located on the same serving stack. On end-to-end cost (Table 3, LongMemEval, Qwen3-32B, n=300 queries), energy-hungry systems like A-Mem and MIRIX reach 115 kJ and 197 kJ respectively -- a 28-47x energy premium over cheaper baselines that the paper argues must be justified by proportionally higher capability, which is often not observed. Systems show sharply divergent robustness to weaker local models: MIRIX fails entirely at the smallest model, Qwen3-1.7B, due to its dependence on the LLM for routed typed-memory search, while other systems (e.g., BM25, which uses purely lexical top-k retrieval and never routes through an LLM for retrieval) remain robust regardless of backbone capability. The paper also finds that systems with similar aggregate accuracy occupy very different positions on the cost-latency-freshness tradeoff space, and that BM25's strong aggregate accuracy showing should not be read as indicating it is broadly sufficient, since its purely lexical matching lacks semantic robustness that other paradigms provide. From these findings the paper derives 10 concrete system recommendations covering construction scheduling, minimum capability floors per system, cost amortization via query volume, freshness-latency tradeoffs, and fleet-scale management.</t>
         </is>
       </c>
       <c r="F282" s="5" t="n"/>
@@ -12023,7 +12015,7 @@
       <c r="H282" s="5" t="n"/>
       <c r="I282" s="5" t="inlineStr">
         <is>
-          <t>e21b1f9b29e0fc0671300eab00a762c316c19793</t>
+          <t>453fe21f545a9b7f885aea2ee9165e4ada4e144f</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12025,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -12048,7 +12040,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>Not applicable - a systematic review. Comparative analysis is internal to the coded corpus: distribution across trust boundaries (TB1 dominant at 83.9%), across five ATLAS attacker-goal categories and seventeen operational patterns, and across research orientations (attack versus defence versus conceptual), the last supplying the offensive/defensive balance analysis the review identifies as missing from prior work.</t>
+          <t>Ten representative agent memory systems are characterized and implicitly compared against one another, spanning four architectural paradigms identified in the paper's taxonomy: (I) flat/full-context retrieval baselines including BM25 (lexical inverted-index top-k retrieval, no LLM-mediated construction or retrieval); (III) consolidating structure-augmented RAG systems including Mem0 (rewrites conversation turns into atomic facts, dense store, fact top-k retrieval), SimpleMem (sliding-window processing into a hybrid store with iterative hybrid retrieval), and A-Mem (treats memory as an evolving note graph with graph-structured map-reduce retrieval); and (IV) agentic control-flow systems including Letta (implements the MemGPT abstraction with blocks+archive storage and tool-call-based retrieval) and MIRIX (routes incoming information to typed memory stores via a multi-store database with routed typed-memory search). Each system's construction/storage/retrieval/mutability properties are cataloged in a taxonomy table (Table 1).</t>
         </is>
       </c>
       <c r="F283" s="5" t="n"/>
@@ -12056,7 +12048,7 @@
       <c r="H283" s="5" t="n"/>
       <c r="I283" s="5" t="inlineStr">
         <is>
-          <t>e21b1f9b29e0fc0671300eab00a762c316c19793</t>
+          <t>453fe21f545a9b7f885aea2ee9165e4ada4e144f</t>
         </is>
       </c>
     </row>
@@ -12066,7 +12058,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -12079,13 +12071,17 @@
           <t>freetext</t>
         </is>
       </c>
-      <c r="E284" s="2" t="n"/>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>N/A - non-adversarial. This is a systems-characterization/benchmarking paper studying the infrastructure cost and performance properties of agent memory systems, not a security paper; the incidental failure mode of interest is systemic cost and latency mismatch -- specifically, that agent memory construction (embedding generation and LLM-mediated extraction/consolidation of past interactions into persistent memory) imposes prefill-and-embedding-dominated costs that are structurally in tension with the latency requirements of concurrent, latency-sensitive query-time retrieval and generation traffic when both are served on the same infrastructure stack.</t>
+        </is>
+      </c>
       <c r="F284" s="5" t="n"/>
       <c r="G284" s="5" t="n"/>
       <c r="H284" s="5" t="n"/>
       <c r="I284" s="5" t="inlineStr">
         <is>
-          <t>e21b1f9b29e0fc0671300eab00a762c316c19793</t>
+          <t>453fe21f545a9b7f885aea2ee9165e4ada4e144f</t>
         </is>
       </c>
     </row>
@@ -12095,7 +12091,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -12110,7 +12106,7 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>The review defines existing knowledge as literature published in specific databases at a particular time, which bounds coverage to three sources (IEEE Xplore, ACM Digital Library, ScienceDirect) and to peer-reviewed venues - a deliberate quality control that necessarily excludes arXiv preprints, where a substantial share of this field's fastest-moving attack and defence work appears, and which likely accounts for the smaller corpus (89 publications) relative to preprint-inclusive reviews. Only 81 of the 89 included publications form the analytical corpus. The coding depends on judgment about where adversarial content first enters the decision pathway, and no inter-rater reliability is surfaced. As a review it produces no primary evidence: the concentration findings describe the literature rather than the underlying risk distribution, so TB1's 83.9% share indicates where researchers work, not where systems are most vulnerable - a distinction the authors themselves draw when noting the mismatch with production architectures.</t>
+          <t>The paper does not contain a section titled 'Limitations,' but the 'Discussion &amp; Conclusion' section (Section 5) explicitly identifies 'several open challenges [that] extend beyond our current scope': (1) multi-node and multi-agent deployments introduce consistency and coordination requirements across distributed memory stores that single-node characterization (as performed in this paper) cannot capture; (2) multimodal memory -- persisting and retrieving images, audio, and structured observations alongside text -- is described as 'an emerging and less mature frontier' that the authors expect will amplify the construction cost, storage footprint, and retrieval complexity challenges identified in this text-only study. The paper frames its taxonomy and profiling methodology as 'a foundation for characterizing these richer settings as they mature,' implicitly acknowledging that the current study's scope (single-node, text-only, ten representative systems) does not yet cover these harder deployment regimes.</t>
         </is>
       </c>
       <c r="F285" s="5" t="n"/>
@@ -12118,7 +12114,7 @@
       <c r="H285" s="5" t="n"/>
       <c r="I285" s="5" t="inlineStr">
         <is>
-          <t>e21b1f9b29e0fc0671300eab00a762c316c19793</t>
+          <t>453fe21f545a9b7f885aea2ee9165e4ada4e144f</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12124,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>A Systematic Literature Review of Prompt Injection Attacks in LLM-Integrated Systems</t>
+          <t>Agent Memory: Characterization and System Implications of Stateful Long-Horizon Workloads</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -12143,7 +12139,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>PRISMA-compliant systematic literature review of prompt injection in LLM-integrated systems, and the closest methodological neighbour to this SoK in the corpus. It opens from the same premise - prompt injection exploits the inability to distinguish trusted instructions from untrusted content when both are processed as natural-language tokens - and makes the same structural observation, that as models are integrated into tool-augmented and memory-enabled systems the attack surface expands beyond the prompt interface. Its stated gap is that no existing review maps this landscape against standardised adversarial frameworks or analyses the balance between offensive and defensive research. Method: IEEE Xplore, ACM Digital Library and ScienceDirect searched for peer-reviewed studies published 2015 to October 2025, yielding 89 included publications of which 81 form the analytical corpus, with an eight-step methodology adapted from PRISMA. Each paper is coded on three axes: trust boundary (the inference-time architectural interface at which adversarial content first enters the model's decision pathway), ATLAS attacker goal (mapped to five categories from MITRE ATLAS v5.4.0, with attacker objectives further classified into seventeen operational patterns aligned to ATLAS techniques), and research orientation (attack, defence, or conceptual/framework contribution). The alignment to MITRE ATLAS is the differentiator from this project's own taxonomy, which is built bottom-up from the corpus rather than mapped onto an external standard.</t>
+          <t>This paper presents the first systems-level characterization of agent memory workloads -- the infrastructure that lets LLM agents persistently store, retrieve, and incrementally update state across sessions, generalizing retrieval-augmented generation (RAG) from static document retrieval to mutable, agent-produced state management. The paper makes four contributions. First, a system-oriented taxonomy classifies agent memory systems along four axes -- construction mechanism, storage organization, retrieval policy, and mutability/update strategy -- covering four broad paradigms: flat retrieval (e.g., BM25 lexical indexing), LLM-mediated extraction, consolidating structure-augmented RAG (e.g., Mem0's atomic-fact rewriting, SimpleMem's hybrid sliding-window store, A-Mem's evolving note graph), and agentic control-flow systems (e.g., Letta's MemGPT-style blocks-and-archive abstraction, MIRIX's routed typed-memory search across a multi-store database) -- with each paradigm predicted to exhibit a distinct cost signature. Second, the authors build a phase-aware profiling harness that attributes system cost (tokens, model calls, GPU utilization, latency, and energy) separately to three phases of the agent memory pipeline: construction (the write path, where interaction history is ingested, chunked, and stored/consolidated into persistent memory), retrieval (the read path, where relevant memory entries are selected and assembled into the prompt), and generation (the final LLM call that produces the agent's response). Third, using this harness, the paper empirically characterizes ten representative agent memory systems across two benchmark suites (LongMemEval and MemoryAgentBench), under both remote API-served models (GPT-4.1-mini/GPT-4o-mini with Text Embedding 3 Small) and a local capability ladder of open Qwen3 models (32B down to 1.7B) paired with Qwen3-Embedding-0.6B, revealing how design choices in each paradigm shift cost between the write path and read path, how capability degrades (sometimes catastrophically) as the underlying LLM shrinks, and how construction dominates total lifecycle cost and energy consumption in a way that is structurally in tension with latency-sensitive query-time serving. Fourth, the paper synthesizes these findings into ten concrete system-design recommendations for practitioners deploying agent memory at scale, covering construction scheduling policies, minimum model-capability floors per memory-system paradigm, cost amortization strategies via query volume, freshness-versus-latency tradeoffs for memory staleness management, and fleet-scale infrastructure management considerations.</t>
         </is>
       </c>
       <c r="F286" s="5" t="n"/>
@@ -12151,7 +12147,7 @@
       <c r="H286" s="5" t="n"/>
       <c r="I286" s="5" t="inlineStr">
         <is>
-          <t>e21b1f9b29e0fc0671300eab00a762c316c19793</t>
+          <t>453fe21f545a9b7f885aea2ee9165e4ada4e144f</t>
         </is>
       </c>
     </row>
@@ -12171,7 +12167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12250,22 +12246,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Diverse and Effective Red Teaming with Auto-generated Rewards and Multi-step Reinforcement Learning</t>
+          <t>SecureGov-Agent: A Governance-Centric Multi-Agent Framework for Privacy-Preserving and Attack-Resilient LLM Agents</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>attack / failure mechanism</t>
+          <t>defense / fix</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>UNNAMED: diverse RL red-teaming (auto-generated rewards + multi-step RL)</t>
+          <t>SecureGov-Agent</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>multi-agent</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -12279,7 +12275,7 @@
       <c r="J2" s="5" t="n"/>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>43408b3330d05250412940a0ea08791b35ebd185</t>
+          <t>e2e5529df48fe6cf893da483360958b32d829724</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12285,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>DRIFT: Dynamic Rule-Based Defense with Injection Isolation for Securing LLM Agents</t>
+          <t>Robustness via Referencing: Defending against Prompt Injection Attacks by Referencing the Executed Instruction</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -12299,7 +12295,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>DRIFT (Dynamic Rule-based Isolation Framework for Trustworthy agentic systems)</t>
+          <t>Robustness via Referencing (instruction-referencing defense)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -12318,7 +12314,7 @@
       <c r="J3" s="5" t="n"/>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>ec9062053726fa4c501b7deb016b2174bd93cc21</t>
+          <t>712e08695ec807163afbbfd9f442ab027ccc29ac</t>
         </is>
       </c>
     </row>
@@ -12328,17 +12324,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Sentinel: SOTA model to protect against prompt injections</t>
+          <t>Prompt Injection as Role Confusion</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Sentinel (qualifire/prompt-injection-sentinel)</t>
+          <t>CoT Forgery (Chain-of-Thought Forgery)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -12357,7 +12353,7 @@
       <c r="J4" s="5" t="n"/>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>d9303eb738a56b0e72404d3ad57964c25611a226</t>
+          <t>3a6ca08f3507de0d642286defa5431f4088d0880</t>
         </is>
       </c>
     </row>
@@ -12367,22 +12363,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard: Safety Monitoring for Computer-Use Agents via Low-Dimensional Projections</t>
+          <t>Pandora: Jailbreak GPTs by Retrieval Augmented Generation Poisoning</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>ProjGuard</t>
+          <t>PANDORA (RAG Poisoning jailbreak)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -12396,7 +12392,7 @@
       <c r="J5" s="5" t="n"/>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>45c41693ece0aebf5d9210aa3a983046ee325c65</t>
+          <t>a2a4ddbed34916cfa345e957cf060da99685e37b</t>
         </is>
       </c>
     </row>
@@ -12406,7 +12402,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ROMA: Recursive Open Meta-Agent Framework for Long-Horizon Multi-Agent Systems</t>
+          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -12416,12 +12412,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>ROMA (Recursive Open Meta-Agents) with GEPA+</t>
+          <t>ToolSelf</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>multi-agent</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -12435,7 +12431,7 @@
       <c r="J6" s="5" t="n"/>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>5814e11d1745afb7cbec86027b01792b9addd58c</t>
+          <t>arxiv:2602.07883</t>
         </is>
       </c>
     </row>
@@ -12445,27 +12441,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FoldAct: Efficient and Stable Context Folding for Long-Horizon Search Agents</t>
+          <t>ConfusedPilot: Confused Deputy Risks in RAG-based LLMs</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>FoldAct</t>
+          <t>ConfusedPilot</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>data-exfiltration</t>
         </is>
       </c>
       <c r="G7" s="5" t="n"/>
@@ -12474,7 +12470,7 @@
       <c r="J7" s="5" t="n"/>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>a916a577bf89c4151f128e21b9fc30310b412125</t>
+          <t>9716eff749e27faf90abb1b7c88728e23ed35032</t>
         </is>
       </c>
     </row>
@@ -12484,7 +12480,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Breaking the Prompt Wall (I): A Real-World Case Study of Attacking ChatGPT via Lightweight Prompt Injection</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -12494,7 +12490,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>distraction effect (attention shift to injected instruction)</t>
+          <t>UNNAMED: rule-tag semantic reframing template attack ('Breaking the Prompt Wall')</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -12504,7 +12500,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="G8" s="5" t="n"/>
@@ -12513,7 +12509,7 @@
       <c r="J8" s="5" t="n"/>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>8c72e098e53eddb8e1e8fb05601a03a7b0ca57e0</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12519,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker: Detecting Prompt Injection Attacks in LLMs</t>
+          <t>Neural Exec: Learning (and Learning from) Execution Triggers for Prompt Injection Attacks</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Attention Tracker</t>
+          <t>Neural Exec</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -12552,7 +12548,7 @@
       <c r="J9" s="5" t="n"/>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>2b289e1d136edeb6354496518af5230bddc09e61</t>
+          <t>2f6de8291c9a803faa7f7a33c74f4a2a3debd83b</t>
         </is>
       </c>
     </row>
@@ -12562,7 +12558,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Memory in the LLM Era: Modular Architectures and Strategies in a Unified Framework</t>
+          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -12572,12 +12568,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>UNNAMED: Tree-based + hierarchical storage combined memory method (Memory in LLM Era unified framework)</t>
+          <t>MAT-based Assurance Framework (Message-Action Traces + governance layer: capability limits + action mediation)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -12591,7 +12587,7 @@
       <c r="J10" s="5" t="n"/>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>8539c9fe2bc5320a8c1f84e01c709fcca0389e94</t>
+          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
         </is>
       </c>
     </row>
@@ -12601,22 +12597,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear: A Conformity-Driven Prompt Injection Attack on Multi-Agent Debate Systems</t>
+          <t>DE-FIVE: Detecting Malicious Image Prompts via Fourier Features and Image Vector Embeddings</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>attack / failure mechanism</t>
+          <t>defense / fix</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>MAD-Spear (Conformity-Driven Prompt Injection Attack)</t>
+          <t>DE-FIVE</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>multi-agent</t>
+          <t>cross-modal</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -12630,7 +12626,7 @@
       <c r="J11" s="5" t="n"/>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>1115a843e8f3d142180f807c97f71cde65d2ad12</t>
+          <t>2609615b172dcbab3fd10fc0a3a0f2d0c318d484</t>
         </is>
       </c>
     </row>
@@ -12640,27 +12636,27 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
+          <t>PRISM: Pareto-Efficient Retrieval over Intent-Aware Structured Memory for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>attack / failure mechanism</t>
+          <t>defense / fix</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>context poisoning (self-induced, non-adversarial)</t>
+          <t>PRISM (Pareto-Efficient Retrieval over Intent-Aware Structured Memory)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>multi-agent</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="G12" s="5" t="n"/>
@@ -12669,175 +12665,19 @@
       <c r="J12" s="5" t="n"/>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2606.25514</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Unlocking Model Potentials Through Adaptive Multi-Agent Scaffolding for Efficient Issue Resolution</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>defense / fix</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>icat-agent (decentralized event-based multi-agent scaffold)</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>multi-agent</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>reasoning-corruption</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>arxiv:2606.25514</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>attack / failure mechanism</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Cross-Tool Description Poisoning</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>tool-metadata</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>goal-hijack</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Think Twice Before You Act: Protecting LLM Agents Against Tool Description Poisoning via Isolated Planning</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>defense / fix</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Tool-Guard</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>tool-metadata</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>goal-hijack</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>96146fc642ef28da0ad11f620d5d2d6e4719e4b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>TSUBASA: Improving Long-Horizon Personalization via Evolving Memory and Self-Learning with Context Distillation</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>defense / fix</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>TSUBASA (evolving memory + context distillation)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>reasoning-corruption</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>84e59205e4350c9596e4a03583fdfd114112586b</t>
+          <t>7e6bdf1fc5a332732034a9f34de501e2c0fb737a</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="G2:G16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
   </dataValidations>
